--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314FEBF7-6ECF-45E4-A243-5D6067C574F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63406A78-EC01-41A9-8E8E-D7B719E90F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17550" yWindow="2805" windowWidth="37800" windowHeight="25620" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29595" yWindow="3720" windowWidth="24480" windowHeight="25620" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="320">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -1439,6 +1439,9 @@
   </si>
   <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario7-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario1-InsultsApplied.json"} }</t>
   </si>
 </sst>
 </file>
@@ -1957,10 +1960,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1982,24 +2003,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2795,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ58"/>
+  <dimension ref="A1:AMJ59"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
@@ -2811,42 +2814,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2856,13 +2859,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2897,74 +2900,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3057,10 +3060,10 @@
       <c r="B16" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="53"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="9" t="s">
         <v>114</v>
       </c>
@@ -3262,13 +3265,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -3338,12 +3341,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>98</v>
+        <v>319</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -3352,71 +3355,63 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>2</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>70</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="E34" s="10"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="12" t="s">
-        <v>80</v>
+      <c r="G34" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -3425,7 +3420,7 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>39</v>
@@ -3438,7 +3433,7 @@
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -3447,20 +3442,20 @@
         <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -3469,20 +3464,20 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>279</v>
+        <v>57</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -3491,20 +3486,20 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F38" s="10"/>
-      <c r="G38" s="2" t="s">
-        <v>254</v>
+      <c r="G38" s="12" t="s">
+        <v>281</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3513,324 +3508,324 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H39" s="17"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B41" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="1" t="s">
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
-        <v>3</v>
-      </c>
-      <c r="B41" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8" ht="263.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H42" s="17"/>
-    </row>
-    <row r="43" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+    </row>
+    <row r="43" spans="1:8" ht="263.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="17"/>
+    </row>
+    <row r="44" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
+        <v>3</v>
+      </c>
+      <c r="B44" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="17"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="17"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H45" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>66</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>284</v>
+        <v>33</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H47" s="17"/>
-    </row>
-    <row r="48" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="H48" s="17"/>
+    </row>
+    <row r="49" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B49" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="1" t="s">
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H49" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
-        <v>4</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="H49" s="17"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H50" s="17"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>4</v>
       </c>
-      <c r="B51" s="54" t="s">
+      <c r="B51" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+    </row>
+    <row r="52" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>4</v>
+      </c>
+      <c r="B52" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="17"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="17"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E53" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>71</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="E54" s="10"/>
       <c r="F54" s="10"/>
-      <c r="G54" s="12" t="s">
-        <v>56</v>
+      <c r="G54" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F55" s="10"/>
-      <c r="G55" s="2" t="s">
-        <v>59</v>
+      <c r="G55" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="H55" s="17"/>
     </row>
@@ -3839,29 +3834,29 @@
         <v>30</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>32</v>
@@ -3874,7 +3869,7 @@
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H57" s="17"/>
     </row>
@@ -3883,52 +3878,48 @@
         <v>27</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>284</v>
+        <v>34</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>82</v>
       </c>
       <c r="F58" s="10"/>
       <c r="G58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="17"/>
+    </row>
+    <row r="59" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" s="10"/>
+      <c r="G59" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="H58" s="17"/>
+      <c r="H59" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
+  <mergeCells count="38">
     <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="G5:H5"/>
@@ -3939,6 +3930,33 @@
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3967,40 +3985,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -4008,13 +4026,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4049,14 +4067,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4069,60 +4087,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4380,13 +4398,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4604,13 +4622,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4636,13 +4654,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
       <c r="G38" s="9" t="s">
         <v>152</v>
       </c>
@@ -4812,27 +4830,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -4845,6 +4842,27 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4873,50 +4891,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4951,14 +4969,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4971,60 +4989,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -5036,13 +5054,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="42"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -5052,13 +5070,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -5338,13 +5356,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -11721,13 +11739,13 @@
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="18" t="s">
         <v>6</v>
       </c>
@@ -15915,13 +15933,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="41" t="s">
+      <c r="B49" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
       <c r="G49" s="18" t="s">
         <v>6</v>
       </c>
@@ -20107,29 +20125,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B17:F17"/>
@@ -20146,6 +20141,29 @@
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20174,50 +20192,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20252,14 +20270,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20272,60 +20290,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20353,13 +20371,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -20434,10 +20452,10 @@
       <c r="B17" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="9" t="s">
         <v>134</v>
       </c>
@@ -20639,13 +20657,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -20895,13 +20913,13 @@
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
@@ -21165,28 +21183,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B45:F45"/>
@@ -21200,6 +21196,28 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21228,50 +21246,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21306,14 +21324,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21326,60 +21344,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21456,10 +21474,10 @@
       <c r="B15" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="9" t="s">
         <v>274</v>
       </c>
@@ -21661,13 +21679,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -21873,13 +21891,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -22083,28 +22101,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
@@ -22115,6 +22111,28 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22143,50 +22161,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22221,14 +22239,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22241,60 +22259,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22368,13 +22386,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="9" t="s">
         <v>158</v>
       </c>
@@ -22556,13 +22574,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -22724,13 +22742,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -22786,13 +22804,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="53"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="42"/>
       <c r="G37" s="9" t="s">
         <v>119</v>
       </c>
@@ -22890,28 +22908,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
@@ -22922,6 +22918,28 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22950,50 +22968,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -23028,14 +23046,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -23048,60 +23066,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -23129,13 +23147,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -23399,13 +23417,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -23567,13 +23585,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -23733,28 +23751,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
@@ -23766,6 +23762,28 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63406A78-EC01-41A9-8E8E-D7B719E90F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2B82D6-4D6E-4DAF-BCD7-9BA6AE562E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29595" yWindow="3720" windowWidth="24480" windowHeight="25620" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22050" yWindow="3465" windowWidth="32130" windowHeight="24720" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="318">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -898,9 +898,6 @@
     <t>{v} = 376</t>
   </si>
   <si>
-    <t>{v} &gt; 2</t>
-  </si>
-  <si>
     <t>{v} = 488</t>
   </si>
   <si>
@@ -917,9 +914,6 @@
   </si>
   <si>
     <t>{v} = 350</t>
-  </si>
-  <si>
-    <t>{v} &gt;  {1}</t>
   </si>
   <si>
     <t>{v} = 650</t>
@@ -1960,28 +1954,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2003,6 +1979,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2409,7 +2403,7 @@
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
@@ -2420,33 +2414,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B2" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="E2" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="F2" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="G2" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="H2" s="27" t="s">
         <v>246</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
@@ -2458,33 +2452,33 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
@@ -2496,85 +2490,85 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="E6" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="G6" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="H6" s="34" t="s">
         <v>227</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="E7" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="G7" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="H7" s="34" t="s">
         <v>233</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B8" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="E8" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="G8" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="H8" s="34" t="s">
         <v>239</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
@@ -2586,7 +2580,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
@@ -2598,7 +2592,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
@@ -2610,7 +2604,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="33"/>
@@ -2622,7 +2616,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33"/>
@@ -2634,7 +2628,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
@@ -2646,7 +2640,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33"/>
@@ -2658,7 +2652,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="33"/>
@@ -2670,7 +2664,7 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
@@ -2682,7 +2676,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="33"/>
@@ -2694,7 +2688,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33"/>
@@ -2706,7 +2700,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="33"/>
@@ -2718,7 +2712,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29"/>
@@ -2730,7 +2724,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="33"/>
@@ -2742,7 +2736,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="33"/>
@@ -2754,7 +2748,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="33"/>
@@ -2766,7 +2760,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="33"/>
@@ -2778,7 +2772,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33"/>
@@ -2814,42 +2808,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2859,13 +2853,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2900,74 +2894,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2996,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -3012,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -3020,7 +3014,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3060,10 +3054,10 @@
       <c r="B16" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
         <v>114</v>
       </c>
@@ -3120,7 +3114,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -3184,14 +3178,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3200,7 +3194,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -3213,7 +3207,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3222,7 +3216,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -3235,7 +3229,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3265,13 +3259,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -3284,7 +3278,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3330,7 +3324,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -3338,7 +3332,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -3346,7 +3340,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -3406,7 +3400,7 @@
         <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -3477,7 +3471,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -3486,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
@@ -3499,7 +3493,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3508,7 +3502,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -3521,7 +3515,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -3551,13 +3545,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
@@ -3570,7 +3564,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -3586,10 +3580,10 @@
       <c r="B43" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="42"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
       <c r="G43" s="9" t="s">
         <v>145</v>
       </c>
@@ -3646,7 +3640,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -3682,13 +3676,13 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>66</v>
@@ -3703,13 +3697,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="1" t="s">
         <v>6</v>
       </c>
@@ -3724,10 +3718,10 @@
       <c r="B50" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="42"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
       <c r="G50" s="9" t="s">
         <v>147</v>
       </c>
@@ -3738,7 +3732,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -3751,13 +3745,13 @@
       <c r="A52" s="8">
         <v>4</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="9"/>
       <c r="H52" s="17"/>
     </row>
@@ -3798,7 +3792,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -3818,7 +3812,7 @@
         <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>71</v>
@@ -3840,7 +3834,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>83</v>
@@ -3862,7 +3856,7 @@
         <v>32</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>82</v>
@@ -3884,7 +3878,7 @@
         <v>32</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>82</v>
@@ -3900,47 +3894,25 @@
         <v>27</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>82</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H59" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B50:F50"/>
@@ -3957,6 +3929,28 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3985,40 +3979,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -4026,13 +4020,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4067,14 +4061,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4087,60 +4081,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4169,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -4275,7 +4269,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -4295,7 +4289,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -4317,7 +4311,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>85</v>
@@ -4339,7 +4333,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>71</v>
@@ -4355,20 +4349,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4377,20 +4371,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -4398,13 +4392,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4417,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -4431,7 +4425,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -4461,7 +4455,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -4521,7 +4515,7 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -4622,13 +4616,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4641,7 +4635,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -4654,13 +4648,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
         <v>152</v>
       </c>
@@ -4671,7 +4665,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -4731,7 +4725,7 @@
         <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -4830,6 +4824,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -4842,27 +4857,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4891,50 +4885,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4969,14 +4963,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4989,60 +4983,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -5054,13 +5048,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -5070,13 +5064,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -5087,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -5103,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -5111,7 +5105,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5211,7 +5205,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -5275,14 +5269,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5291,7 +5285,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -5304,7 +5298,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -5313,7 +5307,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -5326,7 +5320,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -5356,13 +5350,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -6391,7 +6385,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -8469,7 +8463,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9501,7 +9495,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -9509,7 +9503,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -11594,7 +11588,7 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -11636,7 +11630,7 @@
         <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>70</v>
@@ -11658,14 +11652,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -11674,20 +11668,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>71</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -11696,20 +11690,20 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>120</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -11724,7 +11718,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>75</v>
@@ -11739,13 +11733,13 @@
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
       <c r="G42" s="18" t="s">
         <v>6</v>
       </c>
@@ -12774,7 +12768,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -15898,7 +15892,7 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -15933,13 +15927,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="18" t="s">
         <v>6</v>
       </c>
@@ -18000,7 +17994,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -20092,7 +20086,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -20112,7 +20106,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>82</v>
@@ -20125,6 +20119,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B17:F17"/>
@@ -20141,29 +20158,6 @@
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20192,50 +20186,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20270,14 +20264,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20290,60 +20284,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20371,13 +20365,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -20404,7 +20398,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -20412,7 +20406,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20452,10 +20446,10 @@
       <c r="B17" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="53"/>
       <c r="G17" s="9" t="s">
         <v>134</v>
       </c>
@@ -20512,7 +20506,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -20583,7 +20577,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -20592,7 +20586,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -20605,7 +20599,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -20614,7 +20608,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -20627,7 +20621,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -20657,13 +20651,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -20676,7 +20670,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -20706,7 +20700,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -20768,7 +20762,7 @@
         <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -20913,13 +20907,13 @@
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
@@ -20932,7 +20926,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -20980,7 +20974,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -21040,7 +21034,7 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -21183,6 +21177,28 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B45:F45"/>
@@ -21196,28 +21212,6 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21246,50 +21240,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="A2" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21324,14 +21318,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21344,60 +21338,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21426,14 +21420,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -21442,7 +21436,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -21450,7 +21444,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -21472,14 +21466,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
+        <v>273</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -21598,14 +21592,14 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -21614,7 +21608,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -21627,7 +21621,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -21636,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -21649,7 +21643,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -21679,13 +21673,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -21698,7 +21692,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -21728,7 +21722,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -21891,13 +21885,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -21910,7 +21904,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -21940,7 +21934,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -22101,6 +22095,28 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
@@ -22111,28 +22127,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22161,50 +22155,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22239,14 +22233,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22259,60 +22253,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22341,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -22357,7 +22351,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -22365,7 +22359,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22386,13 +22380,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
         <v>158</v>
       </c>
@@ -22500,7 +22494,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -22509,7 +22503,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
@@ -22522,7 +22516,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -22531,7 +22525,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -22544,7 +22538,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -22574,13 +22568,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -22593,7 +22587,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -22607,7 +22601,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -22623,7 +22617,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -22742,13 +22736,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -22761,7 +22755,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
@@ -22791,7 +22785,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -22804,13 +22798,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="42"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
       <c r="G37" s="9" t="s">
         <v>119</v>
       </c>
@@ -22908,6 +22902,28 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
@@ -22918,28 +22934,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22968,50 +22962,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -23046,14 +23040,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -23066,60 +23060,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -23147,13 +23141,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -23164,7 +23158,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -23180,7 +23174,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -23188,7 +23182,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -23210,14 +23204,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -23336,14 +23330,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -23352,7 +23346,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -23365,7 +23359,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -23374,7 +23368,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -23387,7 +23381,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -23417,13 +23411,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -23436,7 +23430,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -23466,7 +23460,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -23480,7 +23474,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -23585,13 +23579,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -23604,7 +23598,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -23634,7 +23628,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -23751,6 +23745,28 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
@@ -23762,28 +23778,6 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612397C5-DB40-4631-90C7-2C52B655E844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD80A8A-3525-4575-AD00-3F2A7ABEB891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25785" yWindow="2565" windowWidth="27825" windowHeight="24720" tabRatio="500" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25635" yWindow="5070" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -843,15 +843,6 @@
     <t>Patient7</t>
   </si>
   <si>
-    <t>{ "PatientAction": {
-      "AirwayObstruction": {
-        "Severity": {
-          "Scalar0To1": {
-            "Value": 0.4
-          } } } }
-  }</t>
-  </si>
-  <si>
     <t>Mild ARDS with Right Mainstem Intubation</t>
   </si>
   <si>
@@ -1682,6 +1673,15 @@
   }}
 }</t>
   </si>
+  <si>
+    <t>{ "PatientAction": {
+      "AirwayObstruction": {
+        "Severity": {
+          "Scalar0To1": {
+            "Value": 0.4 } } ,
+         "HasSecretions": true } }
+  }</t>
+  </si>
 </sst>
 </file>
 
@@ -2199,28 +2199,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2242,6 +2224,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2648,7 +2648,7 @@
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
@@ -3053,50 +3053,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="A2" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3131,14 +3131,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -3151,60 +3151,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3233,14 +3233,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -3257,7 +3257,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3295,14 +3295,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
+        <v>344</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -3421,14 +3421,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3437,7 +3437,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3459,7 +3459,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3502,13 +3502,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3551,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -3572,7 +3572,7 @@
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -3714,13 +3714,13 @@
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
       <c r="G37" s="1" t="s">
         <v>6</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -3763,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="39"/>
@@ -3924,21 +3924,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B10:F10"/>
@@ -3952,11 +3942,21 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3985,50 +3985,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4063,14 +4063,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4083,60 +4083,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4165,14 +4165,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4181,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -4189,7 +4189,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4210,15 +4210,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="43" t="s">
-        <v>316</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
+      <c r="B15" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -4333,7 +4333,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -4355,7 +4355,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4398,13 +4398,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -4431,7 +4431,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>219</v>
+        <v>345</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -4447,7 +4447,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -4468,7 +4468,7 @@
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -4566,13 +4566,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
@@ -4615,7 +4615,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -4628,15 +4628,15 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="42"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
       <c r="G37" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -4732,6 +4732,28 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
@@ -4742,28 +4764,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4792,50 +4792,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4870,14 +4870,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4890,60 +4890,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4972,14 +4972,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4988,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -4996,7 +4996,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5033,15 +5033,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="43" t="s">
-        <v>341</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
+      <c r="B16" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -5156,7 +5156,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -5178,7 +5178,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5221,13 +5221,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5254,7 +5254,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>219</v>
+        <v>345</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -5270,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -5291,7 +5291,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -5389,13 +5389,13 @@
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
@@ -5438,7 +5438,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -5451,15 +5451,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -5555,21 +5555,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B10:F10"/>
@@ -5583,11 +5573,21 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5616,50 +5616,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -5694,14 +5694,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -5714,60 +5714,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5795,13 +5795,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>114</v>
@@ -5812,14 +5812,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -5828,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -5836,7 +5836,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5858,14 +5858,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5984,14 +5984,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -6000,7 +6000,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -6022,7 +6022,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -6065,13 +6065,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -6114,7 +6114,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -6128,14 +6128,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -6233,13 +6233,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -6282,7 +6282,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -6303,7 +6303,7 @@
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -6399,6 +6399,28 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
@@ -6410,28 +6432,6 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6460,50 +6460,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -6538,14 +6538,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -6558,60 +6558,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6639,13 +6639,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>114</v>
@@ -6656,14 +6656,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -6672,7 +6672,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -6680,20 +6680,20 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="19"/>
       <c r="H15" s="17" t="s">
         <v>24</v>
@@ -6718,14 +6718,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -6844,14 +6844,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -6860,7 +6860,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -6882,7 +6882,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -6925,13 +6925,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -6974,7 +6974,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -6988,14 +6988,14 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -7093,13 +7093,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -7142,7 +7142,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -7163,7 +7163,7 @@
       <c r="E40" s="39"/>
       <c r="F40" s="39"/>
       <c r="G40" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -7259,28 +7259,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -7293,6 +7271,28 @@
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -7321,42 +7321,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -7366,13 +7366,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -7407,74 +7407,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -7503,14 +7503,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -7519,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -7527,7 +7527,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7565,14 +7565,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
+        <v>307</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -7691,14 +7691,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -7729,7 +7729,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -7772,13 +7772,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -7812,7 +7812,7 @@
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -7837,7 +7837,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -7845,7 +7845,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7853,7 +7853,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -8015,7 +8015,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -8058,13 +8058,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -8091,12 +8091,12 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="42"/>
+        <v>309</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
       <c r="G43" s="9" t="s">
         <v>127</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
@@ -8210,13 +8210,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="1" t="s">
         <v>6</v>
       </c>
@@ -8229,12 +8229,12 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="42"/>
+        <v>308</v>
+      </c>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
       <c r="G50" s="9" t="s">
         <v>128</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -8258,13 +8258,13 @@
       <c r="A52" s="8">
         <v>4</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="9"/>
       <c r="H52" s="17"/>
     </row>
@@ -8407,7 +8407,7 @@
         <v>27</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
@@ -8420,34 +8420,12 @@
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H59" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B50:F50"/>
@@ -8464,6 +8442,28 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -8492,42 +8492,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -8537,13 +8537,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -8578,74 +8578,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -8674,14 +8674,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -8690,7 +8690,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -8698,7 +8698,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8736,14 +8736,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
+        <v>307</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -8862,14 +8862,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -8878,7 +8878,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -8900,7 +8900,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -8943,13 +8943,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -8975,15 +8975,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="53"/>
       <c r="G28" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -9008,7 +9008,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -9016,7 +9016,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -9024,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -9164,7 +9164,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -9229,13 +9229,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -9262,12 +9262,12 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="42"/>
+        <v>309</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53"/>
       <c r="G43" s="9" t="s">
         <v>127</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
@@ -9381,13 +9381,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="1" t="s">
         <v>6</v>
       </c>
@@ -9400,12 +9400,12 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="42"/>
+        <v>308</v>
+      </c>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
       <c r="G50" s="9" t="s">
         <v>128</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -9429,13 +9429,13 @@
       <c r="A52" s="8">
         <v>4</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="9"/>
       <c r="H52" s="17"/>
     </row>
@@ -9578,7 +9578,7 @@
         <v>27</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
@@ -9591,18 +9591,29 @@
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H59" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -9618,23 +9629,12 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -9663,40 +9663,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -9704,13 +9704,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -9745,14 +9745,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -9765,60 +9765,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -9847,14 +9847,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -9891,14 +9891,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10033,7 +10033,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -10076,13 +10076,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -10109,7 +10109,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -10139,7 +10139,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -10300,13 +10300,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -10332,13 +10332,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
         <v>130</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -10508,6 +10508,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -10520,27 +10541,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10569,40 +10569,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -10610,13 +10610,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -10651,14 +10651,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -10671,60 +10671,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10753,14 +10753,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -10797,14 +10797,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10939,7 +10939,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -10961,7 +10961,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -10982,13 +10982,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -11015,7 +11015,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -11045,7 +11045,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -11206,13 +11206,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -11238,13 +11238,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
         <v>130</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -11414,12 +11414,18 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -11435,18 +11441,12 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -11475,50 +11475,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -11553,14 +11553,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -11573,60 +11573,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -11638,13 +11638,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -11654,13 +11654,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>114</v>
@@ -11671,14 +11671,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -11687,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -11695,7 +11695,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11733,14 +11733,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -11859,14 +11859,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -11875,7 +11875,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -11897,7 +11897,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -11940,13 +11940,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -12996,7 +12996,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="13"/>
@@ -15053,7 +15053,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -16085,7 +16085,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -16093,7 +16093,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -18242,14 +18242,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -18258,7 +18258,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -18271,7 +18271,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -18280,7 +18280,7 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -18293,7 +18293,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -18323,13 +18323,13 @@
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
       <c r="G42" s="18" t="s">
         <v>6</v>
       </c>
@@ -19358,7 +19358,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -19372,7 +19372,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -22517,13 +22517,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="18" t="s">
         <v>6</v>
       </c>
@@ -23552,7 +23552,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -24584,7 +24584,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -26709,6 +26709,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B17:F17"/>
@@ -26725,29 +26748,6 @@
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -26776,50 +26776,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -26854,14 +26854,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -26874,60 +26874,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -26939,13 +26939,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -26955,13 +26955,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>114</v>
@@ -26972,14 +26972,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -26988,7 +26988,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -26996,7 +26996,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -27034,14 +27034,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -27160,14 +27160,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -27176,7 +27176,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -27189,7 +27189,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -27198,7 +27198,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -27211,7 +27211,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -27241,13 +27241,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -28276,7 +28276,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -28297,7 +28297,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="13"/>
@@ -30354,7 +30354,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -31386,7 +31386,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -31394,7 +31394,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -33543,14 +33543,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -33559,7 +33559,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -33572,7 +33572,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -33581,7 +33581,7 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -33594,7 +33594,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -33624,13 +33624,13 @@
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
       <c r="G42" s="18" t="s">
         <v>6</v>
       </c>
@@ -34659,7 +34659,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -34673,7 +34673,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -37818,13 +37818,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="18" t="s">
         <v>6</v>
       </c>
@@ -38853,7 +38853,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -39885,7 +39885,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -42010,21 +42010,18 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
@@ -42037,18 +42034,21 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -42077,50 +42077,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -42155,14 +42155,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -42175,60 +42175,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -42256,13 +42256,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>114</v>
@@ -42280,7 +42280,7 @@
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -42289,7 +42289,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -42297,7 +42297,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -42335,14 +42335,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
+        <v>313</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="53"/>
       <c r="G17" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -42468,7 +42468,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -42477,7 +42477,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -42490,7 +42490,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -42499,7 +42499,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -42512,7 +42512,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -42542,13 +42542,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -42561,7 +42561,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -42591,7 +42591,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -42612,7 +42612,7 @@
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -42798,13 +42798,13 @@
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
@@ -42817,7 +42817,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -42854,7 +42854,7 @@
       <c r="E43" s="39"/>
       <c r="F43" s="39"/>
       <c r="G43" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>94</v>
@@ -42865,7 +42865,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -43068,6 +43068,28 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B45:F45"/>
@@ -43081,28 +43103,6 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -43131,50 +43131,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="44"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="A2" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F2" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -43209,14 +43209,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -43229,60 +43229,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -43311,14 +43311,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -43327,7 +43327,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -43335,7 +43335,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -43357,14 +43357,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
+        <v>314</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -43483,14 +43483,14 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -43499,7 +43499,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -43521,7 +43521,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -43534,7 +43534,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -43564,13 +43564,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -43583,7 +43583,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -43613,7 +43613,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -43634,7 +43634,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -43776,13 +43776,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -43795,7 +43795,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -43825,7 +43825,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -43986,6 +43986,28 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
@@ -43996,28 +44018,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD80A8A-3525-4575-AD00-3F2A7ABEB891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E098AA5-AD56-4B2E-9346-5F2FAD64565E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25635" yWindow="5070" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22050" yWindow="4575" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -1272,28 +1272,6 @@
  - High RR = 34 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
   <si>
-    <t>Ventilator settings are:
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.650    | NA          | 70          | NA  | 0.6    | 14       | 5            | 0.4 |
-Ventilator alarm settings are:
- - High PIP = 40 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 6.8 L/min (~25% below the initial value)
- - Low VT = 490 mL (~25% below the initial value)
- - High RR = 24 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |
-Ventilator alarm settings are:
- - High PIP = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 8.9 L/min (~25% below the initial value)
- - Low VT = 330 mL (~25% below the initial value)
- - High RR = 37 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
-  </si>
-  <si>
     <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
@@ -1364,48 +1342,6 @@
   "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 70, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 650, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -1579,13 +1515,55 @@
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario7_NoSpontaneous-InterventionApplied.json"} }</t>
   </si>
   <si>
+    <t>{ "PatientAction": {
+      "AirwayObstruction": {
+        "Severity": {
+          "Scalar0To1": {
+            "Value": 0.4 } } ,
+         "HasSecretions": true } }
+  }</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 26      | 5            | 0.4 |
+Ventilator alarm settings are:
+ - High PIP = 31 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 7.3 L/min (~25% below the initial value)
+ - Low VT = 290 mL (~25% below the initial value)
+ - High RR = 36 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 31, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.3, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 26, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
     <t>Ventilator settings are:
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
 | PC-CMV | NA     | 25          | NA           | NA  | 0.6    | 10       | 34            | 0.60 |
 Ventilator alarm settings are:
- - High PIP = 30 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 11 L/min (~25% below the initial value)
+ - High PIP = 35 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 9.6 L/min (~25% below the initial value)
  - Low VT = 310 mL (~25% below the initial value)
  - High RR = 40 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
@@ -1593,9 +1571,9 @@
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
     "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 30, "Unit": "cmH2O" } },
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 35, "Unit": "cmH2O" } },
     "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 11, "Unit": "L/min" } },
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 9.6, "Unit": "L/min" } },
     "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 310, "Unit": "mL" } },
     "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 40, "Unit": "1/min" } } } } },
   "Mode": "AssistedControl", 
@@ -1615,8 +1593,8 @@
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
 | PC-CMV | NA     | 18          | NA           | NA  | 0.8    | 23       | 5            | 0.40 |
 Ventilator alarm settings are:
- - High PIP = 24 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 8.4 L/min (~25% below the initial value)
+ - High PIP = 28 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 7.9 L/min (~25% below the initial value)
  - Low VT = 365 mL (~25% below the initial value)
  - High RR = 33 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
@@ -1624,9 +1602,9 @@
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
     "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 24, "Unit": "cmH2O" } },
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 28, "Unit": "cmH2O" } },
     "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.4, "Unit": "L/min" } },
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.9, "Unit": "L/min" } },
     "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 365, "Unit": "mL" } },
     "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 33, "Unit": "1/min" } } } } },
   "Mode": "AssistedControl", 
@@ -1641,46 +1619,68 @@
 }</t>
   </si>
   <si>
-    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
-&lt;br /&gt;
+    <t>Ventilator settings are:
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 26      | 5            | 0.4 |
+| VC-CMV | 0.650    | NA          | 70          | NA  | 0.6    | 14       | 5            | 0.4 |
 Ventilator alarm settings are:
- - High PIP = 26 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 7.5 L/min (~25% below the initial value)
- - Low VT = 290 mL (~25% below the initial value)
- - High RR = 36 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
+ - High PIP (no cycling) = 40 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 6.8 L/min (~25% below the initial value)
+ - Low VT = 490 mL (~25% below the initial value)
+ - High RR = 24 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
     "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 26, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.5, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "Off",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } } } } },
   "Mode": "AssistedControl", 
   "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "Flow": { "ScalarVolumePerTime": { "Value": 70, "Unit": "L/min" } },
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 26, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 650, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
   <si>
-    <t>{ "PatientAction": {
-      "AirwayObstruction": {
-        "Severity": {
-          "Scalar0To1": {
-            "Value": 0.4 } } ,
-         "HasSecretions": true } }
-  }</t>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "Off",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |
+Ventilator alarm settings are:
+ - High PIP (no cycling) = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 8.9 L/min (~25% below the initial value)
+ - Low VT = 330 mL (~25% below the initial value)
+ - High RR = 37 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
 </sst>
 </file>
@@ -3295,14 +3295,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3551,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -3733,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -3763,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="39"/>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
@@ -4431,7 +4431,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5034,14 +5034,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5240,7 +5240,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5254,7 +5254,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -5270,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -5408,7 +5408,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
@@ -5438,7 +5438,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -5858,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
@@ -6718,14 +6718,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -6944,7 +6944,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -6974,7 +6974,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -7112,7 +7112,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -7142,7 +7142,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -7565,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
@@ -8091,7 +8091,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
@@ -8229,7 +8229,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -8736,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
@@ -8962,7 +8962,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -9024,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9248,7 +9248,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -9262,7 +9262,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
@@ -9400,7 +9400,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -9416,7 +9416,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -9891,14 +9891,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10797,14 +10797,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -11001,7 +11001,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -11045,7 +11045,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -11255,7 +11255,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -11733,14 +11733,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -23552,7 +23552,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -27034,14 +27034,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -28276,7 +28276,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -34659,7 +34659,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -38853,7 +38853,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -39885,7 +39885,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -42335,14 +42335,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
       <c r="F17" s="53"/>
       <c r="G17" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -43357,7 +43357,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E098AA5-AD56-4B2E-9346-5F2FAD64565E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B50026D-68E1-47DA-B672-31CB0CAE0CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22050" yWindow="4575" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22050" yWindow="4575" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -1272,6 +1272,17 @@
  - High RR = 34 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
   <si>
+    <t>Ventilator settings are:
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |
+Ventilator alarm settings are:
+ - High PIP = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - Low MVe = 8.9 L/min (~25% below the initial value)
+ - Low VT = 330 mL (~25% below the initial value)
+ - High RR = 37 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
+  </si>
+  <si>
     <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
@@ -1342,6 +1353,27 @@
   "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -1649,38 +1681,6 @@
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "Off",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |
-Ventilator alarm settings are:
- - High PIP (no cycling) = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 8.9 L/min (~25% below the initial value)
- - Low VT = 330 mL (~25% below the initial value)
- - High RR = 37 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
 </sst>
 </file>
@@ -3295,14 +3295,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3551,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -3733,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -3763,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="39"/>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
@@ -4431,7 +4431,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5034,14 +5034,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5240,7 +5240,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5254,7 +5254,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -5270,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -5408,7 +5408,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
@@ -5438,7 +5438,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -5858,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
@@ -6718,14 +6718,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -6944,7 +6944,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -6974,7 +6974,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -7112,7 +7112,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -7142,7 +7142,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -7565,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
@@ -8091,7 +8091,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
@@ -8229,7 +8229,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -8736,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
@@ -8962,7 +8962,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -9024,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9248,7 +9248,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -9262,7 +9262,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
@@ -9400,7 +9400,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -9416,7 +9416,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -9891,14 +9891,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10797,14 +10797,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -11001,7 +11001,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -11045,7 +11045,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -11255,7 +11255,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -11733,14 +11733,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -23552,7 +23552,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -27034,14 +27034,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -28276,7 +28276,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -34659,7 +34659,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -38853,7 +38853,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -39885,7 +39885,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -42335,14 +42335,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
       <c r="F17" s="53"/>
       <c r="G17" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -43357,7 +43357,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B50026D-68E1-47DA-B672-31CB0CAE0CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFD8F6A-3D43-431C-BAC6-C3C6EEFC30F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22050" yWindow="4575" windowWidth="27810" windowHeight="20550" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27750" yWindow="4680" windowWidth="29595" windowHeight="26160" tabRatio="500" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="338">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -350,9 +350,6 @@
     <t>C for moderate COPD</t>
   </si>
   <si>
-    <t>PaO2/FiO2  for severe ARDS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Learning Objectives:
  - Recognize worsening ARDS (moderate)
  - Adjust vent settings for safety
@@ -399,9 +396,6 @@
   }</t>
   </si>
   <si>
-    <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
-  </si>
-  <si>
     <t>Needle decompression procedure performed.</t>
   </si>
   <si>
@@ -411,28 +405,7 @@
     <t xml:space="preserve">Patient is suctioned for large volume of thick secretions. </t>
   </si>
   <si>
-    <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation. After intubation he is on mechanical ventilation and remains sedated with a RASS of -2
-His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation. The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy. He is 5'8'' and weighs 235 lbs. Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
-  </si>
-  <si>
     <t>Patient suctioned and ET tube obstruction removed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection. Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 C, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min. After 12 hours he was intubated.After intubation he is on mechanical ventilation and remains sedated with a RASS of -2.
-The soldier is 6'3'' and weighs 215 lbs. Suctioning reveals thick, tenacious, brownish-yellow secretions. Therapeutic bronchoscopy is performed and 15-20 mL secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 28 year old sailor suffered a crush injury during the transfer of supplies from a fork lift. She suffered an open book pelvic fracture, ruptured bladder and splenic laceration. She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture. The spleen was removed and the bladder repaired. Blood loss was estimated at 2.5 L. The sailor is 5'5" and weighs 138 lbs. </t>
-  </si>
-  <si>
-    <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated. Both eardrums were ruptured and his GCS was 12. He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9" tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
-  </si>
-  <si>
-    <t>A 25 year-old active duty Marine was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7" tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
-  </si>
-  <si>
-    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies.
-Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
   </si>
   <si>
     <t>licker2021hypoxic</t>
@@ -480,15 +453,6 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">The patient is loaded in the aircraft for transport to level III care.  Twenty minutes into the transport SpO2 falls and PIP and Pplat are increased.  The patient remains sedated and is not triggering the ventilator.  </t>
-  </si>
-  <si>
-    <t>The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient becomes agitated and respiratory rate increases and SpO2 has fallen.</t>
-  </si>
-  <si>
-    <t>The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient is heavily sedated. Immediately after take-off multiple ventilator alarms sound, tidal volume falls, respiratory rate increases, and SpO2 has fallen. The patient is growing agitated. Attempting to manually ventilate the patient meets extreme resistance and no air movement.</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteStress": { "Severity": { "Scalar0To1": { "Value": 0.6 } } } } }</t>
   </si>
   <si>
@@ -534,19 +498,6 @@
 | VC-CMV | 0.490    | NA          | 50         | NA  | 0.6    | 24      | 10            | 0.5 |</t>
   </si>
   <si>
-    <t>Ventialtor settings are changed. PEEP and FiO2 increased.
-Learning Objectives:
- - Evaluate effects of changes
-Recommended Actions:
- - None
-Ventilator settings are updated to:
- - FIO2 = 0.50-&gt;1.00
- - PEEP = 8-&gt;12 cmH2O
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.350   | NA          | 42           | NA  | 0.52  | 27       | 12            | 1.00 |</t>
-  </si>
-  <si>
     <t>Patient suctioned and albuterol administered.
 Learning Objectives:
  - Recognize that treatment reduced airway resistance (lower difference PIP - Pplat)
@@ -557,19 +508,6 @@
  - Goal shifts to Comfort (imprive synchrony) due to cycle dyssychrony
  - Decrease FiO2
  - Consider switching mode to PC-CSV (ie Pressure Support)</t>
-  </si>
-  <si>
-    <t>Ventialtor settings are changed. Decrease VT to prevent premature cycling by high-pressure alarm.
-Learning Objectives:
- - Evaluate effects of changes
-Recommended Actions:
- - Increase PEEP to improve oxygenation
- - Increase FiO2 to get SpO2 88-95%
-Ventilator settings are updated to:
- - TV = 450 mL -&gt; 350 mL
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.350  | NA          | 42           | NA  | 0.52  | 27       | 8            | 0.21 |</t>
   </si>
   <si>
     <t>{ "PatientAction": {
@@ -636,15 +574,6 @@
   </si>
   <si>
     <t>{v} = 450</t>
-  </si>
-  <si>
-    <t>{v} = 0.65</t>
-  </si>
-  <si>
-    <t>{v} &lt; 100</t>
-  </si>
-  <si>
-    <t>{v} &gt; 0.4</t>
   </si>
   <si>
     <t>{v} = 350</t>
@@ -867,9 +796,6 @@
     <t>QS/QT for moderate COPD (determined from blood gas values)</t>
   </si>
   <si>
-    <t>QS/QT for severe ARDS (determined from blood gas values)</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
   {
     "Severity": [ 
@@ -889,25 +815,7 @@
     }</t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 1, "Unit": "min" }}}}</t>
-  </si>
-  <si>
     <t>{v} = 50</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.9 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.9 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{v} = 30</t>
-  </si>
-  <si>
-    <t>C requested by SME for severe ARDS</t>
   </si>
   <si>
     <t>C requested by SME for mild ARDS</t>
@@ -952,16 +860,6 @@
     <t>{ "PatientAction": {
       "RespiratoryMechanicsModification": {
         "Modifiers": {
-          "LeftComplianceMultiplier": { "ScalarUnsigned": { "Value": 0.9 }},
-          "RightComplianceMultiplier": { "ScalarUnsigned": { "Value": 0.9 }}
-         },
-         "Incremental": true
-}}}</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": {
-      "RespiratoryMechanicsModification": {
-        "Modifiers": {
           "LeftComplianceMultiplier": { "ScalarUnsigned": { "Value": 1.3 }},
           "RightComplianceMultiplier": { "ScalarUnsigned": { "Value": 1.3 }}
          },
@@ -998,9 +896,6 @@
   </si>
   <si>
     <t>VD/VT for moderate COPD</t>
-  </si>
-  <si>
-    <t>VD/VT for severe ARDS</t>
   </si>
   <si>
     <t>ClinicalShuntFraction</t>
@@ -1118,9 +1013,6 @@
  - None</t>
   </si>
   <si>
-    <t>The patient is loaded in the aircraft for transport to level III care. Twenty minutes into the transport, SpO2 falls and both PIP and Pplat are increased. The patient is triggering the ventilator.</t>
-  </si>
-  <si>
     <t>Learning Objectives:
  - Assess baseline status
  - Recognize presence of autoPEEP (from flow waveform)
@@ -1133,9 +1025,6 @@
  - Evaluate ventilatory status
 Recommended Actions:
  - None</t>
-  </si>
-  <si>
-    <t>The patient is loaded in the aircraft for transport to SAMMC. Halfway through the flight the ventilator starts alarming high inspiratory pressure. The SpO2 falls while PIP and Pplat increase.  The patient is now triggering the ventilator at a much higher rate.</t>
   </si>
   <si>
     <t>Learning Objectives:
@@ -1206,27 +1095,6 @@
  - None</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 38, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 3.5, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 140, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 34, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
@@ -1270,17 +1138,6 @@
  - Low MVe = 10.2 L/min (~25% below the initial value)
  - Low VT = 430 mL (~25% below the initial value)
  - High RR = 34 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |
-Ventilator alarm settings are:
- - High PIP = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
- - Low MVe = 8.9 L/min (~25% below the initial value)
- - Low VT = 330 mL (~25% below the initial value)
- - High RR = 37 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
   <si>
     <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
@@ -1353,48 +1210,6 @@
   "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.9, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 37, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 1.0 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 12, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -1651,22 +1466,56 @@
 }</t>
   </si>
   <si>
+    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 3, "Unit": "min" }}}}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are changed. PEEP and FiO2 increased.
+Learning Objectives:
+ - Evaluate effects of changes
+Recommended Actions:
+ - None
+Ventilator settings are updated to:
+ - FIO2 = 0.50 -&gt; 1.00
+ - PEEP = 8 -&gt; 12 cmH2O</t>
+  </si>
+  <si>
     <t>Ventilator settings are:
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.650    | NA          | 70          | NA  | 0.6    | 14       | 5            | 0.4 |
+| VC-CMV | 0.450  | NA          | 35           | NA  | 0.8  | 20       | 8            | 0.5 |
 Ventilator alarm settings are:
- - High PIP (no cycling) = 40 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
+ - High PIP = 37 cmH2O (~10 cmH2O above the initial value or a max of 40 cmH2O)
  - Low MVe = 6.8 L/min (~25% below the initial value)
- - Low VT = 490 mL (~25% below the initial value)
- - High RR = 24 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
+ - Low VT = 330 mL (~25% below the initial value)
+ - High RR = 30 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
     "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "Off",
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 30, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 35, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 50, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
     "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
     "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
     "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } } } } },
@@ -1679,6 +1528,122 @@
   "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 650, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.650    | NA          | 70          | NA  | 0.6    | 14       | 5            | 0.4 |
+Ventilator alarm settings are:
+ - High PIP = 50 cmH2O (~10 cmH2O above the initial value or a max of 50 cmH2O)
+ - Low MVe = 6.8 L/min (~25% below the initial value)
+ - Low VT = 490 mL (~25% below the initial value)
+ - High RR = 24 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": {
+      "RespiratoryMechanicsModification": {
+        "Modifiers": {
+          "LeftComplianceMultiplier": { "ScalarUnsigned": { "Value": 1.1 }},
+          "RightComplianceMultiplier": { "ScalarUnsigned": { "Value": 1.1 }}
+         },
+         "Incremental": true
+}}}</t>
+  </si>
+  <si>
+    <t>VT for PIP alarm cycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 22 year-old patient was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
+  </si>
+  <si>
+    <t>A 62 year-old patient developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies.
+Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
+  </si>
+  <si>
+    <t>A 25 year-old patient was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7" tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
+  </si>
+  <si>
+    <t>The patient is loaded in the aircraft for transport to the medical center. Halfway through the flight the ventilator starts alarming high inspiratory pressure. The SpO2 falls while PIP and Pplat increase.  The patient is now triggering the ventilator at a much higher rate.</t>
+  </si>
+  <si>
+    <t>A 25 year-old patient was injured following an explosive detonation. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated. Both eardrums were ruptured and his GCS was 12. He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9" tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The patient is loaded in the aircraft for transport to trauma center care.  Twenty minutes into the transport SpO2 falls and PIP and Pplat are increased.  The patient remains sedated and is not triggering the ventilator.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 23 year old patient suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection. Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 C, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min. After 12 hours he was intubated.After intubation he is on mechanical ventilation and remains sedated with a RASS of -2.
+The patient is 6'3'' and weighs 215 lbs. Suctioning reveals thick, tenacious, brownish-yellow secretions. Therapeutic bronchoscopy is performed and 15-20 mL secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for transport to definitive care in the morning. </t>
+  </si>
+  <si>
+    <t>The patient is loaded onto the aircraft for transfer to trauma center care. During transport the patient is heavily sedated. Immediately after take-off multiple ventilator alarms sound, tidal volume falls, respiratory rate increases, and SpO2 has fallen. The patient is growing agitated. Attempting to manually ventilate the patient meets extreme resistance and no air movement.</t>
+  </si>
+  <si>
+    <t>A 54-year-old, patient was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation. After intubation he is on mechanical ventilation and remains sedated with a RASS of -2
+His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation. The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy. He is 5'8'' and weighs 235 lbs. Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for transport to definitive care that night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 28 year old patient suffered a crush injury during the transfer of supplies from a fork lift. She suffered an open book pelvic fracture, ruptured bladder and splenic laceration. She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture. The spleen was removed and the bladder repaired. Blood loss was estimated at 2.5 L. The patient is 5'5" and weighs 138 lbs. </t>
+  </si>
+  <si>
+    <t>The patient is loaded onto the aircraft for transfer to trauma center care. During transport the patient becomes agitated and respiratory rate increases and SpO2 has fallen.</t>
+  </si>
+  <si>
+    <t>The patient is loaded in the aircraft for transport to trauma center care. Twenty minutes into the transport, SpO2 falls and both PIP and Pplat are increased. The patient is triggering the ventilator.</t>
+  </si>
+  <si>
+    <t>Ventilator settings are changed. Decrease VT to prevent premature cycling by high-pressure alarm.
+Learning Objectives:
+ - Evaluate effects of changes
+Recommended Actions:
+ - Increase PEEP to improve oxygenation
+ - Increase FiO2 to get SpO2 88-95%
+Ventilator settings are updated to:
+ - TV = 450 mL -&gt; 350 mL
+ - RR = 20 bpm -&gt; 35 bpm</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 30, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 28, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 35, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
+    "SupplementalSettings": { "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 30, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 28, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 1.0 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 12, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 35, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -2648,7 +2613,7 @@
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="36" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
@@ -2659,33 +2624,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
@@ -2697,33 +2662,33 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
@@ -2735,85 +2700,85 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
@@ -2825,7 +2790,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
@@ -2837,7 +2802,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
@@ -2849,7 +2814,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="33"/>
@@ -2861,7 +2826,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33"/>
@@ -2873,7 +2838,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
@@ -2885,7 +2850,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33"/>
@@ -2897,7 +2862,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="33"/>
@@ -2909,7 +2874,7 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
@@ -2921,7 +2886,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="33"/>
@@ -2933,7 +2898,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33"/>
@@ -2945,7 +2910,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="33"/>
@@ -2957,7 +2922,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29"/>
@@ -2969,7 +2934,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="33"/>
@@ -2981,7 +2946,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="33"/>
@@ -2993,7 +2958,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="33"/>
@@ -3005,7 +2970,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="33"/>
@@ -3017,7 +2982,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33"/>
@@ -3072,16 +3037,16 @@
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -3136,7 +3101,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -3233,14 +3198,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -3249,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -3257,7 +3222,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3295,14 +3260,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -3331,13 +3296,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -3357,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -3377,7 +3342,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -3399,7 +3364,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -3421,14 +3386,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3437,20 +3402,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3459,20 +3424,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3521,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3542,7 +3507,7 @@
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -3551,7 +3516,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -3565,14 +3530,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="9" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -3587,13 +3552,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -3613,7 +3578,7 @@
         <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -3633,7 +3598,7 @@
         <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
@@ -3655,7 +3620,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>81</v>
@@ -3677,7 +3642,7 @@
         <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>29</v>
@@ -3699,7 +3664,7 @@
         <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>29</v>
@@ -3733,7 +3698,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -3754,7 +3719,7 @@
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="9" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -3763,7 +3728,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="39"/>
@@ -3784,7 +3749,7 @@
       <c r="E41" s="39"/>
       <c r="F41" s="39"/>
       <c r="G41" s="9" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -3799,13 +3764,13 @@
         <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>6</v>
@@ -3825,7 +3790,7 @@
         <v>51</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -3845,7 +3810,7 @@
         <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>29</v>
@@ -3867,7 +3832,7 @@
         <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>81</v>
@@ -3889,7 +3854,7 @@
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>29</v>
@@ -3911,7 +3876,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>29</v>
@@ -4010,10 +3975,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -4068,7 +4033,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -4165,14 +4130,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4181,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -4189,7 +4154,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4211,14 +4176,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
       <c r="E15" s="52"/>
       <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -4247,13 +4212,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4273,7 +4238,7 @@
         <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>69</v>
@@ -4295,7 +4260,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>69</v>
@@ -4317,14 +4282,14 @@
         <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -4333,20 +4298,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -4355,20 +4320,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4390,7 +4355,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -4417,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -4431,14 +4396,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="9" t="s">
-        <v>119</v>
+        <v>333</v>
       </c>
       <c r="H26" s="17"/>
     </row>
@@ -4447,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -4461,14 +4426,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -4483,13 +4448,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>6</v>
@@ -4509,7 +4474,7 @@
         <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -4529,7 +4494,7 @@
         <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>66</v>
@@ -4551,7 +4516,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>66</v>
@@ -4585,7 +4550,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
@@ -4606,7 +4571,7 @@
       <c r="E35" s="39"/>
       <c r="F35" s="39"/>
       <c r="G35" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -4615,7 +4580,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -4636,7 +4601,7 @@
       <c r="E37" s="52"/>
       <c r="F37" s="53"/>
       <c r="G37" s="9" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -4651,13 +4616,13 @@
         <v>11</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>6</v>
@@ -4677,7 +4642,7 @@
         <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -4697,7 +4662,7 @@
         <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>66</v>
@@ -4719,7 +4684,7 @@
         <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>66</v>
@@ -4817,10 +4782,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -4875,7 +4840,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -4972,14 +4937,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4988,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -4996,7 +4961,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5034,14 +4999,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5070,13 +5035,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -5096,7 +5061,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>69</v>
@@ -5118,7 +5083,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -5140,14 +5105,14 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -5156,20 +5121,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -5178,20 +5143,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5213,7 +5178,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -5240,7 +5205,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -5254,14 +5219,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="9" t="s">
-        <v>119</v>
+        <v>333</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -5270,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -5284,14 +5249,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -5306,13 +5271,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -5332,7 +5297,7 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -5352,7 +5317,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>66</v>
@@ -5374,7 +5339,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>66</v>
@@ -5408,7 +5373,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
@@ -5429,7 +5394,7 @@
       <c r="E36" s="39"/>
       <c r="F36" s="39"/>
       <c r="G36" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -5438,7 +5403,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -5459,7 +5424,7 @@
       <c r="E38" s="52"/>
       <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -5474,13 +5439,13 @@
         <v>11</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>6</v>
@@ -5500,7 +5465,7 @@
         <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -5520,7 +5485,7 @@
         <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>66</v>
@@ -5542,7 +5507,7 @@
         <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>66</v>
@@ -5641,10 +5606,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>102</v>
+        <v>331</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -5699,7 +5664,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -5796,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -5804,7 +5769,7 @@
       <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5812,14 +5777,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -5828,7 +5793,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -5836,7 +5801,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5858,14 +5823,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="9" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5894,13 +5859,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -5920,7 +5885,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -5940,7 +5905,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -5962,7 +5927,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -5984,14 +5949,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -6000,20 +5965,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -6022,20 +5987,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -6084,7 +6049,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -6098,14 +6063,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -6114,7 +6079,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -6128,14 +6093,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="9" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -6150,13 +6115,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -6176,7 +6141,7 @@
         <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -6196,7 +6161,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>66</v>
@@ -6218,7 +6183,7 @@
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>66</v>
@@ -6252,7 +6217,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -6273,7 +6238,7 @@
       <c r="E37" s="39"/>
       <c r="F37" s="39"/>
       <c r="G37" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -6282,7 +6247,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -6303,7 +6268,7 @@
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="9" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -6318,13 +6283,13 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>6</v>
@@ -6344,7 +6309,7 @@
         <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -6364,7 +6329,7 @@
         <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>66</v>
@@ -6386,7 +6351,7 @@
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>66</v>
@@ -6485,10 +6450,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>102</v>
+        <v>331</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -6543,7 +6508,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -6640,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -6648,7 +6613,7 @@
       <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6656,14 +6621,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -6672,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -6680,7 +6645,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6718,14 +6683,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="9" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -6754,13 +6719,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>6</v>
@@ -6780,7 +6745,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -6800,7 +6765,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -6822,7 +6787,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>69</v>
@@ -6844,14 +6809,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -6860,20 +6825,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -6882,20 +6847,20 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -6944,7 +6909,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -6958,14 +6923,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -6974,7 +6939,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -6988,14 +6953,14 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="9" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -7010,13 +6975,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -7036,7 +7001,7 @@
         <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -7056,7 +7021,7 @@
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>66</v>
@@ -7078,7 +7043,7 @@
         <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>66</v>
@@ -7112,7 +7077,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -7133,7 +7098,7 @@
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
       <c r="G38" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -7142,7 +7107,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -7163,7 +7128,7 @@
       <c r="E40" s="39"/>
       <c r="F40" s="39"/>
       <c r="G40" s="9" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -7178,13 +7143,13 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>6</v>
@@ -7204,7 +7169,7 @@
         <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -7224,7 +7189,7 @@
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>66</v>
@@ -7246,7 +7211,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>66</v>
@@ -7350,10 +7315,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -7412,7 +7377,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -7503,14 +7468,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -7519,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -7527,7 +7492,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7565,14 +7530,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -7601,13 +7566,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -7627,7 +7592,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -7647,7 +7612,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -7669,7 +7634,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -7691,14 +7656,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -7707,20 +7672,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -7729,20 +7694,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -7791,7 +7756,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -7812,7 +7777,7 @@
       <c r="E28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -7821,14 +7786,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -7837,7 +7802,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -7845,7 +7810,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7853,7 +7818,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -7867,7 +7832,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -7887,13 +7852,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>6</v>
@@ -7913,7 +7878,7 @@
         <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -7933,7 +7898,7 @@
         <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>69</v>
@@ -7955,7 +7920,7 @@
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>69</v>
@@ -7977,14 +7942,14 @@
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -7993,20 +7958,20 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -8015,20 +7980,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -8050,7 +8015,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -8077,7 +8042,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -8091,14 +8056,14 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
       <c r="F43" s="53"/>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -8127,13 +8092,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>6</v>
@@ -8153,7 +8118,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -8173,7 +8138,7 @@
         <v>32</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>66</v>
@@ -8189,13 +8154,13 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>66</v>
@@ -8229,14 +8194,14 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
       <c r="F50" s="53"/>
       <c r="G50" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H50" s="17"/>
     </row>
@@ -8245,7 +8210,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -8279,13 +8244,13 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>6</v>
@@ -8305,7 +8270,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -8325,7 +8290,7 @@
         <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>70</v>
@@ -8347,7 +8312,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>82</v>
@@ -8369,7 +8334,7 @@
         <v>32</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>81</v>
@@ -8391,7 +8356,7 @@
         <v>32</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>81</v>
@@ -8407,20 +8372,20 @@
         <v>27</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>81</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="H59" s="17"/>
     </row>
@@ -8521,10 +8486,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -8583,7 +8548,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -8674,14 +8639,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -8690,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -8698,7 +8663,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8736,14 +8701,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -8772,13 +8737,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -8798,7 +8763,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -8818,7 +8783,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -8840,7 +8805,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -8862,14 +8827,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -8878,20 +8843,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -8900,20 +8865,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -8962,7 +8927,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -8983,7 +8948,7 @@
       <c r="E28" s="52"/>
       <c r="F28" s="53"/>
       <c r="G28" s="9" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -8992,14 +8957,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -9008,7 +8973,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -9016,7 +8981,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -9024,7 +8989,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9038,7 +9003,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -9058,13 +9023,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>6</v>
@@ -9084,7 +9049,7 @@
         <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -9104,7 +9069,7 @@
         <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>69</v>
@@ -9126,7 +9091,7 @@
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>69</v>
@@ -9148,14 +9113,14 @@
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -9164,20 +9129,20 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -9186,20 +9151,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -9221,7 +9186,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -9248,7 +9213,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
@@ -9262,14 +9227,14 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
       <c r="F43" s="53"/>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -9298,13 +9263,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>6</v>
@@ -9324,7 +9289,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -9344,7 +9309,7 @@
         <v>32</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>66</v>
@@ -9360,13 +9325,13 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>66</v>
@@ -9400,14 +9365,14 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
       <c r="F50" s="53"/>
       <c r="G50" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H50" s="17"/>
     </row>
@@ -9416,7 +9381,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -9450,13 +9415,13 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>6</v>
@@ -9476,7 +9441,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -9496,7 +9461,7 @@
         <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>70</v>
@@ -9518,7 +9483,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>82</v>
@@ -9540,7 +9505,7 @@
         <v>32</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>81</v>
@@ -9562,7 +9527,7 @@
         <v>32</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>81</v>
@@ -9578,20 +9543,20 @@
         <v>27</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>81</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="H59" s="17"/>
     </row>
@@ -9647,7 +9612,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ46"/>
+  <dimension ref="A1:AMJ44"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
@@ -9690,10 +9655,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>108</v>
+        <v>324</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -9750,7 +9715,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -9847,14 +9812,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -9890,15 +9855,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
+      <c r="B15" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -9927,13 +9892,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -9953,7 +9918,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -9973,7 +9938,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -9995,7 +9960,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>84</v>
@@ -10017,7 +9982,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>70</v>
@@ -10033,20 +9998,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>85</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -10055,20 +10020,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -10095,7 +10060,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -10109,14 +10074,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -10139,7 +10104,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -10153,7 +10118,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -10173,13 +10138,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -10199,12 +10164,12 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -10219,7 +10184,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>66</v>
@@ -10241,7 +10206,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>66</v>
@@ -10263,7 +10228,7 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>66</v>
@@ -10274,147 +10239,147 @@
       </c>
       <c r="H34" s="17"/>
     </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="17"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="35" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="1" t="s">
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>3</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H38" s="17"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+    </row>
+    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>258</v>
+        <v>68</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
-        <v>3</v>
-      </c>
-      <c r="B40" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="17"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="F40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="10"/>
+        <v>126</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="F42" s="10"/>
-      <c r="G42" s="2" t="s">
-        <v>87</v>
+      <c r="G42" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -10423,88 +10388,44 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H44" s="17"/>
-    </row>
-    <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F45" s="10"/>
-      <c r="G45" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="17"/>
-    </row>
-    <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -10531,16 +10452,16 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B35:F35"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10553,7 +10474,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B3CF47-F6D3-4928-9A2C-ABAAB60B7FC0}">
-  <dimension ref="A1:AMJ46"/>
+  <dimension ref="A1:AMJ44"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
@@ -10596,10 +10517,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>108</v>
+        <v>324</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -10656,7 +10577,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -10753,14 +10674,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -10797,14 +10718,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10833,13 +10754,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -10859,7 +10780,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -10879,7 +10800,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -10901,7 +10822,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>84</v>
@@ -10923,7 +10844,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>70</v>
@@ -10939,20 +10860,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>85</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -10961,20 +10882,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -11001,7 +10922,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -11015,14 +10936,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -11045,7 +10966,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -11059,7 +10980,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -11079,13 +11000,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -11105,12 +11026,12 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -11125,7 +11046,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>66</v>
@@ -11147,7 +11068,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>66</v>
@@ -11169,7 +11090,7 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>66</v>
@@ -11180,147 +11101,147 @@
       </c>
       <c r="H34" s="17"/>
     </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="17"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="35" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="1" t="s">
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>3</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H38" s="17"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+    </row>
+    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>321</v>
+        <v>68</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
-        <v>3</v>
-      </c>
-      <c r="B40" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="17"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="F40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="10"/>
+        <v>126</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="F42" s="10"/>
-      <c r="G42" s="2" t="s">
-        <v>87</v>
+      <c r="G42" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -11329,92 +11250,48 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H44" s="17"/>
-    </row>
-    <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F45" s="10"/>
-      <c r="G45" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="17"/>
-    </row>
-    <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" s="10"/>
-      <c r="G46" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
@@ -11422,10 +11299,10 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -11500,10 +11377,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -11558,7 +11435,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -11655,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -11663,7 +11540,7 @@
       <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11671,14 +11548,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="19" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -11687,7 +11564,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -11695,7 +11572,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11733,14 +11610,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -11769,13 +11646,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G19" s="18" t="s">
         <v>6</v>
@@ -11795,7 +11672,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -11815,7 +11692,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -11837,7 +11714,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>69</v>
@@ -11859,14 +11736,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -11875,20 +11752,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -11897,20 +11774,20 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -12975,7 +12852,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -12996,7 +12873,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="19" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="13"/>
@@ -14021,7 +13898,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -14029,7 +13906,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="19"/>
       <c r="H30" s="17" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
@@ -15053,14 +14930,14 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>230</v>
+        <v>109</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="19" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="13"/>
@@ -16085,7 +15962,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -16093,7 +15970,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -16101,7 +15978,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
@@ -17136,13 +17013,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G34" s="18" t="s">
         <v>6</v>
@@ -18178,7 +18055,7 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -18198,14 +18075,14 @@
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="21" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -18220,14 +18097,14 @@
         <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="21" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -18242,14 +18119,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -18258,20 +18135,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F39" s="10"/>
-      <c r="G39" s="21" t="s">
-        <v>247</v>
+      <c r="G39" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -18280,20 +18157,20 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F40" s="10"/>
-      <c r="G40" s="20" t="s">
-        <v>225</v>
+      <c r="G40" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -18308,14 +18185,14 @@
         <v>32</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F41" s="10"/>
-      <c r="G41" s="20" t="s">
-        <v>91</v>
+      <c r="G41" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -19358,7 +19235,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -19367,19 +19244,19 @@
       <c r="G43" s="19"/>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:1024" ht="301.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1024" ht="319.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
       <c r="E44" s="39"/>
       <c r="F44" s="39"/>
       <c r="G44" s="19" t="s">
-        <v>131</v>
+        <v>335</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="13"/>
@@ -20404,7 +20281,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" s="39"/>
       <c r="D45" s="39"/>
@@ -21440,13 +21317,13 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G46" s="18" t="s">
         <v>6</v>
@@ -22482,7 +22359,7 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -22502,7 +22379,7 @@
         <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>81</v>
@@ -23547,19 +23424,19 @@
       <c r="AMI49" s="13"/>
       <c r="AMJ49" s="13"/>
     </row>
-    <row r="50" spans="1:1024" ht="297" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1024" ht="295.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
       <c r="E50" s="39"/>
       <c r="F50" s="39"/>
       <c r="G50" s="19" t="s">
-        <v>129</v>
+        <v>316</v>
       </c>
       <c r="H50" s="17"/>
       <c r="I50" s="13"/>
@@ -24584,7 +24461,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -25634,13 +25511,13 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G53" s="18" t="s">
         <v>6</v>
@@ -26676,7 +26553,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -26696,7 +26573,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>81</v>
@@ -26801,10 +26678,10 @@
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -26859,7 +26736,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -26956,7 +26833,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -26964,7 +26841,7 @@
       <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26972,14 +26849,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="19" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -26988,7 +26865,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -26996,7 +26873,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -27034,14 +26911,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="19" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -27070,13 +26947,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G19" s="18" t="s">
         <v>6</v>
@@ -27096,7 +26973,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -27116,7 +26993,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -27138,7 +27015,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>69</v>
@@ -27160,14 +27037,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -27176,20 +27053,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -27198,20 +27075,20 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -28276,7 +28153,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -28297,7 +28174,7 @@
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="19" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="13"/>
@@ -29322,7 +29199,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -29330,7 +29207,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="19"/>
       <c r="H30" s="17" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
@@ -30354,14 +30231,14 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>230</v>
+        <v>109</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="19" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="13"/>
@@ -31386,7 +31263,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -31394,7 +31271,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -31402,7 +31279,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
@@ -32437,13 +32314,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G34" s="18" t="s">
         <v>6</v>
@@ -33479,7 +33356,7 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -33499,14 +33376,14 @@
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="21" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -33521,14 +33398,14 @@
         <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>69</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="21" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -33543,14 +33420,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -33559,20 +33436,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F39" s="10"/>
-      <c r="G39" s="21" t="s">
-        <v>247</v>
+      <c r="G39" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -33581,20 +33458,20 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F40" s="10"/>
-      <c r="G40" s="20" t="s">
-        <v>225</v>
+      <c r="G40" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -33609,14 +33486,14 @@
         <v>32</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F41" s="10"/>
-      <c r="G41" s="20" t="s">
-        <v>91</v>
+      <c r="G41" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -34659,7 +34536,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -34668,19 +34545,19 @@
       <c r="G43" s="19"/>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:1024" ht="301.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1024" ht="319.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
       <c r="E44" s="39"/>
       <c r="F44" s="39"/>
       <c r="G44" s="19" t="s">
-        <v>131</v>
+        <v>335</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="13"/>
@@ -35705,7 +35582,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" s="39"/>
       <c r="D45" s="39"/>
@@ -36741,13 +36618,13 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G46" s="18" t="s">
         <v>6</v>
@@ -37783,7 +37660,7 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -37803,7 +37680,7 @@
         <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>81</v>
@@ -38848,19 +38725,19 @@
       <c r="AMI49" s="13"/>
       <c r="AMJ49" s="13"/>
     </row>
-    <row r="50" spans="1:1024" ht="297" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1024" ht="295.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
       <c r="E50" s="39"/>
       <c r="F50" s="39"/>
       <c r="G50" s="19" t="s">
-        <v>129</v>
+        <v>316</v>
       </c>
       <c r="H50" s="17"/>
       <c r="I50" s="13"/>
@@ -39885,7 +39762,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -40935,13 +40812,13 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G53" s="18" t="s">
         <v>6</v>
@@ -41977,7 +41854,7 @@
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -41997,7 +41874,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>81</v>
@@ -42096,16 +41973,16 @@
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>106</v>
+        <v>327</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -42160,7 +42037,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -42257,7 +42134,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -42265,7 +42142,7 @@
       <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -42273,14 +42150,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -42289,7 +42166,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -42297,7 +42174,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -42335,14 +42212,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
       <c r="F17" s="53"/>
       <c r="G17" s="9" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -42371,13 +42248,13 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>6</v>
@@ -42397,7 +42274,7 @@
         <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -42417,7 +42294,7 @@
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>69</v>
@@ -42439,7 +42316,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>69</v>
@@ -42461,14 +42338,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -42477,20 +42354,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -42499,20 +42376,20 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -42561,7 +42438,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -42575,14 +42452,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>118</v>
+        <v>328</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -42591,7 +42468,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -42605,14 +42482,14 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="9" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -42627,13 +42504,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -42653,7 +42530,7 @@
         <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -42673,7 +42550,7 @@
         <v>38</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
@@ -42695,7 +42572,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>29</v>
@@ -42717,7 +42594,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>29</v>
@@ -42739,7 +42616,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>81</v>
@@ -42761,7 +42638,7 @@
         <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
@@ -42783,7 +42660,7 @@
         <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>29</v>
@@ -42817,7 +42694,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -42838,7 +42715,7 @@
       <c r="E42" s="39"/>
       <c r="F42" s="39"/>
       <c r="G42" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -42847,17 +42724,17 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
       <c r="E43" s="39"/>
       <c r="F43" s="39"/>
       <c r="G43" s="9" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -42865,7 +42742,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -42899,13 +42776,13 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>6</v>
@@ -42925,7 +42802,7 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -42945,7 +42822,7 @@
         <v>38</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>29</v>
@@ -42967,7 +42844,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>29</v>
@@ -42989,7 +42866,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>29</v>
@@ -43011,7 +42888,7 @@
         <v>32</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>81</v>
@@ -43033,7 +42910,7 @@
         <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>29</v>
@@ -43055,7 +42932,7 @@
         <v>42</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
@@ -43150,16 +43027,16 @@
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
@@ -43214,7 +43091,7 @@
       </c>
       <c r="F5" s="40"/>
       <c r="G5" s="40" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H5" s="40"/>
     </row>
@@ -43311,14 +43188,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -43327,7 +43204,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -43335,7 +43212,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -43357,14 +43234,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
       <c r="E15" s="52"/>
       <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -43393,13 +43270,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -43419,7 +43296,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -43439,7 +43316,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>69</v>
@@ -43461,7 +43338,7 @@
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>69</v>
@@ -43483,14 +43360,14 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -43499,20 +43376,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -43521,20 +43398,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -43583,7 +43460,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -43604,7 +43481,7 @@
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -43613,7 +43490,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -43627,14 +43504,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -43649,13 +43526,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -43675,7 +43552,7 @@
         <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -43695,7 +43572,7 @@
         <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>29</v>
@@ -43717,7 +43594,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>81</v>
@@ -43739,7 +43616,7 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
@@ -43761,7 +43638,7 @@
         <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>29</v>
@@ -43795,7 +43672,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -43816,7 +43693,7 @@
       <c r="E38" s="39"/>
       <c r="F38" s="39"/>
       <c r="G38" s="9" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -43825,7 +43702,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -43846,7 +43723,7 @@
       <c r="E40" s="39"/>
       <c r="F40" s="39"/>
       <c r="G40" s="9" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -43861,13 +43738,13 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>6</v>
@@ -43887,7 +43764,7 @@
         <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -43907,7 +43784,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>29</v>
@@ -43929,7 +43806,7 @@
         <v>32</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>81</v>
@@ -43951,7 +43828,7 @@
         <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>29</v>
@@ -43973,7 +43850,7 @@
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>29</v>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E5426A-139B-4C32-BE42-A219C9CE0CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853751D1-EC21-4D2E-B0CF-73670D6CEB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21960" yWindow="3855" windowWidth="28770" windowHeight="25050" tabRatio="500" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -934,68 +934,6 @@
  - None</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.7, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 360, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 34, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 52, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 488, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 26, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.5, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 12, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 24, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.4, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 365, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 33, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 14.2, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-  "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario1_NoSpontaneous-InitialHemeostasis.json"} }</t>
   </si>
   <si>
@@ -1062,69 +1000,7 @@
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario7_NoSpontaneous-InterventionApplied.json"} }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 31, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.3, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 26, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 28, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.9, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 365, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 33, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 18, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } },
-  "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 3, "Unit": "min" }}}}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 50, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 70, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 650, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
   </si>
   <si>
     <t>VT for PIP alarm cycling</t>
@@ -1392,27 +1268,6 @@
  - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 33, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 30, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 35, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>{v} = 584</t>
   </si>
   <si>
@@ -1499,27 +1354,6 @@
  - Low MVe = 10.4 L/min (~25% below the initial value)
  - Low VT = 438 mL (~25% below the initial value)
  - High RR = 34 bpm (~10 bpm above the initial value or a max of 40 bpm)</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 38, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 10.4, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 438, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 34, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 60, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.62, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 584, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
   </si>
   <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario3-InitialHemeostasis.json"} }</t>
@@ -1675,26 +1509,6 @@
  - Suction</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
-    "HighPressureThreshold" : { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
-    "HighPressureCycleOption": "On",
-    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 9.6, "Unit": "L/min" } },
-    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 310, "Unit": "mL" } },
-    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 35, "Unit": "1/min" } } } } },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 30, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 25, "Unit": "1/min" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Learning Objectives:
  - Assess baseline status
  - Recognize moderate ARDS
@@ -1765,8 +1579,8 @@
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On",
-    "SupplementalSettings": { "Alarms" : { 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } },
+    "SupplementalSettings": { "Connection": "On",  "Alarms" : { 
     "HighPressureThreshold" : { "ScalarPressure": { "Value": 35, "Unit": "cmH2O" } },
     "HighPressureCycleOption": "On",
     "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 11, "Unit": "L/min" } },
@@ -1779,6 +1593,192 @@
   "InspiratoryPressure": { "ScalarPressure": { "Value": 25, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 28, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.9, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 365, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 33, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 18, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } },
+  "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 24, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.4, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 365, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 33, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 14.2, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
+  "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 9.6, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 310, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 35, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 30, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 25, "Unit": "1/min" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 31, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.3, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 26, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 26, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 7.5, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 290, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 36, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 12, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On",  "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 37, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 8.7, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 360, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 34, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 52, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 488, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 33, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 330, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 30, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 35, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 50, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 6.8, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 70, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 650, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, 
+    "SupplementalSettings": { "Connection": "On", "Alarms" : { 
+    "HighPressureThreshold" : { "ScalarPressure": { "Value": 38, "Unit": "cmH2O" } },
+    "HighPressureCycleOption": "On",
+    "LowMinuteVentilationThreshold" : { "ScalarVolumePerTime": { "Value": 10.4, "Unit": "L/min" } },
+    "LowTidalVolumeThreshold" : { "ScalarVolume": { "Value": 438, "Unit": "mL" } },
+    "HighRespiratoryRateThreshold" : { "ScalarFrequency": { "Value": 34, "Unit": "1/min" } } } } },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 60, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.62, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 584, "Unit": "mL" } },
   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
@@ -3185,7 +3185,7 @@
         <v>230</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -3344,7 +3344,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -3399,14 +3399,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
       <c r="G16" s="9" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -3625,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
@@ -3646,7 +3646,7 @@
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -3655,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C29" s="40"/>
       <c r="D29" s="40"/>
@@ -3676,7 +3676,7 @@
       <c r="E30" s="40"/>
       <c r="F30" s="40"/>
       <c r="G30" s="9" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -3775,7 +3775,7 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>28</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -3841,7 +3841,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>32</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3881,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C40" s="40"/>
       <c r="D40" s="40"/>
@@ -3902,7 +3902,7 @@
       <c r="E41" s="40"/>
       <c r="F41" s="40"/>
       <c r="G41" s="9" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -3911,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C42" s="40"/>
       <c r="D42" s="40"/>
@@ -4031,7 +4031,7 @@
         <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>28</v>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -4183,7 +4183,7 @@
         <v>235</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -4342,7 +4342,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4381,14 +4381,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
       <c r="E15" s="54"/>
       <c r="F15" s="55"/>
       <c r="G15" s="9" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -4601,14 +4601,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
       <c r="E26" s="40"/>
       <c r="F26" s="40"/>
       <c r="G26" s="9" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="H26" s="17"/>
     </row>
@@ -4638,7 +4638,7 @@
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -4737,7 +4737,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>28</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -4798,7 +4798,7 @@
       <c r="E36" s="40"/>
       <c r="F36" s="40"/>
       <c r="G36" s="9" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -4927,7 +4927,7 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>28</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -5034,7 +5034,7 @@
         <v>235</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -5193,7 +5193,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -5248,14 +5248,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
       <c r="G16" s="9" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5454,7 +5454,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -5468,14 +5468,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
       <c r="G27" s="9" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -5484,7 +5484,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -5505,7 +5505,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -5604,7 +5604,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>28</v>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -5644,7 +5644,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -5665,7 +5665,7 @@
       <c r="E37" s="40"/>
       <c r="F37" s="40"/>
       <c r="G37" s="9" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -5674,7 +5674,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40"/>
@@ -5794,7 +5794,7 @@
         <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>28</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -5902,7 +5902,7 @@
         <v>240</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -6077,7 +6077,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="9" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -6116,14 +6116,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>252</v>
+        <v>357</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="40"/>
       <c r="E16" s="40"/>
       <c r="F16" s="40"/>
       <c r="G16" s="9" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -6363,7 +6363,7 @@
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
@@ -6434,12 +6434,12 @@
         <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -6448,7 +6448,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>28</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -6509,7 +6509,7 @@
       <c r="E36" s="40"/>
       <c r="F36" s="40"/>
       <c r="G36" s="9" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -6638,7 +6638,7 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>28</v>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -6746,7 +6746,7 @@
         <v>240</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -6921,7 +6921,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="9" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -6976,14 +6976,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
       <c r="G17" s="9" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -7202,7 +7202,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -7223,7 +7223,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -7232,7 +7232,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
@@ -7246,7 +7246,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -7294,12 +7294,12 @@
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -7308,7 +7308,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -7348,7 +7348,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C36" s="40"/>
       <c r="D36" s="40"/>
@@ -7369,7 +7369,7 @@
       <c r="E37" s="40"/>
       <c r="F37" s="40"/>
       <c r="G37" s="9" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -7378,7 +7378,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40"/>
@@ -7498,7 +7498,7 @@
         <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>28</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -7611,7 +7611,7 @@
         <v>215</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -7768,7 +7768,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -7823,14 +7823,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
       <c r="G16" s="9" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -8070,7 +8070,7 @@
       <c r="E28" s="40"/>
       <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -8086,7 +8086,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -8361,7 +8361,7 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>28</v>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -8415,14 +8415,14 @@
         <v>3</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>
       <c r="F46" s="40"/>
       <c r="G46" s="9" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -8553,14 +8553,14 @@
         <v>4</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C53" s="40"/>
       <c r="D53" s="40"/>
       <c r="E53" s="40"/>
       <c r="F53" s="40"/>
       <c r="G53" s="9" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -8848,7 +8848,7 @@
         <v>215</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -9005,7 +9005,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -9060,14 +9060,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
       <c r="E16" s="54"/>
       <c r="F16" s="55"/>
       <c r="G16" s="9" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H16" s="9"/>
     </row>
@@ -9122,7 +9122,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -9286,7 +9286,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
@@ -9307,7 +9307,7 @@
       <c r="E28" s="54"/>
       <c r="F28" s="55"/>
       <c r="G28" s="9" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -9323,7 +9323,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -9348,7 +9348,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -9638,7 +9638,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C45" s="40"/>
       <c r="D45" s="40"/>
@@ -9652,14 +9652,14 @@
         <v>3</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
       <c r="E46" s="40"/>
       <c r="F46" s="40"/>
       <c r="G46" s="9" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -9790,14 +9790,14 @@
         <v>4</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C53" s="40"/>
       <c r="D53" s="40"/>
       <c r="E53" s="40"/>
       <c r="F53" s="40"/>
       <c r="G53" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -9806,7 +9806,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C54" s="40"/>
       <c r="D54" s="40"/>
@@ -10083,7 +10083,7 @@
         <v>219</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -10244,7 +10244,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -10281,14 +10281,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>278</v>
+        <v>363</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
       <c r="E15" s="54"/>
       <c r="F15" s="55"/>
       <c r="G15" s="9" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -10594,7 +10594,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -10701,14 +10701,14 @@
         <v>3</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C37" s="54"/>
       <c r="D37" s="54"/>
       <c r="E37" s="54"/>
       <c r="F37" s="55"/>
       <c r="G37" s="9" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -10945,7 +10945,7 @@
         <v>219</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -11106,7 +11106,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -11143,14 +11143,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>278</v>
+        <v>363</v>
       </c>
       <c r="C15" s="40"/>
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
       <c r="G15" s="9" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -11347,7 +11347,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40"/>
@@ -11368,7 +11368,7 @@
       <c r="E26" s="40"/>
       <c r="F26" s="40"/>
       <c r="G26" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -11391,7 +11391,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -11456,7 +11456,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -11563,14 +11563,14 @@
         <v>3</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C37" s="54"/>
       <c r="D37" s="54"/>
       <c r="E37" s="54"/>
       <c r="F37" s="55"/>
       <c r="G37" s="9" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -11579,7 +11579,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40"/>
@@ -12821,7 +12821,7 @@
         <v>224</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -24172,7 +24172,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="19" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="13"/>
@@ -27275,14 +27275,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
       <c r="G17" s="19" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="13"/>
@@ -31565,7 +31565,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -32602,7 +32602,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="19" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="13"/>
@@ -33627,7 +33627,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
@@ -33635,7 +33635,7 @@
       <c r="F30" s="40"/>
       <c r="G30" s="19"/>
       <c r="H30" s="17" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
@@ -38805,7 +38805,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="20" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -38902,7 +38902,7 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -38915,7 +38915,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -40025,24 +40025,24 @@
     </row>
     <row r="45" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H45" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -41084,7 +41084,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C47" s="40"/>
       <c r="D47" s="40"/>
@@ -42114,14 +42114,14 @@
         <v>3</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C48" s="40"/>
       <c r="D48" s="40"/>
       <c r="E48" s="40"/>
       <c r="F48" s="40"/>
       <c r="G48" s="19" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="H48" s="17"/>
       <c r="I48" s="13"/>
@@ -45257,24 +45257,24 @@
     </row>
     <row r="53" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="36" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H53" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -46316,14 +46316,14 @@
         <v>4</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C55" s="40"/>
       <c r="D55" s="40"/>
       <c r="E55" s="40"/>
       <c r="F55" s="40"/>
       <c r="G55" s="19" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="13"/>
@@ -47348,7 +47348,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C56" s="40"/>
       <c r="D56" s="40"/>
@@ -50470,7 +50470,7 @@
         <v>27</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>28</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="F60" s="10"/>
       <c r="G60" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H60" s="17"/>
     </row>
@@ -50511,32 +50511,30 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B17:F17"/>
@@ -50550,6 +50548,8 @@
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -50605,7 +50605,7 @@
         <v>224</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -50780,7 +50780,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="19" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -50835,14 +50835,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
       <c r="E17" s="40"/>
       <c r="F17" s="40"/>
       <c r="G17" s="19" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -51061,7 +51061,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -51082,7 +51082,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="19" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -51098,7 +51098,7 @@
       <c r="E30" s="40"/>
       <c r="F30" s="40"/>
       <c r="G30" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -51107,7 +51107,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C31" s="40"/>
       <c r="D31" s="40"/>
@@ -51115,7 +51115,7 @@
       <c r="F31" s="40"/>
       <c r="G31" s="19"/>
       <c r="H31" s="17" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -51189,7 +51189,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="20" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -51286,7 +51286,7 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -51393,24 +51393,24 @@
     </row>
     <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H45" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -51436,7 +51436,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C47" s="40"/>
       <c r="D47" s="40"/>
@@ -51450,14 +51450,14 @@
         <v>3</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C48" s="40"/>
       <c r="D48" s="40"/>
       <c r="E48" s="40"/>
       <c r="F48" s="40"/>
       <c r="G48" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -51545,24 +51545,24 @@
     </row>
     <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="36" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H53" s="36" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -51588,14 +51588,14 @@
         <v>4</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C55" s="40"/>
       <c r="D55" s="40"/>
       <c r="E55" s="40"/>
       <c r="F55" s="40"/>
       <c r="G55" s="19" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H55" s="17"/>
     </row>
@@ -51604,7 +51604,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C56" s="40"/>
       <c r="D56" s="40"/>
@@ -51678,7 +51678,7 @@
         <v>27</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>28</v>
@@ -51691,7 +51691,7 @@
       </c>
       <c r="F60" s="10"/>
       <c r="G60" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H60" s="17"/>
     </row>
@@ -51814,7 +51814,7 @@
         <v>225</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -51989,7 +51989,7 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="9" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -52044,14 +52044,14 @@
         <v>1</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>250</v>
+        <v>361</v>
       </c>
       <c r="C17" s="54"/>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
       <c r="F17" s="55"/>
       <c r="G17" s="9" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -52291,7 +52291,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -52464,7 +52464,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
@@ -52477,7 +52477,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -52569,7 +52569,7 @@
       <c r="E43" s="40"/>
       <c r="F43" s="40"/>
       <c r="G43" s="9" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -52585,7 +52585,7 @@
       <c r="E44" s="40"/>
       <c r="F44" s="40"/>
       <c r="G44" s="9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>91</v>
@@ -52758,7 +52758,7 @@
         <v>27</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>28</v>
@@ -52771,7 +52771,7 @@
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -52912,7 +52912,7 @@
         <v>230</v>
       </c>
       <c r="F2" s="52" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
@@ -53071,7 +53071,7 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -53110,14 +53110,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
       <c r="E15" s="54"/>
       <c r="F15" s="55"/>
       <c r="G15" s="9" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -53357,7 +53357,7 @@
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
       <c r="G27" s="9" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -53387,7 +53387,7 @@
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -53486,7 +53486,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>28</v>
@@ -53499,7 +53499,7 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -53552,7 +53552,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>32</v>
@@ -53565,7 +53565,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -53613,7 +53613,7 @@
       <c r="E40" s="40"/>
       <c r="F40" s="40"/>
       <c r="G40" s="9" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -53742,7 +53742,7 @@
         <v>27</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>28</v>
@@ -53755,7 +53755,7 @@
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H47" s="17"/>
     </row>

--- a/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
+++ b/data/human/adult/validation/Scenarios/EnRouteCare/EnRouteCare.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_updates\source\data\human\adult\validation\Scenarios\EnRouteCare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C40105-E6E5-4781-B53C-47C555B1D8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85862730-B75E-4BD4-BFD2-17CFA3285300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23790" yWindow="3195" windowWidth="31125" windowHeight="24240" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4335" yWindow="5385" windowWidth="30630" windowHeight="23445" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="363">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -1787,6 +1787,12 @@
   "TidalVolume":{"ScalarVolume":{"Value":350,"Unit":"mL"}}
 }}}</t>
   </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario3_NoSpontaneous-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "./states/EnRouteCare/Scenario3-InterventionApplied.json"} }</t>
+  </si>
 </sst>
 </file>
 
@@ -2318,10 +2324,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2343,24 +2367,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3176,50 +3182,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3254,14 +3260,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -3274,60 +3280,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3420,10 +3426,10 @@
       <c r="B16" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="9" t="s">
         <v>310</v>
       </c>
@@ -3625,13 +3631,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -3881,13 +3887,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -4113,11 +4119,21 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B10:F10"/>
@@ -4131,21 +4147,11 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4174,50 +4180,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4252,14 +4258,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4272,60 +4278,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4399,13 +4405,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="55"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="9" t="s">
         <v>343</v>
       </c>
@@ -4587,13 +4593,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4777,13 +4783,13 @@
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -4839,13 +4845,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="55"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="44"/>
       <c r="G38" s="9" t="s">
         <v>246</v>
       </c>
@@ -4965,28 +4971,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
@@ -4997,6 +4981,28 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5025,50 +5031,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -5103,14 +5109,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -5123,60 +5129,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5266,13 +5272,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="9" t="s">
         <v>337</v>
       </c>
@@ -5454,13 +5460,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -5644,13 +5650,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -5706,13 +5712,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="53" t="s">
+      <c r="B39" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="55"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
       <c r="G39" s="9" t="s">
         <v>246</v>
       </c>
@@ -5832,11 +5838,21 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B10:F10"/>
@@ -5850,21 +5866,11 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5893,50 +5899,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -5971,14 +5977,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -5991,60 +5997,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6072,13 +6078,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>100</v>
@@ -6342,13 +6348,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -6488,13 +6494,13 @@
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -6676,28 +6682,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
@@ -6709,6 +6693,28 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6737,50 +6743,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -6815,14 +6821,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -6835,60 +6841,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6916,13 +6922,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>100</v>
@@ -6964,13 +6970,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="55"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="19"/>
       <c r="H15" s="17" t="s">
         <v>24</v>
@@ -7202,13 +7208,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -7348,13 +7354,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -7536,6 +7542,28 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -7548,28 +7576,6 @@
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -7598,42 +7604,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -7643,13 +7649,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -7684,74 +7690,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -7844,10 +7850,10 @@
       <c r="B16" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="9" t="s">
         <v>311</v>
       </c>
@@ -8049,13 +8055,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -8401,13 +8407,13 @@
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
       <c r="G44" s="1" t="s">
         <v>6</v>
       </c>
@@ -8553,13 +8559,13 @@
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="1" t="s">
         <v>6</v>
       </c>
@@ -8601,13 +8607,13 @@
       <c r="A55" s="8">
         <v>4</v>
       </c>
-      <c r="B55" s="53" t="s">
+      <c r="B55" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="55"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="44"/>
       <c r="G55" s="9"/>
       <c r="H55" s="17"/>
     </row>
@@ -8769,6 +8775,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B53:F53"/>
@@ -8785,28 +8813,6 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -8835,42 +8841,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -8880,13 +8886,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -8921,74 +8927,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -9081,10 +9087,10 @@
       <c r="B16" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="55"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="9" t="s">
         <v>311</v>
       </c>
@@ -9286,13 +9292,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -9318,13 +9324,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="44"/>
       <c r="G28" s="9" t="s">
         <v>317</v>
       </c>
@@ -9638,13 +9644,13 @@
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
       <c r="G44" s="1" t="s">
         <v>6</v>
       </c>
@@ -9790,13 +9796,13 @@
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="1" t="s">
         <v>6</v>
       </c>
@@ -9838,13 +9844,13 @@
       <c r="A55" s="8">
         <v>4</v>
       </c>
-      <c r="B55" s="53" t="s">
+      <c r="B55" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="55"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="44"/>
       <c r="G55" s="9"/>
       <c r="H55" s="17"/>
     </row>
@@ -10006,23 +10012,12 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -10038,12 +10033,23 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B55:F55"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10072,40 +10078,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -10113,13 +10119,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -10154,14 +10160,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -10174,60 +10180,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10299,13 +10305,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="42" t="s">
         <v>351</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="55"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="9" t="s">
         <v>289</v>
       </c>
@@ -10485,13 +10491,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -10687,13 +10693,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -10719,13 +10725,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="55"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
       <c r="G37" s="9" t="s">
         <v>277</v>
       </c>
@@ -10873,27 +10879,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B37:F37"/>
@@ -10906,6 +10891,27 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10934,40 +10940,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -10975,13 +10981,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -11016,14 +11022,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -11036,60 +11042,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -11347,13 +11353,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -11549,13 +11555,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -11581,13 +11587,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="55"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
       <c r="G37" s="9" t="s">
         <v>304</v>
       </c>
@@ -11735,18 +11741,12 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -11762,12 +11762,18 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -11780,7 +11786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AMJ53"/>
+  <dimension ref="A1:AMJ54"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
@@ -11796,22 +11802,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -12830,20 +12836,20 @@
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -13865,13 +13871,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -15938,14 +15944,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -16974,12 +16980,12 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -18002,12 +18008,12 @@
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
@@ -19030,12 +19036,12 @@
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -20058,12 +20064,12 @@
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
@@ -21085,13 +21091,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -22119,13 +22125,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="55"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -23151,13 +23157,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>100</v>
@@ -30549,13 +30555,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -40068,13 +40074,13 @@
       <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
       <c r="G46" s="18" t="s">
         <v>6</v>
       </c>
@@ -43160,1061 +43166,33 @@
       <c r="AMI48" s="13"/>
       <c r="AMJ48" s="13"/>
     </row>
-    <row r="49" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>3</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>93</v>
+        <v>362</v>
       </c>
       <c r="C49" s="40"/>
       <c r="D49" s="40"/>
       <c r="E49" s="40"/>
       <c r="F49" s="40"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="13"/>
-      <c r="AG49" s="13"/>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="13"/>
-      <c r="AJ49" s="13"/>
-      <c r="AK49" s="13"/>
-      <c r="AL49" s="13"/>
-      <c r="AM49" s="13"/>
-      <c r="AN49" s="13"/>
-      <c r="AO49" s="13"/>
-      <c r="AP49" s="13"/>
-      <c r="AQ49" s="13"/>
-      <c r="AR49" s="13"/>
-      <c r="AS49" s="13"/>
-      <c r="AT49" s="13"/>
-      <c r="AU49" s="13"/>
-      <c r="AV49" s="13"/>
-      <c r="AW49" s="13"/>
-      <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
-      <c r="AZ49" s="13"/>
-      <c r="BA49" s="13"/>
-      <c r="BB49" s="13"/>
-      <c r="BC49" s="13"/>
-      <c r="BD49" s="13"/>
-      <c r="BE49" s="13"/>
-      <c r="BF49" s="13"/>
-      <c r="BG49" s="13"/>
-      <c r="BH49" s="13"/>
-      <c r="BI49" s="13"/>
-      <c r="BJ49" s="13"/>
-      <c r="BK49" s="13"/>
-      <c r="BL49" s="13"/>
-      <c r="BM49" s="13"/>
-      <c r="BN49" s="13"/>
-      <c r="BO49" s="13"/>
-      <c r="BP49" s="13"/>
-      <c r="BQ49" s="13"/>
-      <c r="BR49" s="13"/>
-      <c r="BS49" s="13"/>
-      <c r="BT49" s="13"/>
-      <c r="BU49" s="13"/>
-      <c r="BV49" s="13"/>
-      <c r="BW49" s="13"/>
-      <c r="BX49" s="13"/>
-      <c r="BY49" s="13"/>
-      <c r="BZ49" s="13"/>
-      <c r="CA49" s="13"/>
-      <c r="CB49" s="13"/>
-      <c r="CC49" s="13"/>
-      <c r="CD49" s="13"/>
-      <c r="CE49" s="13"/>
-      <c r="CF49" s="13"/>
-      <c r="CG49" s="13"/>
-      <c r="CH49" s="13"/>
-      <c r="CI49" s="13"/>
-      <c r="CJ49" s="13"/>
-      <c r="CK49" s="13"/>
-      <c r="CL49" s="13"/>
-      <c r="CM49" s="13"/>
-      <c r="CN49" s="13"/>
-      <c r="CO49" s="13"/>
-      <c r="CP49" s="13"/>
-      <c r="CQ49" s="13"/>
-      <c r="CR49" s="13"/>
-      <c r="CS49" s="13"/>
-      <c r="CT49" s="13"/>
-      <c r="CU49" s="13"/>
-      <c r="CV49" s="13"/>
-      <c r="CW49" s="13"/>
-      <c r="CX49" s="13"/>
-      <c r="CY49" s="13"/>
-      <c r="CZ49" s="13"/>
-      <c r="DA49" s="13"/>
-      <c r="DB49" s="13"/>
-      <c r="DC49" s="13"/>
-      <c r="DD49" s="13"/>
-      <c r="DE49" s="13"/>
-      <c r="DF49" s="13"/>
-      <c r="DG49" s="13"/>
-      <c r="DH49" s="13"/>
-      <c r="DI49" s="13"/>
-      <c r="DJ49" s="13"/>
-      <c r="DK49" s="13"/>
-      <c r="DL49" s="13"/>
-      <c r="DM49" s="13"/>
-      <c r="DN49" s="13"/>
-      <c r="DO49" s="13"/>
-      <c r="DP49" s="13"/>
-      <c r="DQ49" s="13"/>
-      <c r="DR49" s="13"/>
-      <c r="DS49" s="13"/>
-      <c r="DT49" s="13"/>
-      <c r="DU49" s="13"/>
-      <c r="DV49" s="13"/>
-      <c r="DW49" s="13"/>
-      <c r="DX49" s="13"/>
-      <c r="DY49" s="13"/>
-      <c r="DZ49" s="13"/>
-      <c r="EA49" s="13"/>
-      <c r="EB49" s="13"/>
-      <c r="EC49" s="13"/>
-      <c r="ED49" s="13"/>
-      <c r="EE49" s="13"/>
-      <c r="EF49" s="13"/>
-      <c r="EG49" s="13"/>
-      <c r="EH49" s="13"/>
-      <c r="EI49" s="13"/>
-      <c r="EJ49" s="13"/>
-      <c r="EK49" s="13"/>
-      <c r="EL49" s="13"/>
-      <c r="EM49" s="13"/>
-      <c r="EN49" s="13"/>
-      <c r="EO49" s="13"/>
-      <c r="EP49" s="13"/>
-      <c r="EQ49" s="13"/>
-      <c r="ER49" s="13"/>
-      <c r="ES49" s="13"/>
-      <c r="ET49" s="13"/>
-      <c r="EU49" s="13"/>
-      <c r="EV49" s="13"/>
-      <c r="EW49" s="13"/>
-      <c r="EX49" s="13"/>
-      <c r="EY49" s="13"/>
-      <c r="EZ49" s="13"/>
-      <c r="FA49" s="13"/>
-      <c r="FB49" s="13"/>
-      <c r="FC49" s="13"/>
-      <c r="FD49" s="13"/>
-      <c r="FE49" s="13"/>
-      <c r="FF49" s="13"/>
-      <c r="FG49" s="13"/>
-      <c r="FH49" s="13"/>
-      <c r="FI49" s="13"/>
-      <c r="FJ49" s="13"/>
-      <c r="FK49" s="13"/>
-      <c r="FL49" s="13"/>
-      <c r="FM49" s="13"/>
-      <c r="FN49" s="13"/>
-      <c r="FO49" s="13"/>
-      <c r="FP49" s="13"/>
-      <c r="FQ49" s="13"/>
-      <c r="FR49" s="13"/>
-      <c r="FS49" s="13"/>
-      <c r="FT49" s="13"/>
-      <c r="FU49" s="13"/>
-      <c r="FV49" s="13"/>
-      <c r="FW49" s="13"/>
-      <c r="FX49" s="13"/>
-      <c r="FY49" s="13"/>
-      <c r="FZ49" s="13"/>
-      <c r="GA49" s="13"/>
-      <c r="GB49" s="13"/>
-      <c r="GC49" s="13"/>
-      <c r="GD49" s="13"/>
-      <c r="GE49" s="13"/>
-      <c r="GF49" s="13"/>
-      <c r="GG49" s="13"/>
-      <c r="GH49" s="13"/>
-      <c r="GI49" s="13"/>
-      <c r="GJ49" s="13"/>
-      <c r="GK49" s="13"/>
-      <c r="GL49" s="13"/>
-      <c r="GM49" s="13"/>
-      <c r="GN49" s="13"/>
-      <c r="GO49" s="13"/>
-      <c r="GP49" s="13"/>
-      <c r="GQ49" s="13"/>
-      <c r="GR49" s="13"/>
-      <c r="GS49" s="13"/>
-      <c r="GT49" s="13"/>
-      <c r="GU49" s="13"/>
-      <c r="GV49" s="13"/>
-      <c r="GW49" s="13"/>
-      <c r="GX49" s="13"/>
-      <c r="GY49" s="13"/>
-      <c r="GZ49" s="13"/>
-      <c r="HA49" s="13"/>
-      <c r="HB49" s="13"/>
-      <c r="HC49" s="13"/>
-      <c r="HD49" s="13"/>
-      <c r="HE49" s="13"/>
-      <c r="HF49" s="13"/>
-      <c r="HG49" s="13"/>
-      <c r="HH49" s="13"/>
-      <c r="HI49" s="13"/>
-      <c r="HJ49" s="13"/>
-      <c r="HK49" s="13"/>
-      <c r="HL49" s="13"/>
-      <c r="HM49" s="13"/>
-      <c r="HN49" s="13"/>
-      <c r="HO49" s="13"/>
-      <c r="HP49" s="13"/>
-      <c r="HQ49" s="13"/>
-      <c r="HR49" s="13"/>
-      <c r="HS49" s="13"/>
-      <c r="HT49" s="13"/>
-      <c r="HU49" s="13"/>
-      <c r="HV49" s="13"/>
-      <c r="HW49" s="13"/>
-      <c r="HX49" s="13"/>
-      <c r="HY49" s="13"/>
-      <c r="HZ49" s="13"/>
-      <c r="IA49" s="13"/>
-      <c r="IB49" s="13"/>
-      <c r="IC49" s="13"/>
-      <c r="ID49" s="13"/>
-      <c r="IE49" s="13"/>
-      <c r="IF49" s="13"/>
-      <c r="IG49" s="13"/>
-      <c r="IH49" s="13"/>
-      <c r="II49" s="13"/>
-      <c r="IJ49" s="13"/>
-      <c r="IK49" s="13"/>
-      <c r="IL49" s="13"/>
-      <c r="IM49" s="13"/>
-      <c r="IN49" s="13"/>
-      <c r="IO49" s="13"/>
-      <c r="IP49" s="13"/>
-      <c r="IQ49" s="13"/>
-      <c r="IR49" s="13"/>
-      <c r="IS49" s="13"/>
-      <c r="IT49" s="13"/>
-      <c r="IU49" s="13"/>
-      <c r="IV49" s="13"/>
-      <c r="IW49" s="13"/>
-      <c r="IX49" s="13"/>
-      <c r="IY49" s="13"/>
-      <c r="IZ49" s="13"/>
-      <c r="JA49" s="13"/>
-      <c r="JB49" s="13"/>
-      <c r="JC49" s="13"/>
-      <c r="JD49" s="13"/>
-      <c r="JE49" s="13"/>
-      <c r="JF49" s="13"/>
-      <c r="JG49" s="13"/>
-      <c r="JH49" s="13"/>
-      <c r="JI49" s="13"/>
-      <c r="JJ49" s="13"/>
-      <c r="JK49" s="13"/>
-      <c r="JL49" s="13"/>
-      <c r="JM49" s="13"/>
-      <c r="JN49" s="13"/>
-      <c r="JO49" s="13"/>
-      <c r="JP49" s="13"/>
-      <c r="JQ49" s="13"/>
-      <c r="JR49" s="13"/>
-      <c r="JS49" s="13"/>
-      <c r="JT49" s="13"/>
-      <c r="JU49" s="13"/>
-      <c r="JV49" s="13"/>
-      <c r="JW49" s="13"/>
-      <c r="JX49" s="13"/>
-      <c r="JY49" s="13"/>
-      <c r="JZ49" s="13"/>
-      <c r="KA49" s="13"/>
-      <c r="KB49" s="13"/>
-      <c r="KC49" s="13"/>
-      <c r="KD49" s="13"/>
-      <c r="KE49" s="13"/>
-      <c r="KF49" s="13"/>
-      <c r="KG49" s="13"/>
-      <c r="KH49" s="13"/>
-      <c r="KI49" s="13"/>
-      <c r="KJ49" s="13"/>
-      <c r="KK49" s="13"/>
-      <c r="KL49" s="13"/>
-      <c r="KM49" s="13"/>
-      <c r="KN49" s="13"/>
-      <c r="KO49" s="13"/>
-      <c r="KP49" s="13"/>
-      <c r="KQ49" s="13"/>
-      <c r="KR49" s="13"/>
-      <c r="KS49" s="13"/>
-      <c r="KT49" s="13"/>
-      <c r="KU49" s="13"/>
-      <c r="KV49" s="13"/>
-      <c r="KW49" s="13"/>
-      <c r="KX49" s="13"/>
-      <c r="KY49" s="13"/>
-      <c r="KZ49" s="13"/>
-      <c r="LA49" s="13"/>
-      <c r="LB49" s="13"/>
-      <c r="LC49" s="13"/>
-      <c r="LD49" s="13"/>
-      <c r="LE49" s="13"/>
-      <c r="LF49" s="13"/>
-      <c r="LG49" s="13"/>
-      <c r="LH49" s="13"/>
-      <c r="LI49" s="13"/>
-      <c r="LJ49" s="13"/>
-      <c r="LK49" s="13"/>
-      <c r="LL49" s="13"/>
-      <c r="LM49" s="13"/>
-      <c r="LN49" s="13"/>
-      <c r="LO49" s="13"/>
-      <c r="LP49" s="13"/>
-      <c r="LQ49" s="13"/>
-      <c r="LR49" s="13"/>
-      <c r="LS49" s="13"/>
-      <c r="LT49" s="13"/>
-      <c r="LU49" s="13"/>
-      <c r="LV49" s="13"/>
-      <c r="LW49" s="13"/>
-      <c r="LX49" s="13"/>
-      <c r="LY49" s="13"/>
-      <c r="LZ49" s="13"/>
-      <c r="MA49" s="13"/>
-      <c r="MB49" s="13"/>
-      <c r="MC49" s="13"/>
-      <c r="MD49" s="13"/>
-      <c r="ME49" s="13"/>
-      <c r="MF49" s="13"/>
-      <c r="MG49" s="13"/>
-      <c r="MH49" s="13"/>
-      <c r="MI49" s="13"/>
-      <c r="MJ49" s="13"/>
-      <c r="MK49" s="13"/>
-      <c r="ML49" s="13"/>
-      <c r="MM49" s="13"/>
-      <c r="MN49" s="13"/>
-      <c r="MO49" s="13"/>
-      <c r="MP49" s="13"/>
-      <c r="MQ49" s="13"/>
-      <c r="MR49" s="13"/>
-      <c r="MS49" s="13"/>
-      <c r="MT49" s="13"/>
-      <c r="MU49" s="13"/>
-      <c r="MV49" s="13"/>
-      <c r="MW49" s="13"/>
-      <c r="MX49" s="13"/>
-      <c r="MY49" s="13"/>
-      <c r="MZ49" s="13"/>
-      <c r="NA49" s="13"/>
-      <c r="NB49" s="13"/>
-      <c r="NC49" s="13"/>
-      <c r="ND49" s="13"/>
-      <c r="NE49" s="13"/>
-      <c r="NF49" s="13"/>
-      <c r="NG49" s="13"/>
-      <c r="NH49" s="13"/>
-      <c r="NI49" s="13"/>
-      <c r="NJ49" s="13"/>
-      <c r="NK49" s="13"/>
-      <c r="NL49" s="13"/>
-      <c r="NM49" s="13"/>
-      <c r="NN49" s="13"/>
-      <c r="NO49" s="13"/>
-      <c r="NP49" s="13"/>
-      <c r="NQ49" s="13"/>
-      <c r="NR49" s="13"/>
-      <c r="NS49" s="13"/>
-      <c r="NT49" s="13"/>
-      <c r="NU49" s="13"/>
-      <c r="NV49" s="13"/>
-      <c r="NW49" s="13"/>
-      <c r="NX49" s="13"/>
-      <c r="NY49" s="13"/>
-      <c r="NZ49" s="13"/>
-      <c r="OA49" s="13"/>
-      <c r="OB49" s="13"/>
-      <c r="OC49" s="13"/>
-      <c r="OD49" s="13"/>
-      <c r="OE49" s="13"/>
-      <c r="OF49" s="13"/>
-      <c r="OG49" s="13"/>
-      <c r="OH49" s="13"/>
-      <c r="OI49" s="13"/>
-      <c r="OJ49" s="13"/>
-      <c r="OK49" s="13"/>
-      <c r="OL49" s="13"/>
-      <c r="OM49" s="13"/>
-      <c r="ON49" s="13"/>
-      <c r="OO49" s="13"/>
-      <c r="OP49" s="13"/>
-      <c r="OQ49" s="13"/>
-      <c r="OR49" s="13"/>
-      <c r="OS49" s="13"/>
-      <c r="OT49" s="13"/>
-      <c r="OU49" s="13"/>
-      <c r="OV49" s="13"/>
-      <c r="OW49" s="13"/>
-      <c r="OX49" s="13"/>
-      <c r="OY49" s="13"/>
-      <c r="OZ49" s="13"/>
-      <c r="PA49" s="13"/>
-      <c r="PB49" s="13"/>
-      <c r="PC49" s="13"/>
-      <c r="PD49" s="13"/>
-      <c r="PE49" s="13"/>
-      <c r="PF49" s="13"/>
-      <c r="PG49" s="13"/>
-      <c r="PH49" s="13"/>
-      <c r="PI49" s="13"/>
-      <c r="PJ49" s="13"/>
-      <c r="PK49" s="13"/>
-      <c r="PL49" s="13"/>
-      <c r="PM49" s="13"/>
-      <c r="PN49" s="13"/>
-      <c r="PO49" s="13"/>
-      <c r="PP49" s="13"/>
-      <c r="PQ49" s="13"/>
-      <c r="PR49" s="13"/>
-      <c r="PS49" s="13"/>
-      <c r="PT49" s="13"/>
-      <c r="PU49" s="13"/>
-      <c r="PV49" s="13"/>
-      <c r="PW49" s="13"/>
-      <c r="PX49" s="13"/>
-      <c r="PY49" s="13"/>
-      <c r="PZ49" s="13"/>
-      <c r="QA49" s="13"/>
-      <c r="QB49" s="13"/>
-      <c r="QC49" s="13"/>
-      <c r="QD49" s="13"/>
-      <c r="QE49" s="13"/>
-      <c r="QF49" s="13"/>
-      <c r="QG49" s="13"/>
-      <c r="QH49" s="13"/>
-      <c r="QI49" s="13"/>
-      <c r="QJ49" s="13"/>
-      <c r="QK49" s="13"/>
-      <c r="QL49" s="13"/>
-      <c r="QM49" s="13"/>
-      <c r="QN49" s="13"/>
-      <c r="QO49" s="13"/>
-      <c r="QP49" s="13"/>
-      <c r="QQ49" s="13"/>
-      <c r="QR49" s="13"/>
-      <c r="QS49" s="13"/>
-      <c r="QT49" s="13"/>
-      <c r="QU49" s="13"/>
-      <c r="QV49" s="13"/>
-      <c r="QW49" s="13"/>
-      <c r="QX49" s="13"/>
-      <c r="QY49" s="13"/>
-      <c r="QZ49" s="13"/>
-      <c r="RA49" s="13"/>
-      <c r="RB49" s="13"/>
-      <c r="RC49" s="13"/>
-      <c r="RD49" s="13"/>
-      <c r="RE49" s="13"/>
-      <c r="RF49" s="13"/>
-      <c r="RG49" s="13"/>
-      <c r="RH49" s="13"/>
-      <c r="RI49" s="13"/>
-      <c r="RJ49" s="13"/>
-      <c r="RK49" s="13"/>
-      <c r="RL49" s="13"/>
-      <c r="RM49" s="13"/>
-      <c r="RN49" s="13"/>
-      <c r="RO49" s="13"/>
-      <c r="RP49" s="13"/>
-      <c r="RQ49" s="13"/>
-      <c r="RR49" s="13"/>
-      <c r="RS49" s="13"/>
-      <c r="RT49" s="13"/>
-      <c r="RU49" s="13"/>
-      <c r="RV49" s="13"/>
-      <c r="RW49" s="13"/>
-      <c r="RX49" s="13"/>
-      <c r="RY49" s="13"/>
-      <c r="RZ49" s="13"/>
-      <c r="SA49" s="13"/>
-      <c r="SB49" s="13"/>
-      <c r="SC49" s="13"/>
-      <c r="SD49" s="13"/>
-      <c r="SE49" s="13"/>
-      <c r="SF49" s="13"/>
-      <c r="SG49" s="13"/>
-      <c r="SH49" s="13"/>
-      <c r="SI49" s="13"/>
-      <c r="SJ49" s="13"/>
-      <c r="SK49" s="13"/>
-      <c r="SL49" s="13"/>
-      <c r="SM49" s="13"/>
-      <c r="SN49" s="13"/>
-      <c r="SO49" s="13"/>
-      <c r="SP49" s="13"/>
-      <c r="SQ49" s="13"/>
-      <c r="SR49" s="13"/>
-      <c r="SS49" s="13"/>
-      <c r="ST49" s="13"/>
-      <c r="SU49" s="13"/>
-      <c r="SV49" s="13"/>
-      <c r="SW49" s="13"/>
-      <c r="SX49" s="13"/>
-      <c r="SY49" s="13"/>
-      <c r="SZ49" s="13"/>
-      <c r="TA49" s="13"/>
-      <c r="TB49" s="13"/>
-      <c r="TC49" s="13"/>
-      <c r="TD49" s="13"/>
-      <c r="TE49" s="13"/>
-      <c r="TF49" s="13"/>
-      <c r="TG49" s="13"/>
-      <c r="TH49" s="13"/>
-      <c r="TI49" s="13"/>
-      <c r="TJ49" s="13"/>
-      <c r="TK49" s="13"/>
-      <c r="TL49" s="13"/>
-      <c r="TM49" s="13"/>
-      <c r="TN49" s="13"/>
-      <c r="TO49" s="13"/>
-      <c r="TP49" s="13"/>
-      <c r="TQ49" s="13"/>
-      <c r="TR49" s="13"/>
-      <c r="TS49" s="13"/>
-      <c r="TT49" s="13"/>
-      <c r="TU49" s="13"/>
-      <c r="TV49" s="13"/>
-      <c r="TW49" s="13"/>
-      <c r="TX49" s="13"/>
-      <c r="TY49" s="13"/>
-      <c r="TZ49" s="13"/>
-      <c r="UA49" s="13"/>
-      <c r="UB49" s="13"/>
-      <c r="UC49" s="13"/>
-      <c r="UD49" s="13"/>
-      <c r="UE49" s="13"/>
-      <c r="UF49" s="13"/>
-      <c r="UG49" s="13"/>
-      <c r="UH49" s="13"/>
-      <c r="UI49" s="13"/>
-      <c r="UJ49" s="13"/>
-      <c r="UK49" s="13"/>
-      <c r="UL49" s="13"/>
-      <c r="UM49" s="13"/>
-      <c r="UN49" s="13"/>
-      <c r="UO49" s="13"/>
-      <c r="UP49" s="13"/>
-      <c r="UQ49" s="13"/>
-      <c r="UR49" s="13"/>
-      <c r="US49" s="13"/>
-      <c r="UT49" s="13"/>
-      <c r="UU49" s="13"/>
-      <c r="UV49" s="13"/>
-      <c r="UW49" s="13"/>
-      <c r="UX49" s="13"/>
-      <c r="UY49" s="13"/>
-      <c r="UZ49" s="13"/>
-      <c r="VA49" s="13"/>
-      <c r="VB49" s="13"/>
-      <c r="VC49" s="13"/>
-      <c r="VD49" s="13"/>
-      <c r="VE49" s="13"/>
-      <c r="VF49" s="13"/>
-      <c r="VG49" s="13"/>
-      <c r="VH49" s="13"/>
-      <c r="VI49" s="13"/>
-      <c r="VJ49" s="13"/>
-      <c r="VK49" s="13"/>
-      <c r="VL49" s="13"/>
-      <c r="VM49" s="13"/>
-      <c r="VN49" s="13"/>
-      <c r="VO49" s="13"/>
-      <c r="VP49" s="13"/>
-      <c r="VQ49" s="13"/>
-      <c r="VR49" s="13"/>
-      <c r="VS49" s="13"/>
-      <c r="VT49" s="13"/>
-      <c r="VU49" s="13"/>
-      <c r="VV49" s="13"/>
-      <c r="VW49" s="13"/>
-      <c r="VX49" s="13"/>
-      <c r="VY49" s="13"/>
-      <c r="VZ49" s="13"/>
-      <c r="WA49" s="13"/>
-      <c r="WB49" s="13"/>
-      <c r="WC49" s="13"/>
-      <c r="WD49" s="13"/>
-      <c r="WE49" s="13"/>
-      <c r="WF49" s="13"/>
-      <c r="WG49" s="13"/>
-      <c r="WH49" s="13"/>
-      <c r="WI49" s="13"/>
-      <c r="WJ49" s="13"/>
-      <c r="WK49" s="13"/>
-      <c r="WL49" s="13"/>
-      <c r="WM49" s="13"/>
-      <c r="WN49" s="13"/>
-      <c r="WO49" s="13"/>
-      <c r="WP49" s="13"/>
-      <c r="WQ49" s="13"/>
-      <c r="WR49" s="13"/>
-      <c r="WS49" s="13"/>
-      <c r="WT49" s="13"/>
-      <c r="WU49" s="13"/>
-      <c r="WV49" s="13"/>
-      <c r="WW49" s="13"/>
-      <c r="WX49" s="13"/>
-      <c r="WY49" s="13"/>
-      <c r="WZ49" s="13"/>
-      <c r="XA49" s="13"/>
-      <c r="XB49" s="13"/>
-      <c r="XC49" s="13"/>
-      <c r="XD49" s="13"/>
-      <c r="XE49" s="13"/>
-      <c r="XF49" s="13"/>
-      <c r="XG49" s="13"/>
-      <c r="XH49" s="13"/>
-      <c r="XI49" s="13"/>
-      <c r="XJ49" s="13"/>
-      <c r="XK49" s="13"/>
-      <c r="XL49" s="13"/>
-      <c r="XM49" s="13"/>
-      <c r="XN49" s="13"/>
-      <c r="XO49" s="13"/>
-      <c r="XP49" s="13"/>
-      <c r="XQ49" s="13"/>
-      <c r="XR49" s="13"/>
-      <c r="XS49" s="13"/>
-      <c r="XT49" s="13"/>
-      <c r="XU49" s="13"/>
-      <c r="XV49" s="13"/>
-      <c r="XW49" s="13"/>
-      <c r="XX49" s="13"/>
-      <c r="XY49" s="13"/>
-      <c r="XZ49" s="13"/>
-      <c r="YA49" s="13"/>
-      <c r="YB49" s="13"/>
-      <c r="YC49" s="13"/>
-      <c r="YD49" s="13"/>
-      <c r="YE49" s="13"/>
-      <c r="YF49" s="13"/>
-      <c r="YG49" s="13"/>
-      <c r="YH49" s="13"/>
-      <c r="YI49" s="13"/>
-      <c r="YJ49" s="13"/>
-      <c r="YK49" s="13"/>
-      <c r="YL49" s="13"/>
-      <c r="YM49" s="13"/>
-      <c r="YN49" s="13"/>
-      <c r="YO49" s="13"/>
-      <c r="YP49" s="13"/>
-      <c r="YQ49" s="13"/>
-      <c r="YR49" s="13"/>
-      <c r="YS49" s="13"/>
-      <c r="YT49" s="13"/>
-      <c r="YU49" s="13"/>
-      <c r="YV49" s="13"/>
-      <c r="YW49" s="13"/>
-      <c r="YX49" s="13"/>
-      <c r="YY49" s="13"/>
-      <c r="YZ49" s="13"/>
-      <c r="ZA49" s="13"/>
-      <c r="ZB49" s="13"/>
-      <c r="ZC49" s="13"/>
-      <c r="ZD49" s="13"/>
-      <c r="ZE49" s="13"/>
-      <c r="ZF49" s="13"/>
-      <c r="ZG49" s="13"/>
-      <c r="ZH49" s="13"/>
-      <c r="ZI49" s="13"/>
-      <c r="ZJ49" s="13"/>
-      <c r="ZK49" s="13"/>
-      <c r="ZL49" s="13"/>
-      <c r="ZM49" s="13"/>
-      <c r="ZN49" s="13"/>
-      <c r="ZO49" s="13"/>
-      <c r="ZP49" s="13"/>
-      <c r="ZQ49" s="13"/>
-      <c r="ZR49" s="13"/>
-      <c r="ZS49" s="13"/>
-      <c r="ZT49" s="13"/>
-      <c r="ZU49" s="13"/>
-      <c r="ZV49" s="13"/>
-      <c r="ZW49" s="13"/>
-      <c r="ZX49" s="13"/>
-      <c r="ZY49" s="13"/>
-      <c r="ZZ49" s="13"/>
-      <c r="AAA49" s="13"/>
-      <c r="AAB49" s="13"/>
-      <c r="AAC49" s="13"/>
-      <c r="AAD49" s="13"/>
-      <c r="AAE49" s="13"/>
-      <c r="AAF49" s="13"/>
-      <c r="AAG49" s="13"/>
-      <c r="AAH49" s="13"/>
-      <c r="AAI49" s="13"/>
-      <c r="AAJ49" s="13"/>
-      <c r="AAK49" s="13"/>
-      <c r="AAL49" s="13"/>
-      <c r="AAM49" s="13"/>
-      <c r="AAN49" s="13"/>
-      <c r="AAO49" s="13"/>
-      <c r="AAP49" s="13"/>
-      <c r="AAQ49" s="13"/>
-      <c r="AAR49" s="13"/>
-      <c r="AAS49" s="13"/>
-      <c r="AAT49" s="13"/>
-      <c r="AAU49" s="13"/>
-      <c r="AAV49" s="13"/>
-      <c r="AAW49" s="13"/>
-      <c r="AAX49" s="13"/>
-      <c r="AAY49" s="13"/>
-      <c r="AAZ49" s="13"/>
-      <c r="ABA49" s="13"/>
-      <c r="ABB49" s="13"/>
-      <c r="ABC49" s="13"/>
-      <c r="ABD49" s="13"/>
-      <c r="ABE49" s="13"/>
-      <c r="ABF49" s="13"/>
-      <c r="ABG49" s="13"/>
-      <c r="ABH49" s="13"/>
-      <c r="ABI49" s="13"/>
-      <c r="ABJ49" s="13"/>
-      <c r="ABK49" s="13"/>
-      <c r="ABL49" s="13"/>
-      <c r="ABM49" s="13"/>
-      <c r="ABN49" s="13"/>
-      <c r="ABO49" s="13"/>
-      <c r="ABP49" s="13"/>
-      <c r="ABQ49" s="13"/>
-      <c r="ABR49" s="13"/>
-      <c r="ABS49" s="13"/>
-      <c r="ABT49" s="13"/>
-      <c r="ABU49" s="13"/>
-      <c r="ABV49" s="13"/>
-      <c r="ABW49" s="13"/>
-      <c r="ABX49" s="13"/>
-      <c r="ABY49" s="13"/>
-      <c r="ABZ49" s="13"/>
-      <c r="ACA49" s="13"/>
-      <c r="ACB49" s="13"/>
-      <c r="ACC49" s="13"/>
-      <c r="ACD49" s="13"/>
-      <c r="ACE49" s="13"/>
-      <c r="ACF49" s="13"/>
-      <c r="ACG49" s="13"/>
-      <c r="ACH49" s="13"/>
-      <c r="ACI49" s="13"/>
-      <c r="ACJ49" s="13"/>
-      <c r="ACK49" s="13"/>
-      <c r="ACL49" s="13"/>
-      <c r="ACM49" s="13"/>
-      <c r="ACN49" s="13"/>
-      <c r="ACO49" s="13"/>
-      <c r="ACP49" s="13"/>
-      <c r="ACQ49" s="13"/>
-      <c r="ACR49" s="13"/>
-      <c r="ACS49" s="13"/>
-      <c r="ACT49" s="13"/>
-      <c r="ACU49" s="13"/>
-      <c r="ACV49" s="13"/>
-      <c r="ACW49" s="13"/>
-      <c r="ACX49" s="13"/>
-      <c r="ACY49" s="13"/>
-      <c r="ACZ49" s="13"/>
-      <c r="ADA49" s="13"/>
-      <c r="ADB49" s="13"/>
-      <c r="ADC49" s="13"/>
-      <c r="ADD49" s="13"/>
-      <c r="ADE49" s="13"/>
-      <c r="ADF49" s="13"/>
-      <c r="ADG49" s="13"/>
-      <c r="ADH49" s="13"/>
-      <c r="ADI49" s="13"/>
-      <c r="ADJ49" s="13"/>
-      <c r="ADK49" s="13"/>
-      <c r="ADL49" s="13"/>
-      <c r="ADM49" s="13"/>
-      <c r="ADN49" s="13"/>
-      <c r="ADO49" s="13"/>
-      <c r="ADP49" s="13"/>
-      <c r="ADQ49" s="13"/>
-      <c r="ADR49" s="13"/>
-      <c r="ADS49" s="13"/>
-      <c r="ADT49" s="13"/>
-      <c r="ADU49" s="13"/>
-      <c r="ADV49" s="13"/>
-      <c r="ADW49" s="13"/>
-      <c r="ADX49" s="13"/>
-      <c r="ADY49" s="13"/>
-      <c r="ADZ49" s="13"/>
-      <c r="AEA49" s="13"/>
-      <c r="AEB49" s="13"/>
-      <c r="AEC49" s="13"/>
-      <c r="AED49" s="13"/>
-      <c r="AEE49" s="13"/>
-      <c r="AEF49" s="13"/>
-      <c r="AEG49" s="13"/>
-      <c r="AEH49" s="13"/>
-      <c r="AEI49" s="13"/>
-      <c r="AEJ49" s="13"/>
-      <c r="AEK49" s="13"/>
-      <c r="AEL49" s="13"/>
-      <c r="AEM49" s="13"/>
-      <c r="AEN49" s="13"/>
-      <c r="AEO49" s="13"/>
-      <c r="AEP49" s="13"/>
-      <c r="AEQ49" s="13"/>
-      <c r="AER49" s="13"/>
-      <c r="AES49" s="13"/>
-      <c r="AET49" s="13"/>
-      <c r="AEU49" s="13"/>
-      <c r="AEV49" s="13"/>
-      <c r="AEW49" s="13"/>
-      <c r="AEX49" s="13"/>
-      <c r="AEY49" s="13"/>
-      <c r="AEZ49" s="13"/>
-      <c r="AFA49" s="13"/>
-      <c r="AFB49" s="13"/>
-      <c r="AFC49" s="13"/>
-      <c r="AFD49" s="13"/>
-      <c r="AFE49" s="13"/>
-      <c r="AFF49" s="13"/>
-      <c r="AFG49" s="13"/>
-      <c r="AFH49" s="13"/>
-      <c r="AFI49" s="13"/>
-      <c r="AFJ49" s="13"/>
-      <c r="AFK49" s="13"/>
-      <c r="AFL49" s="13"/>
-      <c r="AFM49" s="13"/>
-      <c r="AFN49" s="13"/>
-      <c r="AFO49" s="13"/>
-      <c r="AFP49" s="13"/>
-      <c r="AFQ49" s="13"/>
-      <c r="AFR49" s="13"/>
-      <c r="AFS49" s="13"/>
-      <c r="AFT49" s="13"/>
-      <c r="AFU49" s="13"/>
-      <c r="AFV49" s="13"/>
-      <c r="AFW49" s="13"/>
-      <c r="AFX49" s="13"/>
-      <c r="AFY49" s="13"/>
-      <c r="AFZ49" s="13"/>
-      <c r="AGA49" s="13"/>
-      <c r="AGB49" s="13"/>
-      <c r="AGC49" s="13"/>
-      <c r="AGD49" s="13"/>
-      <c r="AGE49" s="13"/>
-      <c r="AGF49" s="13"/>
-      <c r="AGG49" s="13"/>
-      <c r="AGH49" s="13"/>
-      <c r="AGI49" s="13"/>
-      <c r="AGJ49" s="13"/>
-      <c r="AGK49" s="13"/>
-      <c r="AGL49" s="13"/>
-      <c r="AGM49" s="13"/>
-      <c r="AGN49" s="13"/>
-      <c r="AGO49" s="13"/>
-      <c r="AGP49" s="13"/>
-      <c r="AGQ49" s="13"/>
-      <c r="AGR49" s="13"/>
-      <c r="AGS49" s="13"/>
-      <c r="AGT49" s="13"/>
-      <c r="AGU49" s="13"/>
-      <c r="AGV49" s="13"/>
-      <c r="AGW49" s="13"/>
-      <c r="AGX49" s="13"/>
-      <c r="AGY49" s="13"/>
-      <c r="AGZ49" s="13"/>
-      <c r="AHA49" s="13"/>
-      <c r="AHB49" s="13"/>
-      <c r="AHC49" s="13"/>
-      <c r="AHD49" s="13"/>
-      <c r="AHE49" s="13"/>
-      <c r="AHF49" s="13"/>
-      <c r="AHG49" s="13"/>
-      <c r="AHH49" s="13"/>
-      <c r="AHI49" s="13"/>
-      <c r="AHJ49" s="13"/>
-      <c r="AHK49" s="13"/>
-      <c r="AHL49" s="13"/>
-      <c r="AHM49" s="13"/>
-      <c r="AHN49" s="13"/>
-      <c r="AHO49" s="13"/>
-      <c r="AHP49" s="13"/>
-      <c r="AHQ49" s="13"/>
-      <c r="AHR49" s="13"/>
-      <c r="AHS49" s="13"/>
-      <c r="AHT49" s="13"/>
-      <c r="AHU49" s="13"/>
-      <c r="AHV49" s="13"/>
-      <c r="AHW49" s="13"/>
-      <c r="AHX49" s="13"/>
-      <c r="AHY49" s="13"/>
-      <c r="AHZ49" s="13"/>
-      <c r="AIA49" s="13"/>
-      <c r="AIB49" s="13"/>
-      <c r="AIC49" s="13"/>
-      <c r="AID49" s="13"/>
-      <c r="AIE49" s="13"/>
-      <c r="AIF49" s="13"/>
-      <c r="AIG49" s="13"/>
-      <c r="AIH49" s="13"/>
-      <c r="AII49" s="13"/>
-      <c r="AIJ49" s="13"/>
-      <c r="AIK49" s="13"/>
-      <c r="AIL49" s="13"/>
-      <c r="AIM49" s="13"/>
-      <c r="AIN49" s="13"/>
-      <c r="AIO49" s="13"/>
-      <c r="AIP49" s="13"/>
-      <c r="AIQ49" s="13"/>
-      <c r="AIR49" s="13"/>
-      <c r="AIS49" s="13"/>
-      <c r="AIT49" s="13"/>
-      <c r="AIU49" s="13"/>
-      <c r="AIV49" s="13"/>
-      <c r="AIW49" s="13"/>
-      <c r="AIX49" s="13"/>
-      <c r="AIY49" s="13"/>
-      <c r="AIZ49" s="13"/>
-      <c r="AJA49" s="13"/>
-      <c r="AJB49" s="13"/>
-      <c r="AJC49" s="13"/>
-      <c r="AJD49" s="13"/>
-      <c r="AJE49" s="13"/>
-      <c r="AJF49" s="13"/>
-      <c r="AJG49" s="13"/>
-      <c r="AJH49" s="13"/>
-      <c r="AJI49" s="13"/>
-      <c r="AJJ49" s="13"/>
-      <c r="AJK49" s="13"/>
-      <c r="AJL49" s="13"/>
-      <c r="AJM49" s="13"/>
-      <c r="AJN49" s="13"/>
-      <c r="AJO49" s="13"/>
-      <c r="AJP49" s="13"/>
-      <c r="AJQ49" s="13"/>
-      <c r="AJR49" s="13"/>
-      <c r="AJS49" s="13"/>
-      <c r="AJT49" s="13"/>
-      <c r="AJU49" s="13"/>
-      <c r="AJV49" s="13"/>
-      <c r="AJW49" s="13"/>
-      <c r="AJX49" s="13"/>
-      <c r="AJY49" s="13"/>
-      <c r="AJZ49" s="13"/>
-      <c r="AKA49" s="13"/>
-      <c r="AKB49" s="13"/>
-      <c r="AKC49" s="13"/>
-      <c r="AKD49" s="13"/>
-      <c r="AKE49" s="13"/>
-      <c r="AKF49" s="13"/>
-      <c r="AKG49" s="13"/>
-      <c r="AKH49" s="13"/>
-      <c r="AKI49" s="13"/>
-      <c r="AKJ49" s="13"/>
-      <c r="AKK49" s="13"/>
-      <c r="AKL49" s="13"/>
-      <c r="AKM49" s="13"/>
-      <c r="AKN49" s="13"/>
-      <c r="AKO49" s="13"/>
-      <c r="AKP49" s="13"/>
-      <c r="AKQ49" s="13"/>
-      <c r="AKR49" s="13"/>
-      <c r="AKS49" s="13"/>
-      <c r="AKT49" s="13"/>
-      <c r="AKU49" s="13"/>
-      <c r="AKV49" s="13"/>
-      <c r="AKW49" s="13"/>
-      <c r="AKX49" s="13"/>
-      <c r="AKY49" s="13"/>
-      <c r="AKZ49" s="13"/>
-      <c r="ALA49" s="13"/>
-      <c r="ALB49" s="13"/>
-      <c r="ALC49" s="13"/>
-      <c r="ALD49" s="13"/>
-      <c r="ALE49" s="13"/>
-      <c r="ALF49" s="13"/>
-      <c r="ALG49" s="13"/>
-      <c r="ALH49" s="13"/>
-      <c r="ALI49" s="13"/>
-      <c r="ALJ49" s="13"/>
-      <c r="ALK49" s="13"/>
-      <c r="ALL49" s="13"/>
-      <c r="ALM49" s="13"/>
-      <c r="ALN49" s="13"/>
-      <c r="ALO49" s="13"/>
-      <c r="ALP49" s="13"/>
-      <c r="ALQ49" s="13"/>
-      <c r="ALR49" s="13"/>
-      <c r="ALS49" s="13"/>
-      <c r="ALT49" s="13"/>
-      <c r="ALU49" s="13"/>
-      <c r="ALV49" s="13"/>
-      <c r="ALW49" s="13"/>
-      <c r="ALX49" s="13"/>
-      <c r="ALY49" s="13"/>
-      <c r="ALZ49" s="13"/>
-      <c r="AMA49" s="13"/>
-      <c r="AMB49" s="13"/>
-      <c r="AMC49" s="13"/>
-      <c r="AMD49" s="13"/>
-      <c r="AME49" s="13"/>
-      <c r="AMF49" s="13"/>
-      <c r="AMG49" s="13"/>
-      <c r="AMH49" s="13"/>
-      <c r="AMI49" s="13"/>
-      <c r="AMJ49" s="13"/>
-    </row>
-    <row r="50" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>3</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="17"/>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
       <c r="K50" s="13"/>
@@ -45232,88 +44210,1126 @@
       <c r="AMI50" s="13"/>
       <c r="AMJ50" s="13"/>
     </row>
-    <row r="51" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H51" s="17"/>
+    <row r="51" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="13"/>
+      <c r="Z51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="13"/>
+      <c r="AD51" s="13"/>
+      <c r="AE51" s="13"/>
+      <c r="AF51" s="13"/>
+      <c r="AG51" s="13"/>
+      <c r="AH51" s="13"/>
+      <c r="AI51" s="13"/>
+      <c r="AJ51" s="13"/>
+      <c r="AK51" s="13"/>
+      <c r="AL51" s="13"/>
+      <c r="AM51" s="13"/>
+      <c r="AN51" s="13"/>
+      <c r="AO51" s="13"/>
+      <c r="AP51" s="13"/>
+      <c r="AQ51" s="13"/>
+      <c r="AR51" s="13"/>
+      <c r="AS51" s="13"/>
+      <c r="AT51" s="13"/>
+      <c r="AU51" s="13"/>
+      <c r="AV51" s="13"/>
+      <c r="AW51" s="13"/>
+      <c r="AX51" s="13"/>
+      <c r="AY51" s="13"/>
+      <c r="AZ51" s="13"/>
+      <c r="BA51" s="13"/>
+      <c r="BB51" s="13"/>
+      <c r="BC51" s="13"/>
+      <c r="BD51" s="13"/>
+      <c r="BE51" s="13"/>
+      <c r="BF51" s="13"/>
+      <c r="BG51" s="13"/>
+      <c r="BH51" s="13"/>
+      <c r="BI51" s="13"/>
+      <c r="BJ51" s="13"/>
+      <c r="BK51" s="13"/>
+      <c r="BL51" s="13"/>
+      <c r="BM51" s="13"/>
+      <c r="BN51" s="13"/>
+      <c r="BO51" s="13"/>
+      <c r="BP51" s="13"/>
+      <c r="BQ51" s="13"/>
+      <c r="BR51" s="13"/>
+      <c r="BS51" s="13"/>
+      <c r="BT51" s="13"/>
+      <c r="BU51" s="13"/>
+      <c r="BV51" s="13"/>
+      <c r="BW51" s="13"/>
+      <c r="BX51" s="13"/>
+      <c r="BY51" s="13"/>
+      <c r="BZ51" s="13"/>
+      <c r="CA51" s="13"/>
+      <c r="CB51" s="13"/>
+      <c r="CC51" s="13"/>
+      <c r="CD51" s="13"/>
+      <c r="CE51" s="13"/>
+      <c r="CF51" s="13"/>
+      <c r="CG51" s="13"/>
+      <c r="CH51" s="13"/>
+      <c r="CI51" s="13"/>
+      <c r="CJ51" s="13"/>
+      <c r="CK51" s="13"/>
+      <c r="CL51" s="13"/>
+      <c r="CM51" s="13"/>
+      <c r="CN51" s="13"/>
+      <c r="CO51" s="13"/>
+      <c r="CP51" s="13"/>
+      <c r="CQ51" s="13"/>
+      <c r="CR51" s="13"/>
+      <c r="CS51" s="13"/>
+      <c r="CT51" s="13"/>
+      <c r="CU51" s="13"/>
+      <c r="CV51" s="13"/>
+      <c r="CW51" s="13"/>
+      <c r="CX51" s="13"/>
+      <c r="CY51" s="13"/>
+      <c r="CZ51" s="13"/>
+      <c r="DA51" s="13"/>
+      <c r="DB51" s="13"/>
+      <c r="DC51" s="13"/>
+      <c r="DD51" s="13"/>
+      <c r="DE51" s="13"/>
+      <c r="DF51" s="13"/>
+      <c r="DG51" s="13"/>
+      <c r="DH51" s="13"/>
+      <c r="DI51" s="13"/>
+      <c r="DJ51" s="13"/>
+      <c r="DK51" s="13"/>
+      <c r="DL51" s="13"/>
+      <c r="DM51" s="13"/>
+      <c r="DN51" s="13"/>
+      <c r="DO51" s="13"/>
+      <c r="DP51" s="13"/>
+      <c r="DQ51" s="13"/>
+      <c r="DR51" s="13"/>
+      <c r="DS51" s="13"/>
+      <c r="DT51" s="13"/>
+      <c r="DU51" s="13"/>
+      <c r="DV51" s="13"/>
+      <c r="DW51" s="13"/>
+      <c r="DX51" s="13"/>
+      <c r="DY51" s="13"/>
+      <c r="DZ51" s="13"/>
+      <c r="EA51" s="13"/>
+      <c r="EB51" s="13"/>
+      <c r="EC51" s="13"/>
+      <c r="ED51" s="13"/>
+      <c r="EE51" s="13"/>
+      <c r="EF51" s="13"/>
+      <c r="EG51" s="13"/>
+      <c r="EH51" s="13"/>
+      <c r="EI51" s="13"/>
+      <c r="EJ51" s="13"/>
+      <c r="EK51" s="13"/>
+      <c r="EL51" s="13"/>
+      <c r="EM51" s="13"/>
+      <c r="EN51" s="13"/>
+      <c r="EO51" s="13"/>
+      <c r="EP51" s="13"/>
+      <c r="EQ51" s="13"/>
+      <c r="ER51" s="13"/>
+      <c r="ES51" s="13"/>
+      <c r="ET51" s="13"/>
+      <c r="EU51" s="13"/>
+      <c r="EV51" s="13"/>
+      <c r="EW51" s="13"/>
+      <c r="EX51" s="13"/>
+      <c r="EY51" s="13"/>
+      <c r="EZ51" s="13"/>
+      <c r="FA51" s="13"/>
+      <c r="FB51" s="13"/>
+      <c r="FC51" s="13"/>
+      <c r="FD51" s="13"/>
+      <c r="FE51" s="13"/>
+      <c r="FF51" s="13"/>
+      <c r="FG51" s="13"/>
+      <c r="FH51" s="13"/>
+      <c r="FI51" s="13"/>
+      <c r="FJ51" s="13"/>
+      <c r="FK51" s="13"/>
+      <c r="FL51" s="13"/>
+      <c r="FM51" s="13"/>
+      <c r="FN51" s="13"/>
+      <c r="FO51" s="13"/>
+      <c r="FP51" s="13"/>
+      <c r="FQ51" s="13"/>
+      <c r="FR51" s="13"/>
+      <c r="FS51" s="13"/>
+      <c r="FT51" s="13"/>
+      <c r="FU51" s="13"/>
+      <c r="FV51" s="13"/>
+      <c r="FW51" s="13"/>
+      <c r="FX51" s="13"/>
+      <c r="FY51" s="13"/>
+      <c r="FZ51" s="13"/>
+      <c r="GA51" s="13"/>
+      <c r="GB51" s="13"/>
+      <c r="GC51" s="13"/>
+      <c r="GD51" s="13"/>
+      <c r="GE51" s="13"/>
+      <c r="GF51" s="13"/>
+      <c r="GG51" s="13"/>
+      <c r="GH51" s="13"/>
+      <c r="GI51" s="13"/>
+      <c r="GJ51" s="13"/>
+      <c r="GK51" s="13"/>
+      <c r="GL51" s="13"/>
+      <c r="GM51" s="13"/>
+      <c r="GN51" s="13"/>
+      <c r="GO51" s="13"/>
+      <c r="GP51" s="13"/>
+      <c r="GQ51" s="13"/>
+      <c r="GR51" s="13"/>
+      <c r="GS51" s="13"/>
+      <c r="GT51" s="13"/>
+      <c r="GU51" s="13"/>
+      <c r="GV51" s="13"/>
+      <c r="GW51" s="13"/>
+      <c r="GX51" s="13"/>
+      <c r="GY51" s="13"/>
+      <c r="GZ51" s="13"/>
+      <c r="HA51" s="13"/>
+      <c r="HB51" s="13"/>
+      <c r="HC51" s="13"/>
+      <c r="HD51" s="13"/>
+      <c r="HE51" s="13"/>
+      <c r="HF51" s="13"/>
+      <c r="HG51" s="13"/>
+      <c r="HH51" s="13"/>
+      <c r="HI51" s="13"/>
+      <c r="HJ51" s="13"/>
+      <c r="HK51" s="13"/>
+      <c r="HL51" s="13"/>
+      <c r="HM51" s="13"/>
+      <c r="HN51" s="13"/>
+      <c r="HO51" s="13"/>
+      <c r="HP51" s="13"/>
+      <c r="HQ51" s="13"/>
+      <c r="HR51" s="13"/>
+      <c r="HS51" s="13"/>
+      <c r="HT51" s="13"/>
+      <c r="HU51" s="13"/>
+      <c r="HV51" s="13"/>
+      <c r="HW51" s="13"/>
+      <c r="HX51" s="13"/>
+      <c r="HY51" s="13"/>
+      <c r="HZ51" s="13"/>
+      <c r="IA51" s="13"/>
+      <c r="IB51" s="13"/>
+      <c r="IC51" s="13"/>
+      <c r="ID51" s="13"/>
+      <c r="IE51" s="13"/>
+      <c r="IF51" s="13"/>
+      <c r="IG51" s="13"/>
+      <c r="IH51" s="13"/>
+      <c r="II51" s="13"/>
+      <c r="IJ51" s="13"/>
+      <c r="IK51" s="13"/>
+      <c r="IL51" s="13"/>
+      <c r="IM51" s="13"/>
+      <c r="IN51" s="13"/>
+      <c r="IO51" s="13"/>
+      <c r="IP51" s="13"/>
+      <c r="IQ51" s="13"/>
+      <c r="IR51" s="13"/>
+      <c r="IS51" s="13"/>
+      <c r="IT51" s="13"/>
+      <c r="IU51" s="13"/>
+      <c r="IV51" s="13"/>
+      <c r="IW51" s="13"/>
+      <c r="IX51" s="13"/>
+      <c r="IY51" s="13"/>
+      <c r="IZ51" s="13"/>
+      <c r="JA51" s="13"/>
+      <c r="JB51" s="13"/>
+      <c r="JC51" s="13"/>
+      <c r="JD51" s="13"/>
+      <c r="JE51" s="13"/>
+      <c r="JF51" s="13"/>
+      <c r="JG51" s="13"/>
+      <c r="JH51" s="13"/>
+      <c r="JI51" s="13"/>
+      <c r="JJ51" s="13"/>
+      <c r="JK51" s="13"/>
+      <c r="JL51" s="13"/>
+      <c r="JM51" s="13"/>
+      <c r="JN51" s="13"/>
+      <c r="JO51" s="13"/>
+      <c r="JP51" s="13"/>
+      <c r="JQ51" s="13"/>
+      <c r="JR51" s="13"/>
+      <c r="JS51" s="13"/>
+      <c r="JT51" s="13"/>
+      <c r="JU51" s="13"/>
+      <c r="JV51" s="13"/>
+      <c r="JW51" s="13"/>
+      <c r="JX51" s="13"/>
+      <c r="JY51" s="13"/>
+      <c r="JZ51" s="13"/>
+      <c r="KA51" s="13"/>
+      <c r="KB51" s="13"/>
+      <c r="KC51" s="13"/>
+      <c r="KD51" s="13"/>
+      <c r="KE51" s="13"/>
+      <c r="KF51" s="13"/>
+      <c r="KG51" s="13"/>
+      <c r="KH51" s="13"/>
+      <c r="KI51" s="13"/>
+      <c r="KJ51" s="13"/>
+      <c r="KK51" s="13"/>
+      <c r="KL51" s="13"/>
+      <c r="KM51" s="13"/>
+      <c r="KN51" s="13"/>
+      <c r="KO51" s="13"/>
+      <c r="KP51" s="13"/>
+      <c r="KQ51" s="13"/>
+      <c r="KR51" s="13"/>
+      <c r="KS51" s="13"/>
+      <c r="KT51" s="13"/>
+      <c r="KU51" s="13"/>
+      <c r="KV51" s="13"/>
+      <c r="KW51" s="13"/>
+      <c r="KX51" s="13"/>
+      <c r="KY51" s="13"/>
+      <c r="KZ51" s="13"/>
+      <c r="LA51" s="13"/>
+      <c r="LB51" s="13"/>
+      <c r="LC51" s="13"/>
+      <c r="LD51" s="13"/>
+      <c r="LE51" s="13"/>
+      <c r="LF51" s="13"/>
+      <c r="LG51" s="13"/>
+      <c r="LH51" s="13"/>
+      <c r="LI51" s="13"/>
+      <c r="LJ51" s="13"/>
+      <c r="LK51" s="13"/>
+      <c r="LL51" s="13"/>
+      <c r="LM51" s="13"/>
+      <c r="LN51" s="13"/>
+      <c r="LO51" s="13"/>
+      <c r="LP51" s="13"/>
+      <c r="LQ51" s="13"/>
+      <c r="LR51" s="13"/>
+      <c r="LS51" s="13"/>
+      <c r="LT51" s="13"/>
+      <c r="LU51" s="13"/>
+      <c r="LV51" s="13"/>
+      <c r="LW51" s="13"/>
+      <c r="LX51" s="13"/>
+      <c r="LY51" s="13"/>
+      <c r="LZ51" s="13"/>
+      <c r="MA51" s="13"/>
+      <c r="MB51" s="13"/>
+      <c r="MC51" s="13"/>
+      <c r="MD51" s="13"/>
+      <c r="ME51" s="13"/>
+      <c r="MF51" s="13"/>
+      <c r="MG51" s="13"/>
+      <c r="MH51" s="13"/>
+      <c r="MI51" s="13"/>
+      <c r="MJ51" s="13"/>
+      <c r="MK51" s="13"/>
+      <c r="ML51" s="13"/>
+      <c r="MM51" s="13"/>
+      <c r="MN51" s="13"/>
+      <c r="MO51" s="13"/>
+      <c r="MP51" s="13"/>
+      <c r="MQ51" s="13"/>
+      <c r="MR51" s="13"/>
+      <c r="MS51" s="13"/>
+      <c r="MT51" s="13"/>
+      <c r="MU51" s="13"/>
+      <c r="MV51" s="13"/>
+      <c r="MW51" s="13"/>
+      <c r="MX51" s="13"/>
+      <c r="MY51" s="13"/>
+      <c r="MZ51" s="13"/>
+      <c r="NA51" s="13"/>
+      <c r="NB51" s="13"/>
+      <c r="NC51" s="13"/>
+      <c r="ND51" s="13"/>
+      <c r="NE51" s="13"/>
+      <c r="NF51" s="13"/>
+      <c r="NG51" s="13"/>
+      <c r="NH51" s="13"/>
+      <c r="NI51" s="13"/>
+      <c r="NJ51" s="13"/>
+      <c r="NK51" s="13"/>
+      <c r="NL51" s="13"/>
+      <c r="NM51" s="13"/>
+      <c r="NN51" s="13"/>
+      <c r="NO51" s="13"/>
+      <c r="NP51" s="13"/>
+      <c r="NQ51" s="13"/>
+      <c r="NR51" s="13"/>
+      <c r="NS51" s="13"/>
+      <c r="NT51" s="13"/>
+      <c r="NU51" s="13"/>
+      <c r="NV51" s="13"/>
+      <c r="NW51" s="13"/>
+      <c r="NX51" s="13"/>
+      <c r="NY51" s="13"/>
+      <c r="NZ51" s="13"/>
+      <c r="OA51" s="13"/>
+      <c r="OB51" s="13"/>
+      <c r="OC51" s="13"/>
+      <c r="OD51" s="13"/>
+      <c r="OE51" s="13"/>
+      <c r="OF51" s="13"/>
+      <c r="OG51" s="13"/>
+      <c r="OH51" s="13"/>
+      <c r="OI51" s="13"/>
+      <c r="OJ51" s="13"/>
+      <c r="OK51" s="13"/>
+      <c r="OL51" s="13"/>
+      <c r="OM51" s="13"/>
+      <c r="ON51" s="13"/>
+      <c r="OO51" s="13"/>
+      <c r="OP51" s="13"/>
+      <c r="OQ51" s="13"/>
+      <c r="OR51" s="13"/>
+      <c r="OS51" s="13"/>
+      <c r="OT51" s="13"/>
+      <c r="OU51" s="13"/>
+      <c r="OV51" s="13"/>
+      <c r="OW51" s="13"/>
+      <c r="OX51" s="13"/>
+      <c r="OY51" s="13"/>
+      <c r="OZ51" s="13"/>
+      <c r="PA51" s="13"/>
+      <c r="PB51" s="13"/>
+      <c r="PC51" s="13"/>
+      <c r="PD51" s="13"/>
+      <c r="PE51" s="13"/>
+      <c r="PF51" s="13"/>
+      <c r="PG51" s="13"/>
+      <c r="PH51" s="13"/>
+      <c r="PI51" s="13"/>
+      <c r="PJ51" s="13"/>
+      <c r="PK51" s="13"/>
+      <c r="PL51" s="13"/>
+      <c r="PM51" s="13"/>
+      <c r="PN51" s="13"/>
+      <c r="PO51" s="13"/>
+      <c r="PP51" s="13"/>
+      <c r="PQ51" s="13"/>
+      <c r="PR51" s="13"/>
+      <c r="PS51" s="13"/>
+      <c r="PT51" s="13"/>
+      <c r="PU51" s="13"/>
+      <c r="PV51" s="13"/>
+      <c r="PW51" s="13"/>
+      <c r="PX51" s="13"/>
+      <c r="PY51" s="13"/>
+      <c r="PZ51" s="13"/>
+      <c r="QA51" s="13"/>
+      <c r="QB51" s="13"/>
+      <c r="QC51" s="13"/>
+      <c r="QD51" s="13"/>
+      <c r="QE51" s="13"/>
+      <c r="QF51" s="13"/>
+      <c r="QG51" s="13"/>
+      <c r="QH51" s="13"/>
+      <c r="QI51" s="13"/>
+      <c r="QJ51" s="13"/>
+      <c r="QK51" s="13"/>
+      <c r="QL51" s="13"/>
+      <c r="QM51" s="13"/>
+      <c r="QN51" s="13"/>
+      <c r="QO51" s="13"/>
+      <c r="QP51" s="13"/>
+      <c r="QQ51" s="13"/>
+      <c r="QR51" s="13"/>
+      <c r="QS51" s="13"/>
+      <c r="QT51" s="13"/>
+      <c r="QU51" s="13"/>
+      <c r="QV51" s="13"/>
+      <c r="QW51" s="13"/>
+      <c r="QX51" s="13"/>
+      <c r="QY51" s="13"/>
+      <c r="QZ51" s="13"/>
+      <c r="RA51" s="13"/>
+      <c r="RB51" s="13"/>
+      <c r="RC51" s="13"/>
+      <c r="RD51" s="13"/>
+      <c r="RE51" s="13"/>
+      <c r="RF51" s="13"/>
+      <c r="RG51" s="13"/>
+      <c r="RH51" s="13"/>
+      <c r="RI51" s="13"/>
+      <c r="RJ51" s="13"/>
+      <c r="RK51" s="13"/>
+      <c r="RL51" s="13"/>
+      <c r="RM51" s="13"/>
+      <c r="RN51" s="13"/>
+      <c r="RO51" s="13"/>
+      <c r="RP51" s="13"/>
+      <c r="RQ51" s="13"/>
+      <c r="RR51" s="13"/>
+      <c r="RS51" s="13"/>
+      <c r="RT51" s="13"/>
+      <c r="RU51" s="13"/>
+      <c r="RV51" s="13"/>
+      <c r="RW51" s="13"/>
+      <c r="RX51" s="13"/>
+      <c r="RY51" s="13"/>
+      <c r="RZ51" s="13"/>
+      <c r="SA51" s="13"/>
+      <c r="SB51" s="13"/>
+      <c r="SC51" s="13"/>
+      <c r="SD51" s="13"/>
+      <c r="SE51" s="13"/>
+      <c r="SF51" s="13"/>
+      <c r="SG51" s="13"/>
+      <c r="SH51" s="13"/>
+      <c r="SI51" s="13"/>
+      <c r="SJ51" s="13"/>
+      <c r="SK51" s="13"/>
+      <c r="SL51" s="13"/>
+      <c r="SM51" s="13"/>
+      <c r="SN51" s="13"/>
+      <c r="SO51" s="13"/>
+      <c r="SP51" s="13"/>
+      <c r="SQ51" s="13"/>
+      <c r="SR51" s="13"/>
+      <c r="SS51" s="13"/>
+      <c r="ST51" s="13"/>
+      <c r="SU51" s="13"/>
+      <c r="SV51" s="13"/>
+      <c r="SW51" s="13"/>
+      <c r="SX51" s="13"/>
+      <c r="SY51" s="13"/>
+      <c r="SZ51" s="13"/>
+      <c r="TA51" s="13"/>
+      <c r="TB51" s="13"/>
+      <c r="TC51" s="13"/>
+      <c r="TD51" s="13"/>
+      <c r="TE51" s="13"/>
+      <c r="TF51" s="13"/>
+      <c r="TG51" s="13"/>
+      <c r="TH51" s="13"/>
+      <c r="TI51" s="13"/>
+      <c r="TJ51" s="13"/>
+      <c r="TK51" s="13"/>
+      <c r="TL51" s="13"/>
+      <c r="TM51" s="13"/>
+      <c r="TN51" s="13"/>
+      <c r="TO51" s="13"/>
+      <c r="TP51" s="13"/>
+      <c r="TQ51" s="13"/>
+      <c r="TR51" s="13"/>
+      <c r="TS51" s="13"/>
+      <c r="TT51" s="13"/>
+      <c r="TU51" s="13"/>
+      <c r="TV51" s="13"/>
+      <c r="TW51" s="13"/>
+      <c r="TX51" s="13"/>
+      <c r="TY51" s="13"/>
+      <c r="TZ51" s="13"/>
+      <c r="UA51" s="13"/>
+      <c r="UB51" s="13"/>
+      <c r="UC51" s="13"/>
+      <c r="UD51" s="13"/>
+      <c r="UE51" s="13"/>
+      <c r="UF51" s="13"/>
+      <c r="UG51" s="13"/>
+      <c r="UH51" s="13"/>
+      <c r="UI51" s="13"/>
+      <c r="UJ51" s="13"/>
+      <c r="UK51" s="13"/>
+      <c r="UL51" s="13"/>
+      <c r="UM51" s="13"/>
+      <c r="UN51" s="13"/>
+      <c r="UO51" s="13"/>
+      <c r="UP51" s="13"/>
+      <c r="UQ51" s="13"/>
+      <c r="UR51" s="13"/>
+      <c r="US51" s="13"/>
+      <c r="UT51" s="13"/>
+      <c r="UU51" s="13"/>
+      <c r="UV51" s="13"/>
+      <c r="UW51" s="13"/>
+      <c r="UX51" s="13"/>
+      <c r="UY51" s="13"/>
+      <c r="UZ51" s="13"/>
+      <c r="VA51" s="13"/>
+      <c r="VB51" s="13"/>
+      <c r="VC51" s="13"/>
+      <c r="VD51" s="13"/>
+      <c r="VE51" s="13"/>
+      <c r="VF51" s="13"/>
+      <c r="VG51" s="13"/>
+      <c r="VH51" s="13"/>
+      <c r="VI51" s="13"/>
+      <c r="VJ51" s="13"/>
+      <c r="VK51" s="13"/>
+      <c r="VL51" s="13"/>
+      <c r="VM51" s="13"/>
+      <c r="VN51" s="13"/>
+      <c r="VO51" s="13"/>
+      <c r="VP51" s="13"/>
+      <c r="VQ51" s="13"/>
+      <c r="VR51" s="13"/>
+      <c r="VS51" s="13"/>
+      <c r="VT51" s="13"/>
+      <c r="VU51" s="13"/>
+      <c r="VV51" s="13"/>
+      <c r="VW51" s="13"/>
+      <c r="VX51" s="13"/>
+      <c r="VY51" s="13"/>
+      <c r="VZ51" s="13"/>
+      <c r="WA51" s="13"/>
+      <c r="WB51" s="13"/>
+      <c r="WC51" s="13"/>
+      <c r="WD51" s="13"/>
+      <c r="WE51" s="13"/>
+      <c r="WF51" s="13"/>
+      <c r="WG51" s="13"/>
+      <c r="WH51" s="13"/>
+      <c r="WI51" s="13"/>
+      <c r="WJ51" s="13"/>
+      <c r="WK51" s="13"/>
+      <c r="WL51" s="13"/>
+      <c r="WM51" s="13"/>
+      <c r="WN51" s="13"/>
+      <c r="WO51" s="13"/>
+      <c r="WP51" s="13"/>
+      <c r="WQ51" s="13"/>
+      <c r="WR51" s="13"/>
+      <c r="WS51" s="13"/>
+      <c r="WT51" s="13"/>
+      <c r="WU51" s="13"/>
+      <c r="WV51" s="13"/>
+      <c r="WW51" s="13"/>
+      <c r="WX51" s="13"/>
+      <c r="WY51" s="13"/>
+      <c r="WZ51" s="13"/>
+      <c r="XA51" s="13"/>
+      <c r="XB51" s="13"/>
+      <c r="XC51" s="13"/>
+      <c r="XD51" s="13"/>
+      <c r="XE51" s="13"/>
+      <c r="XF51" s="13"/>
+      <c r="XG51" s="13"/>
+      <c r="XH51" s="13"/>
+      <c r="XI51" s="13"/>
+      <c r="XJ51" s="13"/>
+      <c r="XK51" s="13"/>
+      <c r="XL51" s="13"/>
+      <c r="XM51" s="13"/>
+      <c r="XN51" s="13"/>
+      <c r="XO51" s="13"/>
+      <c r="XP51" s="13"/>
+      <c r="XQ51" s="13"/>
+      <c r="XR51" s="13"/>
+      <c r="XS51" s="13"/>
+      <c r="XT51" s="13"/>
+      <c r="XU51" s="13"/>
+      <c r="XV51" s="13"/>
+      <c r="XW51" s="13"/>
+      <c r="XX51" s="13"/>
+      <c r="XY51" s="13"/>
+      <c r="XZ51" s="13"/>
+      <c r="YA51" s="13"/>
+      <c r="YB51" s="13"/>
+      <c r="YC51" s="13"/>
+      <c r="YD51" s="13"/>
+      <c r="YE51" s="13"/>
+      <c r="YF51" s="13"/>
+      <c r="YG51" s="13"/>
+      <c r="YH51" s="13"/>
+      <c r="YI51" s="13"/>
+      <c r="YJ51" s="13"/>
+      <c r="YK51" s="13"/>
+      <c r="YL51" s="13"/>
+      <c r="YM51" s="13"/>
+      <c r="YN51" s="13"/>
+      <c r="YO51" s="13"/>
+      <c r="YP51" s="13"/>
+      <c r="YQ51" s="13"/>
+      <c r="YR51" s="13"/>
+      <c r="YS51" s="13"/>
+      <c r="YT51" s="13"/>
+      <c r="YU51" s="13"/>
+      <c r="YV51" s="13"/>
+      <c r="YW51" s="13"/>
+      <c r="YX51" s="13"/>
+      <c r="YY51" s="13"/>
+      <c r="YZ51" s="13"/>
+      <c r="ZA51" s="13"/>
+      <c r="ZB51" s="13"/>
+      <c r="ZC51" s="13"/>
+      <c r="ZD51" s="13"/>
+      <c r="ZE51" s="13"/>
+      <c r="ZF51" s="13"/>
+      <c r="ZG51" s="13"/>
+      <c r="ZH51" s="13"/>
+      <c r="ZI51" s="13"/>
+      <c r="ZJ51" s="13"/>
+      <c r="ZK51" s="13"/>
+      <c r="ZL51" s="13"/>
+      <c r="ZM51" s="13"/>
+      <c r="ZN51" s="13"/>
+      <c r="ZO51" s="13"/>
+      <c r="ZP51" s="13"/>
+      <c r="ZQ51" s="13"/>
+      <c r="ZR51" s="13"/>
+      <c r="ZS51" s="13"/>
+      <c r="ZT51" s="13"/>
+      <c r="ZU51" s="13"/>
+      <c r="ZV51" s="13"/>
+      <c r="ZW51" s="13"/>
+      <c r="ZX51" s="13"/>
+      <c r="ZY51" s="13"/>
+      <c r="ZZ51" s="13"/>
+      <c r="AAA51" s="13"/>
+      <c r="AAB51" s="13"/>
+      <c r="AAC51" s="13"/>
+      <c r="AAD51" s="13"/>
+      <c r="AAE51" s="13"/>
+      <c r="AAF51" s="13"/>
+      <c r="AAG51" s="13"/>
+      <c r="AAH51" s="13"/>
+      <c r="AAI51" s="13"/>
+      <c r="AAJ51" s="13"/>
+      <c r="AAK51" s="13"/>
+      <c r="AAL51" s="13"/>
+      <c r="AAM51" s="13"/>
+      <c r="AAN51" s="13"/>
+      <c r="AAO51" s="13"/>
+      <c r="AAP51" s="13"/>
+      <c r="AAQ51" s="13"/>
+      <c r="AAR51" s="13"/>
+      <c r="AAS51" s="13"/>
+      <c r="AAT51" s="13"/>
+      <c r="AAU51" s="13"/>
+      <c r="AAV51" s="13"/>
+      <c r="AAW51" s="13"/>
+      <c r="AAX51" s="13"/>
+      <c r="AAY51" s="13"/>
+      <c r="AAZ51" s="13"/>
+      <c r="ABA51" s="13"/>
+      <c r="ABB51" s="13"/>
+      <c r="ABC51" s="13"/>
+      <c r="ABD51" s="13"/>
+      <c r="ABE51" s="13"/>
+      <c r="ABF51" s="13"/>
+      <c r="ABG51" s="13"/>
+      <c r="ABH51" s="13"/>
+      <c r="ABI51" s="13"/>
+      <c r="ABJ51" s="13"/>
+      <c r="ABK51" s="13"/>
+      <c r="ABL51" s="13"/>
+      <c r="ABM51" s="13"/>
+      <c r="ABN51" s="13"/>
+      <c r="ABO51" s="13"/>
+      <c r="ABP51" s="13"/>
+      <c r="ABQ51" s="13"/>
+      <c r="ABR51" s="13"/>
+      <c r="ABS51" s="13"/>
+      <c r="ABT51" s="13"/>
+      <c r="ABU51" s="13"/>
+      <c r="ABV51" s="13"/>
+      <c r="ABW51" s="13"/>
+      <c r="ABX51" s="13"/>
+      <c r="ABY51" s="13"/>
+      <c r="ABZ51" s="13"/>
+      <c r="ACA51" s="13"/>
+      <c r="ACB51" s="13"/>
+      <c r="ACC51" s="13"/>
+      <c r="ACD51" s="13"/>
+      <c r="ACE51" s="13"/>
+      <c r="ACF51" s="13"/>
+      <c r="ACG51" s="13"/>
+      <c r="ACH51" s="13"/>
+      <c r="ACI51" s="13"/>
+      <c r="ACJ51" s="13"/>
+      <c r="ACK51" s="13"/>
+      <c r="ACL51" s="13"/>
+      <c r="ACM51" s="13"/>
+      <c r="ACN51" s="13"/>
+      <c r="ACO51" s="13"/>
+      <c r="ACP51" s="13"/>
+      <c r="ACQ51" s="13"/>
+      <c r="ACR51" s="13"/>
+      <c r="ACS51" s="13"/>
+      <c r="ACT51" s="13"/>
+      <c r="ACU51" s="13"/>
+      <c r="ACV51" s="13"/>
+      <c r="ACW51" s="13"/>
+      <c r="ACX51" s="13"/>
+      <c r="ACY51" s="13"/>
+      <c r="ACZ51" s="13"/>
+      <c r="ADA51" s="13"/>
+      <c r="ADB51" s="13"/>
+      <c r="ADC51" s="13"/>
+      <c r="ADD51" s="13"/>
+      <c r="ADE51" s="13"/>
+      <c r="ADF51" s="13"/>
+      <c r="ADG51" s="13"/>
+      <c r="ADH51" s="13"/>
+      <c r="ADI51" s="13"/>
+      <c r="ADJ51" s="13"/>
+      <c r="ADK51" s="13"/>
+      <c r="ADL51" s="13"/>
+      <c r="ADM51" s="13"/>
+      <c r="ADN51" s="13"/>
+      <c r="ADO51" s="13"/>
+      <c r="ADP51" s="13"/>
+      <c r="ADQ51" s="13"/>
+      <c r="ADR51" s="13"/>
+      <c r="ADS51" s="13"/>
+      <c r="ADT51" s="13"/>
+      <c r="ADU51" s="13"/>
+      <c r="ADV51" s="13"/>
+      <c r="ADW51" s="13"/>
+      <c r="ADX51" s="13"/>
+      <c r="ADY51" s="13"/>
+      <c r="ADZ51" s="13"/>
+      <c r="AEA51" s="13"/>
+      <c r="AEB51" s="13"/>
+      <c r="AEC51" s="13"/>
+      <c r="AED51" s="13"/>
+      <c r="AEE51" s="13"/>
+      <c r="AEF51" s="13"/>
+      <c r="AEG51" s="13"/>
+      <c r="AEH51" s="13"/>
+      <c r="AEI51" s="13"/>
+      <c r="AEJ51" s="13"/>
+      <c r="AEK51" s="13"/>
+      <c r="AEL51" s="13"/>
+      <c r="AEM51" s="13"/>
+      <c r="AEN51" s="13"/>
+      <c r="AEO51" s="13"/>
+      <c r="AEP51" s="13"/>
+      <c r="AEQ51" s="13"/>
+      <c r="AER51" s="13"/>
+      <c r="AES51" s="13"/>
+      <c r="AET51" s="13"/>
+      <c r="AEU51" s="13"/>
+      <c r="AEV51" s="13"/>
+      <c r="AEW51" s="13"/>
+      <c r="AEX51" s="13"/>
+      <c r="AEY51" s="13"/>
+      <c r="AEZ51" s="13"/>
+      <c r="AFA51" s="13"/>
+      <c r="AFB51" s="13"/>
+      <c r="AFC51" s="13"/>
+      <c r="AFD51" s="13"/>
+      <c r="AFE51" s="13"/>
+      <c r="AFF51" s="13"/>
+      <c r="AFG51" s="13"/>
+      <c r="AFH51" s="13"/>
+      <c r="AFI51" s="13"/>
+      <c r="AFJ51" s="13"/>
+      <c r="AFK51" s="13"/>
+      <c r="AFL51" s="13"/>
+      <c r="AFM51" s="13"/>
+      <c r="AFN51" s="13"/>
+      <c r="AFO51" s="13"/>
+      <c r="AFP51" s="13"/>
+      <c r="AFQ51" s="13"/>
+      <c r="AFR51" s="13"/>
+      <c r="AFS51" s="13"/>
+      <c r="AFT51" s="13"/>
+      <c r="AFU51" s="13"/>
+      <c r="AFV51" s="13"/>
+      <c r="AFW51" s="13"/>
+      <c r="AFX51" s="13"/>
+      <c r="AFY51" s="13"/>
+      <c r="AFZ51" s="13"/>
+      <c r="AGA51" s="13"/>
+      <c r="AGB51" s="13"/>
+      <c r="AGC51" s="13"/>
+      <c r="AGD51" s="13"/>
+      <c r="AGE51" s="13"/>
+      <c r="AGF51" s="13"/>
+      <c r="AGG51" s="13"/>
+      <c r="AGH51" s="13"/>
+      <c r="AGI51" s="13"/>
+      <c r="AGJ51" s="13"/>
+      <c r="AGK51" s="13"/>
+      <c r="AGL51" s="13"/>
+      <c r="AGM51" s="13"/>
+      <c r="AGN51" s="13"/>
+      <c r="AGO51" s="13"/>
+      <c r="AGP51" s="13"/>
+      <c r="AGQ51" s="13"/>
+      <c r="AGR51" s="13"/>
+      <c r="AGS51" s="13"/>
+      <c r="AGT51" s="13"/>
+      <c r="AGU51" s="13"/>
+      <c r="AGV51" s="13"/>
+      <c r="AGW51" s="13"/>
+      <c r="AGX51" s="13"/>
+      <c r="AGY51" s="13"/>
+      <c r="AGZ51" s="13"/>
+      <c r="AHA51" s="13"/>
+      <c r="AHB51" s="13"/>
+      <c r="AHC51" s="13"/>
+      <c r="AHD51" s="13"/>
+      <c r="AHE51" s="13"/>
+      <c r="AHF51" s="13"/>
+      <c r="AHG51" s="13"/>
+      <c r="AHH51" s="13"/>
+      <c r="AHI51" s="13"/>
+      <c r="AHJ51" s="13"/>
+      <c r="AHK51" s="13"/>
+      <c r="AHL51" s="13"/>
+      <c r="AHM51" s="13"/>
+      <c r="AHN51" s="13"/>
+      <c r="AHO51" s="13"/>
+      <c r="AHP51" s="13"/>
+      <c r="AHQ51" s="13"/>
+      <c r="AHR51" s="13"/>
+      <c r="AHS51" s="13"/>
+      <c r="AHT51" s="13"/>
+      <c r="AHU51" s="13"/>
+      <c r="AHV51" s="13"/>
+      <c r="AHW51" s="13"/>
+      <c r="AHX51" s="13"/>
+      <c r="AHY51" s="13"/>
+      <c r="AHZ51" s="13"/>
+      <c r="AIA51" s="13"/>
+      <c r="AIB51" s="13"/>
+      <c r="AIC51" s="13"/>
+      <c r="AID51" s="13"/>
+      <c r="AIE51" s="13"/>
+      <c r="AIF51" s="13"/>
+      <c r="AIG51" s="13"/>
+      <c r="AIH51" s="13"/>
+      <c r="AII51" s="13"/>
+      <c r="AIJ51" s="13"/>
+      <c r="AIK51" s="13"/>
+      <c r="AIL51" s="13"/>
+      <c r="AIM51" s="13"/>
+      <c r="AIN51" s="13"/>
+      <c r="AIO51" s="13"/>
+      <c r="AIP51" s="13"/>
+      <c r="AIQ51" s="13"/>
+      <c r="AIR51" s="13"/>
+      <c r="AIS51" s="13"/>
+      <c r="AIT51" s="13"/>
+      <c r="AIU51" s="13"/>
+      <c r="AIV51" s="13"/>
+      <c r="AIW51" s="13"/>
+      <c r="AIX51" s="13"/>
+      <c r="AIY51" s="13"/>
+      <c r="AIZ51" s="13"/>
+      <c r="AJA51" s="13"/>
+      <c r="AJB51" s="13"/>
+      <c r="AJC51" s="13"/>
+      <c r="AJD51" s="13"/>
+      <c r="AJE51" s="13"/>
+      <c r="AJF51" s="13"/>
+      <c r="AJG51" s="13"/>
+      <c r="AJH51" s="13"/>
+      <c r="AJI51" s="13"/>
+      <c r="AJJ51" s="13"/>
+      <c r="AJK51" s="13"/>
+      <c r="AJL51" s="13"/>
+      <c r="AJM51" s="13"/>
+      <c r="AJN51" s="13"/>
+      <c r="AJO51" s="13"/>
+      <c r="AJP51" s="13"/>
+      <c r="AJQ51" s="13"/>
+      <c r="AJR51" s="13"/>
+      <c r="AJS51" s="13"/>
+      <c r="AJT51" s="13"/>
+      <c r="AJU51" s="13"/>
+      <c r="AJV51" s="13"/>
+      <c r="AJW51" s="13"/>
+      <c r="AJX51" s="13"/>
+      <c r="AJY51" s="13"/>
+      <c r="AJZ51" s="13"/>
+      <c r="AKA51" s="13"/>
+      <c r="AKB51" s="13"/>
+      <c r="AKC51" s="13"/>
+      <c r="AKD51" s="13"/>
+      <c r="AKE51" s="13"/>
+      <c r="AKF51" s="13"/>
+      <c r="AKG51" s="13"/>
+      <c r="AKH51" s="13"/>
+      <c r="AKI51" s="13"/>
+      <c r="AKJ51" s="13"/>
+      <c r="AKK51" s="13"/>
+      <c r="AKL51" s="13"/>
+      <c r="AKM51" s="13"/>
+      <c r="AKN51" s="13"/>
+      <c r="AKO51" s="13"/>
+      <c r="AKP51" s="13"/>
+      <c r="AKQ51" s="13"/>
+      <c r="AKR51" s="13"/>
+      <c r="AKS51" s="13"/>
+      <c r="AKT51" s="13"/>
+      <c r="AKU51" s="13"/>
+      <c r="AKV51" s="13"/>
+      <c r="AKW51" s="13"/>
+      <c r="AKX51" s="13"/>
+      <c r="AKY51" s="13"/>
+      <c r="AKZ51" s="13"/>
+      <c r="ALA51" s="13"/>
+      <c r="ALB51" s="13"/>
+      <c r="ALC51" s="13"/>
+      <c r="ALD51" s="13"/>
+      <c r="ALE51" s="13"/>
+      <c r="ALF51" s="13"/>
+      <c r="ALG51" s="13"/>
+      <c r="ALH51" s="13"/>
+      <c r="ALI51" s="13"/>
+      <c r="ALJ51" s="13"/>
+      <c r="ALK51" s="13"/>
+      <c r="ALL51" s="13"/>
+      <c r="ALM51" s="13"/>
+      <c r="ALN51" s="13"/>
+      <c r="ALO51" s="13"/>
+      <c r="ALP51" s="13"/>
+      <c r="ALQ51" s="13"/>
+      <c r="ALR51" s="13"/>
+      <c r="ALS51" s="13"/>
+      <c r="ALT51" s="13"/>
+      <c r="ALU51" s="13"/>
+      <c r="ALV51" s="13"/>
+      <c r="ALW51" s="13"/>
+      <c r="ALX51" s="13"/>
+      <c r="ALY51" s="13"/>
+      <c r="ALZ51" s="13"/>
+      <c r="AMA51" s="13"/>
+      <c r="AMB51" s="13"/>
+      <c r="AMC51" s="13"/>
+      <c r="AMD51" s="13"/>
+      <c r="AME51" s="13"/>
+      <c r="AMF51" s="13"/>
+      <c r="AMG51" s="13"/>
+      <c r="AMH51" s="13"/>
+      <c r="AMI51" s="13"/>
+      <c r="AMJ51" s="13"/>
     </row>
     <row r="52" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>29</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="20" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="36" t="s">
-        <v>283</v>
+        <v>41</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
+      <c r="F53" s="10"/>
+      <c r="G53" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H53" s="17"/>
+    </row>
+    <row r="54" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="H53" s="36" t="s">
+      <c r="H54" s="36" t="s">
         <v>280</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+  <mergeCells count="36">
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
@@ -45321,18 +45337,23 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -45345,7 +45366,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2717D58E-0787-4FFD-8710-3E949B3DDA9E}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:AMJ54"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
@@ -45360,50 +45381,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -45438,14 +45459,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -45458,60 +45479,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -45523,13 +45544,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="55"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -45539,13 +45560,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>100</v>
@@ -45825,13 +45846,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -46200,13 +46221,13 @@
       <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
       <c r="G46" s="18" t="s">
         <v>6</v>
       </c>
@@ -46244,120 +46265,1157 @@
       </c>
       <c r="H48" s="17"/>
     </row>
-    <row r="49" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>3</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>93</v>
+        <v>361</v>
       </c>
       <c r="C49" s="40"/>
       <c r="D49" s="40"/>
       <c r="E49" s="40"/>
       <c r="F49" s="40"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="17"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="11"/>
+      <c r="V49" s="11"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11"/>
+      <c r="AB49" s="11"/>
+      <c r="AC49" s="11"/>
+      <c r="AD49" s="11"/>
+      <c r="AE49" s="11"/>
+      <c r="AF49" s="11"/>
+      <c r="AG49" s="11"/>
+      <c r="AH49" s="11"/>
+      <c r="AI49" s="11"/>
+      <c r="AJ49" s="11"/>
+      <c r="AK49" s="11"/>
+      <c r="AL49" s="11"/>
+      <c r="AM49" s="11"/>
+      <c r="AN49" s="11"/>
+      <c r="AO49" s="11"/>
+      <c r="AP49" s="11"/>
+      <c r="AQ49" s="11"/>
+      <c r="AR49" s="11"/>
+      <c r="AS49" s="11"/>
+      <c r="AT49" s="11"/>
+      <c r="AU49" s="11"/>
+      <c r="AV49" s="11"/>
+      <c r="AW49" s="11"/>
+      <c r="AX49" s="11"/>
+      <c r="AY49" s="11"/>
+      <c r="AZ49" s="11"/>
+      <c r="BA49" s="11"/>
+      <c r="BB49" s="11"/>
+      <c r="BC49" s="11"/>
+      <c r="BD49" s="11"/>
+      <c r="BE49" s="11"/>
+      <c r="BF49" s="11"/>
+      <c r="BG49" s="11"/>
+      <c r="BH49" s="11"/>
+      <c r="BI49" s="11"/>
+      <c r="BJ49" s="11"/>
+      <c r="BK49" s="11"/>
+      <c r="BL49" s="11"/>
+      <c r="BM49" s="11"/>
+      <c r="BN49" s="11"/>
+      <c r="BO49" s="11"/>
+      <c r="BP49" s="11"/>
+      <c r="BQ49" s="11"/>
+      <c r="BR49" s="11"/>
+      <c r="BS49" s="11"/>
+      <c r="BT49" s="11"/>
+      <c r="BU49" s="11"/>
+      <c r="BV49" s="11"/>
+      <c r="BW49" s="11"/>
+      <c r="BX49" s="11"/>
+      <c r="BY49" s="11"/>
+      <c r="BZ49" s="11"/>
+      <c r="CA49" s="11"/>
+      <c r="CB49" s="11"/>
+      <c r="CC49" s="11"/>
+      <c r="CD49" s="11"/>
+      <c r="CE49" s="11"/>
+      <c r="CF49" s="11"/>
+      <c r="CG49" s="11"/>
+      <c r="CH49" s="11"/>
+      <c r="CI49" s="11"/>
+      <c r="CJ49" s="11"/>
+      <c r="CK49" s="11"/>
+      <c r="CL49" s="11"/>
+      <c r="CM49" s="11"/>
+      <c r="CN49" s="11"/>
+      <c r="CO49" s="11"/>
+      <c r="CP49" s="11"/>
+      <c r="CQ49" s="11"/>
+      <c r="CR49" s="11"/>
+      <c r="CS49" s="11"/>
+      <c r="CT49" s="11"/>
+      <c r="CU49" s="11"/>
+      <c r="CV49" s="11"/>
+      <c r="CW49" s="11"/>
+      <c r="CX49" s="11"/>
+      <c r="CY49" s="11"/>
+      <c r="CZ49" s="11"/>
+      <c r="DA49" s="11"/>
+      <c r="DB49" s="11"/>
+      <c r="DC49" s="11"/>
+      <c r="DD49" s="11"/>
+      <c r="DE49" s="11"/>
+      <c r="DF49" s="11"/>
+      <c r="DG49" s="11"/>
+      <c r="DH49" s="11"/>
+      <c r="DI49" s="11"/>
+      <c r="DJ49" s="11"/>
+      <c r="DK49" s="11"/>
+      <c r="DL49" s="11"/>
+      <c r="DM49" s="11"/>
+      <c r="DN49" s="11"/>
+      <c r="DO49" s="11"/>
+      <c r="DP49" s="11"/>
+      <c r="DQ49" s="11"/>
+      <c r="DR49" s="11"/>
+      <c r="DS49" s="11"/>
+      <c r="DT49" s="11"/>
+      <c r="DU49" s="11"/>
+      <c r="DV49" s="11"/>
+      <c r="DW49" s="11"/>
+      <c r="DX49" s="11"/>
+      <c r="DY49" s="11"/>
+      <c r="DZ49" s="11"/>
+      <c r="EA49" s="11"/>
+      <c r="EB49" s="11"/>
+      <c r="EC49" s="11"/>
+      <c r="ED49" s="11"/>
+      <c r="EE49" s="11"/>
+      <c r="EF49" s="11"/>
+      <c r="EG49" s="11"/>
+      <c r="EH49" s="11"/>
+      <c r="EI49" s="11"/>
+      <c r="EJ49" s="11"/>
+      <c r="EK49" s="11"/>
+      <c r="EL49" s="11"/>
+      <c r="EM49" s="11"/>
+      <c r="EN49" s="11"/>
+      <c r="EO49" s="11"/>
+      <c r="EP49" s="11"/>
+      <c r="EQ49" s="11"/>
+      <c r="ER49" s="11"/>
+      <c r="ES49" s="11"/>
+      <c r="ET49" s="11"/>
+      <c r="EU49" s="11"/>
+      <c r="EV49" s="11"/>
+      <c r="EW49" s="11"/>
+      <c r="EX49" s="11"/>
+      <c r="EY49" s="11"/>
+      <c r="EZ49" s="11"/>
+      <c r="FA49" s="11"/>
+      <c r="FB49" s="11"/>
+      <c r="FC49" s="11"/>
+      <c r="FD49" s="11"/>
+      <c r="FE49" s="11"/>
+      <c r="FF49" s="11"/>
+      <c r="FG49" s="11"/>
+      <c r="FH49" s="11"/>
+      <c r="FI49" s="11"/>
+      <c r="FJ49" s="11"/>
+      <c r="FK49" s="11"/>
+      <c r="FL49" s="11"/>
+      <c r="FM49" s="11"/>
+      <c r="FN49" s="11"/>
+      <c r="FO49" s="11"/>
+      <c r="FP49" s="11"/>
+      <c r="FQ49" s="11"/>
+      <c r="FR49" s="11"/>
+      <c r="FS49" s="11"/>
+      <c r="FT49" s="11"/>
+      <c r="FU49" s="11"/>
+      <c r="FV49" s="11"/>
+      <c r="FW49" s="11"/>
+      <c r="FX49" s="11"/>
+      <c r="FY49" s="11"/>
+      <c r="FZ49" s="11"/>
+      <c r="GA49" s="11"/>
+      <c r="GB49" s="11"/>
+      <c r="GC49" s="11"/>
+      <c r="GD49" s="11"/>
+      <c r="GE49" s="11"/>
+      <c r="GF49" s="11"/>
+      <c r="GG49" s="11"/>
+      <c r="GH49" s="11"/>
+      <c r="GI49" s="11"/>
+      <c r="GJ49" s="11"/>
+      <c r="GK49" s="11"/>
+      <c r="GL49" s="11"/>
+      <c r="GM49" s="11"/>
+      <c r="GN49" s="11"/>
+      <c r="GO49" s="11"/>
+      <c r="GP49" s="11"/>
+      <c r="GQ49" s="11"/>
+      <c r="GR49" s="11"/>
+      <c r="GS49" s="11"/>
+      <c r="GT49" s="11"/>
+      <c r="GU49" s="11"/>
+      <c r="GV49" s="11"/>
+      <c r="GW49" s="11"/>
+      <c r="GX49" s="11"/>
+      <c r="GY49" s="11"/>
+      <c r="GZ49" s="11"/>
+      <c r="HA49" s="11"/>
+      <c r="HB49" s="11"/>
+      <c r="HC49" s="11"/>
+      <c r="HD49" s="11"/>
+      <c r="HE49" s="11"/>
+      <c r="HF49" s="11"/>
+      <c r="HG49" s="11"/>
+      <c r="HH49" s="11"/>
+      <c r="HI49" s="11"/>
+      <c r="HJ49" s="11"/>
+      <c r="HK49" s="11"/>
+      <c r="HL49" s="11"/>
+      <c r="HM49" s="11"/>
+      <c r="HN49" s="11"/>
+      <c r="HO49" s="11"/>
+      <c r="HP49" s="11"/>
+      <c r="HQ49" s="11"/>
+      <c r="HR49" s="11"/>
+      <c r="HS49" s="11"/>
+      <c r="HT49" s="11"/>
+      <c r="HU49" s="11"/>
+      <c r="HV49" s="11"/>
+      <c r="HW49" s="11"/>
+      <c r="HX49" s="11"/>
+      <c r="HY49" s="11"/>
+      <c r="HZ49" s="11"/>
+      <c r="IA49" s="11"/>
+      <c r="IB49" s="11"/>
+      <c r="IC49" s="11"/>
+      <c r="ID49" s="11"/>
+      <c r="IE49" s="11"/>
+      <c r="IF49" s="11"/>
+      <c r="IG49" s="11"/>
+      <c r="IH49" s="11"/>
+      <c r="II49" s="11"/>
+      <c r="IJ49" s="11"/>
+      <c r="IK49" s="11"/>
+      <c r="IL49" s="11"/>
+      <c r="IM49" s="11"/>
+      <c r="IN49" s="11"/>
+      <c r="IO49" s="11"/>
+      <c r="IP49" s="11"/>
+      <c r="IQ49" s="11"/>
+      <c r="IR49" s="11"/>
+      <c r="IS49" s="11"/>
+      <c r="IT49" s="11"/>
+      <c r="IU49" s="11"/>
+      <c r="IV49" s="11"/>
+      <c r="IW49" s="11"/>
+      <c r="IX49" s="11"/>
+      <c r="IY49" s="11"/>
+      <c r="IZ49" s="11"/>
+      <c r="JA49" s="11"/>
+      <c r="JB49" s="11"/>
+      <c r="JC49" s="11"/>
+      <c r="JD49" s="11"/>
+      <c r="JE49" s="11"/>
+      <c r="JF49" s="11"/>
+      <c r="JG49" s="11"/>
+      <c r="JH49" s="11"/>
+      <c r="JI49" s="11"/>
+      <c r="JJ49" s="11"/>
+      <c r="JK49" s="11"/>
+      <c r="JL49" s="11"/>
+      <c r="JM49" s="11"/>
+      <c r="JN49" s="11"/>
+      <c r="JO49" s="11"/>
+      <c r="JP49" s="11"/>
+      <c r="JQ49" s="11"/>
+      <c r="JR49" s="11"/>
+      <c r="JS49" s="11"/>
+      <c r="JT49" s="11"/>
+      <c r="JU49" s="11"/>
+      <c r="JV49" s="11"/>
+      <c r="JW49" s="11"/>
+      <c r="JX49" s="11"/>
+      <c r="JY49" s="11"/>
+      <c r="JZ49" s="11"/>
+      <c r="KA49" s="11"/>
+      <c r="KB49" s="11"/>
+      <c r="KC49" s="11"/>
+      <c r="KD49" s="11"/>
+      <c r="KE49" s="11"/>
+      <c r="KF49" s="11"/>
+      <c r="KG49" s="11"/>
+      <c r="KH49" s="11"/>
+      <c r="KI49" s="11"/>
+      <c r="KJ49" s="11"/>
+      <c r="KK49" s="11"/>
+      <c r="KL49" s="11"/>
+      <c r="KM49" s="11"/>
+      <c r="KN49" s="11"/>
+      <c r="KO49" s="11"/>
+      <c r="KP49" s="11"/>
+      <c r="KQ49" s="11"/>
+      <c r="KR49" s="11"/>
+      <c r="KS49" s="11"/>
+      <c r="KT49" s="11"/>
+      <c r="KU49" s="11"/>
+      <c r="KV49" s="11"/>
+      <c r="KW49" s="11"/>
+      <c r="KX49" s="11"/>
+      <c r="KY49" s="11"/>
+      <c r="KZ49" s="11"/>
+      <c r="LA49" s="11"/>
+      <c r="LB49" s="11"/>
+      <c r="LC49" s="11"/>
+      <c r="LD49" s="11"/>
+      <c r="LE49" s="11"/>
+      <c r="LF49" s="11"/>
+      <c r="LG49" s="11"/>
+      <c r="LH49" s="11"/>
+      <c r="LI49" s="11"/>
+      <c r="LJ49" s="11"/>
+      <c r="LK49" s="11"/>
+      <c r="LL49" s="11"/>
+      <c r="LM49" s="11"/>
+      <c r="LN49" s="11"/>
+      <c r="LO49" s="11"/>
+      <c r="LP49" s="11"/>
+      <c r="LQ49" s="11"/>
+      <c r="LR49" s="11"/>
+      <c r="LS49" s="11"/>
+      <c r="LT49" s="11"/>
+      <c r="LU49" s="11"/>
+      <c r="LV49" s="11"/>
+      <c r="LW49" s="11"/>
+      <c r="LX49" s="11"/>
+      <c r="LY49" s="11"/>
+      <c r="LZ49" s="11"/>
+      <c r="MA49" s="11"/>
+      <c r="MB49" s="11"/>
+      <c r="MC49" s="11"/>
+      <c r="MD49" s="11"/>
+      <c r="ME49" s="11"/>
+      <c r="MF49" s="11"/>
+      <c r="MG49" s="11"/>
+      <c r="MH49" s="11"/>
+      <c r="MI49" s="11"/>
+      <c r="MJ49" s="11"/>
+      <c r="MK49" s="11"/>
+      <c r="ML49" s="11"/>
+      <c r="MM49" s="11"/>
+      <c r="MN49" s="11"/>
+      <c r="MO49" s="11"/>
+      <c r="MP49" s="11"/>
+      <c r="MQ49" s="11"/>
+      <c r="MR49" s="11"/>
+      <c r="MS49" s="11"/>
+      <c r="MT49" s="11"/>
+      <c r="MU49" s="11"/>
+      <c r="MV49" s="11"/>
+      <c r="MW49" s="11"/>
+      <c r="MX49" s="11"/>
+      <c r="MY49" s="11"/>
+      <c r="MZ49" s="11"/>
+      <c r="NA49" s="11"/>
+      <c r="NB49" s="11"/>
+      <c r="NC49" s="11"/>
+      <c r="ND49" s="11"/>
+      <c r="NE49" s="11"/>
+      <c r="NF49" s="11"/>
+      <c r="NG49" s="11"/>
+      <c r="NH49" s="11"/>
+      <c r="NI49" s="11"/>
+      <c r="NJ49" s="11"/>
+      <c r="NK49" s="11"/>
+      <c r="NL49" s="11"/>
+      <c r="NM49" s="11"/>
+      <c r="NN49" s="11"/>
+      <c r="NO49" s="11"/>
+      <c r="NP49" s="11"/>
+      <c r="NQ49" s="11"/>
+      <c r="NR49" s="11"/>
+      <c r="NS49" s="11"/>
+      <c r="NT49" s="11"/>
+      <c r="NU49" s="11"/>
+      <c r="NV49" s="11"/>
+      <c r="NW49" s="11"/>
+      <c r="NX49" s="11"/>
+      <c r="NY49" s="11"/>
+      <c r="NZ49" s="11"/>
+      <c r="OA49" s="11"/>
+      <c r="OB49" s="11"/>
+      <c r="OC49" s="11"/>
+      <c r="OD49" s="11"/>
+      <c r="OE49" s="11"/>
+      <c r="OF49" s="11"/>
+      <c r="OG49" s="11"/>
+      <c r="OH49" s="11"/>
+      <c r="OI49" s="11"/>
+      <c r="OJ49" s="11"/>
+      <c r="OK49" s="11"/>
+      <c r="OL49" s="11"/>
+      <c r="OM49" s="11"/>
+      <c r="ON49" s="11"/>
+      <c r="OO49" s="11"/>
+      <c r="OP49" s="11"/>
+      <c r="OQ49" s="11"/>
+      <c r="OR49" s="11"/>
+      <c r="OS49" s="11"/>
+      <c r="OT49" s="11"/>
+      <c r="OU49" s="11"/>
+      <c r="OV49" s="11"/>
+      <c r="OW49" s="11"/>
+      <c r="OX49" s="11"/>
+      <c r="OY49" s="11"/>
+      <c r="OZ49" s="11"/>
+      <c r="PA49" s="11"/>
+      <c r="PB49" s="11"/>
+      <c r="PC49" s="11"/>
+      <c r="PD49" s="11"/>
+      <c r="PE49" s="11"/>
+      <c r="PF49" s="11"/>
+      <c r="PG49" s="11"/>
+      <c r="PH49" s="11"/>
+      <c r="PI49" s="11"/>
+      <c r="PJ49" s="11"/>
+      <c r="PK49" s="11"/>
+      <c r="PL49" s="11"/>
+      <c r="PM49" s="11"/>
+      <c r="PN49" s="11"/>
+      <c r="PO49" s="11"/>
+      <c r="PP49" s="11"/>
+      <c r="PQ49" s="11"/>
+      <c r="PR49" s="11"/>
+      <c r="PS49" s="11"/>
+      <c r="PT49" s="11"/>
+      <c r="PU49" s="11"/>
+      <c r="PV49" s="11"/>
+      <c r="PW49" s="11"/>
+      <c r="PX49" s="11"/>
+      <c r="PY49" s="11"/>
+      <c r="PZ49" s="11"/>
+      <c r="QA49" s="11"/>
+      <c r="QB49" s="11"/>
+      <c r="QC49" s="11"/>
+      <c r="QD49" s="11"/>
+      <c r="QE49" s="11"/>
+      <c r="QF49" s="11"/>
+      <c r="QG49" s="11"/>
+      <c r="QH49" s="11"/>
+      <c r="QI49" s="11"/>
+      <c r="QJ49" s="11"/>
+      <c r="QK49" s="11"/>
+      <c r="QL49" s="11"/>
+      <c r="QM49" s="11"/>
+      <c r="QN49" s="11"/>
+      <c r="QO49" s="11"/>
+      <c r="QP49" s="11"/>
+      <c r="QQ49" s="11"/>
+      <c r="QR49" s="11"/>
+      <c r="QS49" s="11"/>
+      <c r="QT49" s="11"/>
+      <c r="QU49" s="11"/>
+      <c r="QV49" s="11"/>
+      <c r="QW49" s="11"/>
+      <c r="QX49" s="11"/>
+      <c r="QY49" s="11"/>
+      <c r="QZ49" s="11"/>
+      <c r="RA49" s="11"/>
+      <c r="RB49" s="11"/>
+      <c r="RC49" s="11"/>
+      <c r="RD49" s="11"/>
+      <c r="RE49" s="11"/>
+      <c r="RF49" s="11"/>
+      <c r="RG49" s="11"/>
+      <c r="RH49" s="11"/>
+      <c r="RI49" s="11"/>
+      <c r="RJ49" s="11"/>
+      <c r="RK49" s="11"/>
+      <c r="RL49" s="11"/>
+      <c r="RM49" s="11"/>
+      <c r="RN49" s="11"/>
+      <c r="RO49" s="11"/>
+      <c r="RP49" s="11"/>
+      <c r="RQ49" s="11"/>
+      <c r="RR49" s="11"/>
+      <c r="RS49" s="11"/>
+      <c r="RT49" s="11"/>
+      <c r="RU49" s="11"/>
+      <c r="RV49" s="11"/>
+      <c r="RW49" s="11"/>
+      <c r="RX49" s="11"/>
+      <c r="RY49" s="11"/>
+      <c r="RZ49" s="11"/>
+      <c r="SA49" s="11"/>
+      <c r="SB49" s="11"/>
+      <c r="SC49" s="11"/>
+      <c r="SD49" s="11"/>
+      <c r="SE49" s="11"/>
+      <c r="SF49" s="11"/>
+      <c r="SG49" s="11"/>
+      <c r="SH49" s="11"/>
+      <c r="SI49" s="11"/>
+      <c r="SJ49" s="11"/>
+      <c r="SK49" s="11"/>
+      <c r="SL49" s="11"/>
+      <c r="SM49" s="11"/>
+      <c r="SN49" s="11"/>
+      <c r="SO49" s="11"/>
+      <c r="SP49" s="11"/>
+      <c r="SQ49" s="11"/>
+      <c r="SR49" s="11"/>
+      <c r="SS49" s="11"/>
+      <c r="ST49" s="11"/>
+      <c r="SU49" s="11"/>
+      <c r="SV49" s="11"/>
+      <c r="SW49" s="11"/>
+      <c r="SX49" s="11"/>
+      <c r="SY49" s="11"/>
+      <c r="SZ49" s="11"/>
+      <c r="TA49" s="11"/>
+      <c r="TB49" s="11"/>
+      <c r="TC49" s="11"/>
+      <c r="TD49" s="11"/>
+      <c r="TE49" s="11"/>
+      <c r="TF49" s="11"/>
+      <c r="TG49" s="11"/>
+      <c r="TH49" s="11"/>
+      <c r="TI49" s="11"/>
+      <c r="TJ49" s="11"/>
+      <c r="TK49" s="11"/>
+      <c r="TL49" s="11"/>
+      <c r="TM49" s="11"/>
+      <c r="TN49" s="11"/>
+      <c r="TO49" s="11"/>
+      <c r="TP49" s="11"/>
+      <c r="TQ49" s="11"/>
+      <c r="TR49" s="11"/>
+      <c r="TS49" s="11"/>
+      <c r="TT49" s="11"/>
+      <c r="TU49" s="11"/>
+      <c r="TV49" s="11"/>
+      <c r="TW49" s="11"/>
+      <c r="TX49" s="11"/>
+      <c r="TY49" s="11"/>
+      <c r="TZ49" s="11"/>
+      <c r="UA49" s="11"/>
+      <c r="UB49" s="11"/>
+      <c r="UC49" s="11"/>
+      <c r="UD49" s="11"/>
+      <c r="UE49" s="11"/>
+      <c r="UF49" s="11"/>
+      <c r="UG49" s="11"/>
+      <c r="UH49" s="11"/>
+      <c r="UI49" s="11"/>
+      <c r="UJ49" s="11"/>
+      <c r="UK49" s="11"/>
+      <c r="UL49" s="11"/>
+      <c r="UM49" s="11"/>
+      <c r="UN49" s="11"/>
+      <c r="UO49" s="11"/>
+      <c r="UP49" s="11"/>
+      <c r="UQ49" s="11"/>
+      <c r="UR49" s="11"/>
+      <c r="US49" s="11"/>
+      <c r="UT49" s="11"/>
+      <c r="UU49" s="11"/>
+      <c r="UV49" s="11"/>
+      <c r="UW49" s="11"/>
+      <c r="UX49" s="11"/>
+      <c r="UY49" s="11"/>
+      <c r="UZ49" s="11"/>
+      <c r="VA49" s="11"/>
+      <c r="VB49" s="11"/>
+      <c r="VC49" s="11"/>
+      <c r="VD49" s="11"/>
+      <c r="VE49" s="11"/>
+      <c r="VF49" s="11"/>
+      <c r="VG49" s="11"/>
+      <c r="VH49" s="11"/>
+      <c r="VI49" s="11"/>
+      <c r="VJ49" s="11"/>
+      <c r="VK49" s="11"/>
+      <c r="VL49" s="11"/>
+      <c r="VM49" s="11"/>
+      <c r="VN49" s="11"/>
+      <c r="VO49" s="11"/>
+      <c r="VP49" s="11"/>
+      <c r="VQ49" s="11"/>
+      <c r="VR49" s="11"/>
+      <c r="VS49" s="11"/>
+      <c r="VT49" s="11"/>
+      <c r="VU49" s="11"/>
+      <c r="VV49" s="11"/>
+      <c r="VW49" s="11"/>
+      <c r="VX49" s="11"/>
+      <c r="VY49" s="11"/>
+      <c r="VZ49" s="11"/>
+      <c r="WA49" s="11"/>
+      <c r="WB49" s="11"/>
+      <c r="WC49" s="11"/>
+      <c r="WD49" s="11"/>
+      <c r="WE49" s="11"/>
+      <c r="WF49" s="11"/>
+      <c r="WG49" s="11"/>
+      <c r="WH49" s="11"/>
+      <c r="WI49" s="11"/>
+      <c r="WJ49" s="11"/>
+      <c r="WK49" s="11"/>
+      <c r="WL49" s="11"/>
+      <c r="WM49" s="11"/>
+      <c r="WN49" s="11"/>
+      <c r="WO49" s="11"/>
+      <c r="WP49" s="11"/>
+      <c r="WQ49" s="11"/>
+      <c r="WR49" s="11"/>
+      <c r="WS49" s="11"/>
+      <c r="WT49" s="11"/>
+      <c r="WU49" s="11"/>
+      <c r="WV49" s="11"/>
+      <c r="WW49" s="11"/>
+      <c r="WX49" s="11"/>
+      <c r="WY49" s="11"/>
+      <c r="WZ49" s="11"/>
+      <c r="XA49" s="11"/>
+      <c r="XB49" s="11"/>
+      <c r="XC49" s="11"/>
+      <c r="XD49" s="11"/>
+      <c r="XE49" s="11"/>
+      <c r="XF49" s="11"/>
+      <c r="XG49" s="11"/>
+      <c r="XH49" s="11"/>
+      <c r="XI49" s="11"/>
+      <c r="XJ49" s="11"/>
+      <c r="XK49" s="11"/>
+      <c r="XL49" s="11"/>
+      <c r="XM49" s="11"/>
+      <c r="XN49" s="11"/>
+      <c r="XO49" s="11"/>
+      <c r="XP49" s="11"/>
+      <c r="XQ49" s="11"/>
+      <c r="XR49" s="11"/>
+      <c r="XS49" s="11"/>
+      <c r="XT49" s="11"/>
+      <c r="XU49" s="11"/>
+      <c r="XV49" s="11"/>
+      <c r="XW49" s="11"/>
+      <c r="XX49" s="11"/>
+      <c r="XY49" s="11"/>
+      <c r="XZ49" s="11"/>
+      <c r="YA49" s="11"/>
+      <c r="YB49" s="11"/>
+      <c r="YC49" s="11"/>
+      <c r="YD49" s="11"/>
+      <c r="YE49" s="11"/>
+      <c r="YF49" s="11"/>
+      <c r="YG49" s="11"/>
+      <c r="YH49" s="11"/>
+      <c r="YI49" s="11"/>
+      <c r="YJ49" s="11"/>
+      <c r="YK49" s="11"/>
+      <c r="YL49" s="11"/>
+      <c r="YM49" s="11"/>
+      <c r="YN49" s="11"/>
+      <c r="YO49" s="11"/>
+      <c r="YP49" s="11"/>
+      <c r="YQ49" s="11"/>
+      <c r="YR49" s="11"/>
+      <c r="YS49" s="11"/>
+      <c r="YT49" s="11"/>
+      <c r="YU49" s="11"/>
+      <c r="YV49" s="11"/>
+      <c r="YW49" s="11"/>
+      <c r="YX49" s="11"/>
+      <c r="YY49" s="11"/>
+      <c r="YZ49" s="11"/>
+      <c r="ZA49" s="11"/>
+      <c r="ZB49" s="11"/>
+      <c r="ZC49" s="11"/>
+      <c r="ZD49" s="11"/>
+      <c r="ZE49" s="11"/>
+      <c r="ZF49" s="11"/>
+      <c r="ZG49" s="11"/>
+      <c r="ZH49" s="11"/>
+      <c r="ZI49" s="11"/>
+      <c r="ZJ49" s="11"/>
+      <c r="ZK49" s="11"/>
+      <c r="ZL49" s="11"/>
+      <c r="ZM49" s="11"/>
+      <c r="ZN49" s="11"/>
+      <c r="ZO49" s="11"/>
+      <c r="ZP49" s="11"/>
+      <c r="ZQ49" s="11"/>
+      <c r="ZR49" s="11"/>
+      <c r="ZS49" s="11"/>
+      <c r="ZT49" s="11"/>
+      <c r="ZU49" s="11"/>
+      <c r="ZV49" s="11"/>
+      <c r="ZW49" s="11"/>
+      <c r="ZX49" s="11"/>
+      <c r="ZY49" s="11"/>
+      <c r="ZZ49" s="11"/>
+      <c r="AAA49" s="11"/>
+      <c r="AAB49" s="11"/>
+      <c r="AAC49" s="11"/>
+      <c r="AAD49" s="11"/>
+      <c r="AAE49" s="11"/>
+      <c r="AAF49" s="11"/>
+      <c r="AAG49" s="11"/>
+      <c r="AAH49" s="11"/>
+      <c r="AAI49" s="11"/>
+      <c r="AAJ49" s="11"/>
+      <c r="AAK49" s="11"/>
+      <c r="AAL49" s="11"/>
+      <c r="AAM49" s="11"/>
+      <c r="AAN49" s="11"/>
+      <c r="AAO49" s="11"/>
+      <c r="AAP49" s="11"/>
+      <c r="AAQ49" s="11"/>
+      <c r="AAR49" s="11"/>
+      <c r="AAS49" s="11"/>
+      <c r="AAT49" s="11"/>
+      <c r="AAU49" s="11"/>
+      <c r="AAV49" s="11"/>
+      <c r="AAW49" s="11"/>
+      <c r="AAX49" s="11"/>
+      <c r="AAY49" s="11"/>
+      <c r="AAZ49" s="11"/>
+      <c r="ABA49" s="11"/>
+      <c r="ABB49" s="11"/>
+      <c r="ABC49" s="11"/>
+      <c r="ABD49" s="11"/>
+      <c r="ABE49" s="11"/>
+      <c r="ABF49" s="11"/>
+      <c r="ABG49" s="11"/>
+      <c r="ABH49" s="11"/>
+      <c r="ABI49" s="11"/>
+      <c r="ABJ49" s="11"/>
+      <c r="ABK49" s="11"/>
+      <c r="ABL49" s="11"/>
+      <c r="ABM49" s="11"/>
+      <c r="ABN49" s="11"/>
+      <c r="ABO49" s="11"/>
+      <c r="ABP49" s="11"/>
+      <c r="ABQ49" s="11"/>
+      <c r="ABR49" s="11"/>
+      <c r="ABS49" s="11"/>
+      <c r="ABT49" s="11"/>
+      <c r="ABU49" s="11"/>
+      <c r="ABV49" s="11"/>
+      <c r="ABW49" s="11"/>
+      <c r="ABX49" s="11"/>
+      <c r="ABY49" s="11"/>
+      <c r="ABZ49" s="11"/>
+      <c r="ACA49" s="11"/>
+      <c r="ACB49" s="11"/>
+      <c r="ACC49" s="11"/>
+      <c r="ACD49" s="11"/>
+      <c r="ACE49" s="11"/>
+      <c r="ACF49" s="11"/>
+      <c r="ACG49" s="11"/>
+      <c r="ACH49" s="11"/>
+      <c r="ACI49" s="11"/>
+      <c r="ACJ49" s="11"/>
+      <c r="ACK49" s="11"/>
+      <c r="ACL49" s="11"/>
+      <c r="ACM49" s="11"/>
+      <c r="ACN49" s="11"/>
+      <c r="ACO49" s="11"/>
+      <c r="ACP49" s="11"/>
+      <c r="ACQ49" s="11"/>
+      <c r="ACR49" s="11"/>
+      <c r="ACS49" s="11"/>
+      <c r="ACT49" s="11"/>
+      <c r="ACU49" s="11"/>
+      <c r="ACV49" s="11"/>
+      <c r="ACW49" s="11"/>
+      <c r="ACX49" s="11"/>
+      <c r="ACY49" s="11"/>
+      <c r="ACZ49" s="11"/>
+      <c r="ADA49" s="11"/>
+      <c r="ADB49" s="11"/>
+      <c r="ADC49" s="11"/>
+      <c r="ADD49" s="11"/>
+      <c r="ADE49" s="11"/>
+      <c r="ADF49" s="11"/>
+      <c r="ADG49" s="11"/>
+      <c r="ADH49" s="11"/>
+      <c r="ADI49" s="11"/>
+      <c r="ADJ49" s="11"/>
+      <c r="ADK49" s="11"/>
+      <c r="ADL49" s="11"/>
+      <c r="ADM49" s="11"/>
+      <c r="ADN49" s="11"/>
+      <c r="ADO49" s="11"/>
+      <c r="ADP49" s="11"/>
+      <c r="ADQ49" s="11"/>
+      <c r="ADR49" s="11"/>
+      <c r="ADS49" s="11"/>
+      <c r="ADT49" s="11"/>
+      <c r="ADU49" s="11"/>
+      <c r="ADV49" s="11"/>
+      <c r="ADW49" s="11"/>
+      <c r="ADX49" s="11"/>
+      <c r="ADY49" s="11"/>
+      <c r="ADZ49" s="11"/>
+      <c r="AEA49" s="11"/>
+      <c r="AEB49" s="11"/>
+      <c r="AEC49" s="11"/>
+      <c r="AED49" s="11"/>
+      <c r="AEE49" s="11"/>
+      <c r="AEF49" s="11"/>
+      <c r="AEG49" s="11"/>
+      <c r="AEH49" s="11"/>
+      <c r="AEI49" s="11"/>
+      <c r="AEJ49" s="11"/>
+      <c r="AEK49" s="11"/>
+      <c r="AEL49" s="11"/>
+      <c r="AEM49" s="11"/>
+      <c r="AEN49" s="11"/>
+      <c r="AEO49" s="11"/>
+      <c r="AEP49" s="11"/>
+      <c r="AEQ49" s="11"/>
+      <c r="AER49" s="11"/>
+      <c r="AES49" s="11"/>
+      <c r="AET49" s="11"/>
+      <c r="AEU49" s="11"/>
+      <c r="AEV49" s="11"/>
+      <c r="AEW49" s="11"/>
+      <c r="AEX49" s="11"/>
+      <c r="AEY49" s="11"/>
+      <c r="AEZ49" s="11"/>
+      <c r="AFA49" s="11"/>
+      <c r="AFB49" s="11"/>
+      <c r="AFC49" s="11"/>
+      <c r="AFD49" s="11"/>
+      <c r="AFE49" s="11"/>
+      <c r="AFF49" s="11"/>
+      <c r="AFG49" s="11"/>
+      <c r="AFH49" s="11"/>
+      <c r="AFI49" s="11"/>
+      <c r="AFJ49" s="11"/>
+      <c r="AFK49" s="11"/>
+      <c r="AFL49" s="11"/>
+      <c r="AFM49" s="11"/>
+      <c r="AFN49" s="11"/>
+      <c r="AFO49" s="11"/>
+      <c r="AFP49" s="11"/>
+      <c r="AFQ49" s="11"/>
+      <c r="AFR49" s="11"/>
+      <c r="AFS49" s="11"/>
+      <c r="AFT49" s="11"/>
+      <c r="AFU49" s="11"/>
+      <c r="AFV49" s="11"/>
+      <c r="AFW49" s="11"/>
+      <c r="AFX49" s="11"/>
+      <c r="AFY49" s="11"/>
+      <c r="AFZ49" s="11"/>
+      <c r="AGA49" s="11"/>
+      <c r="AGB49" s="11"/>
+      <c r="AGC49" s="11"/>
+      <c r="AGD49" s="11"/>
+      <c r="AGE49" s="11"/>
+      <c r="AGF49" s="11"/>
+      <c r="AGG49" s="11"/>
+      <c r="AGH49" s="11"/>
+      <c r="AGI49" s="11"/>
+      <c r="AGJ49" s="11"/>
+      <c r="AGK49" s="11"/>
+      <c r="AGL49" s="11"/>
+      <c r="AGM49" s="11"/>
+      <c r="AGN49" s="11"/>
+      <c r="AGO49" s="11"/>
+      <c r="AGP49" s="11"/>
+      <c r="AGQ49" s="11"/>
+      <c r="AGR49" s="11"/>
+      <c r="AGS49" s="11"/>
+      <c r="AGT49" s="11"/>
+      <c r="AGU49" s="11"/>
+      <c r="AGV49" s="11"/>
+      <c r="AGW49" s="11"/>
+      <c r="AGX49" s="11"/>
+      <c r="AGY49" s="11"/>
+      <c r="AGZ49" s="11"/>
+      <c r="AHA49" s="11"/>
+      <c r="AHB49" s="11"/>
+      <c r="AHC49" s="11"/>
+      <c r="AHD49" s="11"/>
+      <c r="AHE49" s="11"/>
+      <c r="AHF49" s="11"/>
+      <c r="AHG49" s="11"/>
+      <c r="AHH49" s="11"/>
+      <c r="AHI49" s="11"/>
+      <c r="AHJ49" s="11"/>
+      <c r="AHK49" s="11"/>
+      <c r="AHL49" s="11"/>
+      <c r="AHM49" s="11"/>
+      <c r="AHN49" s="11"/>
+      <c r="AHO49" s="11"/>
+      <c r="AHP49" s="11"/>
+      <c r="AHQ49" s="11"/>
+      <c r="AHR49" s="11"/>
+      <c r="AHS49" s="11"/>
+      <c r="AHT49" s="11"/>
+      <c r="AHU49" s="11"/>
+      <c r="AHV49" s="11"/>
+      <c r="AHW49" s="11"/>
+      <c r="AHX49" s="11"/>
+      <c r="AHY49" s="11"/>
+      <c r="AHZ49" s="11"/>
+      <c r="AIA49" s="11"/>
+      <c r="AIB49" s="11"/>
+      <c r="AIC49" s="11"/>
+      <c r="AID49" s="11"/>
+      <c r="AIE49" s="11"/>
+      <c r="AIF49" s="11"/>
+      <c r="AIG49" s="11"/>
+      <c r="AIH49" s="11"/>
+      <c r="AII49" s="11"/>
+      <c r="AIJ49" s="11"/>
+      <c r="AIK49" s="11"/>
+      <c r="AIL49" s="11"/>
+      <c r="AIM49" s="11"/>
+      <c r="AIN49" s="11"/>
+      <c r="AIO49" s="11"/>
+      <c r="AIP49" s="11"/>
+      <c r="AIQ49" s="11"/>
+      <c r="AIR49" s="11"/>
+      <c r="AIS49" s="11"/>
+      <c r="AIT49" s="11"/>
+      <c r="AIU49" s="11"/>
+      <c r="AIV49" s="11"/>
+      <c r="AIW49" s="11"/>
+      <c r="AIX49" s="11"/>
+      <c r="AIY49" s="11"/>
+      <c r="AIZ49" s="11"/>
+      <c r="AJA49" s="11"/>
+      <c r="AJB49" s="11"/>
+      <c r="AJC49" s="11"/>
+      <c r="AJD49" s="11"/>
+      <c r="AJE49" s="11"/>
+      <c r="AJF49" s="11"/>
+      <c r="AJG49" s="11"/>
+      <c r="AJH49" s="11"/>
+      <c r="AJI49" s="11"/>
+      <c r="AJJ49" s="11"/>
+      <c r="AJK49" s="11"/>
+      <c r="AJL49" s="11"/>
+      <c r="AJM49" s="11"/>
+      <c r="AJN49" s="11"/>
+      <c r="AJO49" s="11"/>
+      <c r="AJP49" s="11"/>
+      <c r="AJQ49" s="11"/>
+      <c r="AJR49" s="11"/>
+      <c r="AJS49" s="11"/>
+      <c r="AJT49" s="11"/>
+      <c r="AJU49" s="11"/>
+      <c r="AJV49" s="11"/>
+      <c r="AJW49" s="11"/>
+      <c r="AJX49" s="11"/>
+      <c r="AJY49" s="11"/>
+      <c r="AJZ49" s="11"/>
+      <c r="AKA49" s="11"/>
+      <c r="AKB49" s="11"/>
+      <c r="AKC49" s="11"/>
+      <c r="AKD49" s="11"/>
+      <c r="AKE49" s="11"/>
+      <c r="AKF49" s="11"/>
+      <c r="AKG49" s="11"/>
+      <c r="AKH49" s="11"/>
+      <c r="AKI49" s="11"/>
+      <c r="AKJ49" s="11"/>
+      <c r="AKK49" s="11"/>
+      <c r="AKL49" s="11"/>
+      <c r="AKM49" s="11"/>
+      <c r="AKN49" s="11"/>
+      <c r="AKO49" s="11"/>
+      <c r="AKP49" s="11"/>
+      <c r="AKQ49" s="11"/>
+      <c r="AKR49" s="11"/>
+      <c r="AKS49" s="11"/>
+      <c r="AKT49" s="11"/>
+      <c r="AKU49" s="11"/>
+      <c r="AKV49" s="11"/>
+      <c r="AKW49" s="11"/>
+      <c r="AKX49" s="11"/>
+      <c r="AKY49" s="11"/>
+      <c r="AKZ49" s="11"/>
+      <c r="ALA49" s="11"/>
+      <c r="ALB49" s="11"/>
+      <c r="ALC49" s="11"/>
+      <c r="ALD49" s="11"/>
+      <c r="ALE49" s="11"/>
+      <c r="ALF49" s="11"/>
+      <c r="ALG49" s="11"/>
+      <c r="ALH49" s="11"/>
+      <c r="ALI49" s="11"/>
+      <c r="ALJ49" s="11"/>
+      <c r="ALK49" s="11"/>
+      <c r="ALL49" s="11"/>
+      <c r="ALM49" s="11"/>
+      <c r="ALN49" s="11"/>
+      <c r="ALO49" s="11"/>
+      <c r="ALP49" s="11"/>
+      <c r="ALQ49" s="11"/>
+      <c r="ALR49" s="11"/>
+      <c r="ALS49" s="11"/>
+      <c r="ALT49" s="11"/>
+      <c r="ALU49" s="11"/>
+      <c r="ALV49" s="11"/>
+      <c r="ALW49" s="11"/>
+      <c r="ALX49" s="11"/>
+      <c r="ALY49" s="11"/>
+      <c r="ALZ49" s="11"/>
+      <c r="AMA49" s="11"/>
+      <c r="AMB49" s="11"/>
+      <c r="AMC49" s="11"/>
+      <c r="AMD49" s="11"/>
+      <c r="AME49" s="11"/>
+      <c r="AMF49" s="11"/>
+      <c r="AMG49" s="11"/>
+      <c r="AMH49" s="11"/>
+      <c r="AMI49" s="11"/>
+      <c r="AMJ49" s="11"/>
+    </row>
+    <row r="50" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>3</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="17"/>
+    </row>
+    <row r="51" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E51" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F51" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G51" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H51" s="17"/>
-    </row>
-    <row r="52" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>29</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="20" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H52" s="17"/>
     </row>
-    <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="36" t="s">
-        <v>283</v>
+        <v>41</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
+      <c r="F53" s="10"/>
+      <c r="G53" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H53" s="17"/>
+    </row>
+    <row r="54" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="H53" s="36" t="s">
+      <c r="H54" s="36" t="s">
         <v>280</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B31:F31"/>
+  <mergeCells count="36">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
@@ -46370,21 +47428,15 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -46413,50 +47465,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>275</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -46491,14 +47543,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -46511,60 +47563,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -46592,13 +47644,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="55"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>100</v>
@@ -46673,10 +47725,10 @@
       <c r="B17" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="55"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
       <c r="G17" s="9" t="s">
         <v>290</v>
       </c>
@@ -46878,13 +47930,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -47156,13 +48208,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
@@ -47448,28 +48500,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B46:F46"/>
@@ -47483,6 +48513,28 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -47511,50 +48563,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="45"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="48" t="s">
         <v>276</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -47589,14 +48641,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -47609,60 +48661,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -47739,10 +48791,10 @@
       <c r="B15" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="55"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="9" t="s">
         <v>309</v>
       </c>
@@ -47944,13 +48996,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -48200,13 +49252,13 @@
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
       <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
@@ -48432,28 +49484,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
@@ -48464,6 +49494,28 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
